--- a/class1/excel/linear_model.xlsx
+++ b/class1/excel/linear_model.xlsx
@@ -1,19 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\snguyen4\Dropbox\git\math110\class1\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sonou\Dropbox\git\math110\class1\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF1E14D6-F621-4EF4-9B31-FC18F02AAF23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7672C4FF-F281-48D1-B145-C98FDDF2D5F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{4FAC78D1-5AA2-459B-93EB-3E606E562966}"/>
+    <workbookView xWindow="-156" yWindow="-156" windowWidth="31032" windowHeight="17592" activeTab="1" xr2:uid="{4FAC78D1-5AA2-459B-93EB-3E606E562966}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Employee Turnover" sheetId="1" r:id="rId1"/>
+    <sheet name="DirectTV" sheetId="2" r:id="rId2"/>
+    <sheet name="DirectTV (2)" sheetId="3" r:id="rId3"/>
+    <sheet name="DirectTV (3)" sheetId="6" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="17">
   <si>
     <t>E (Employee Turnover)</t>
   </si>
@@ -52,12 +55,52 @@
   <si>
     <t>Intercept</t>
   </si>
+  <si>
+    <t>Subcribers of DirectTV</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Subscribers</t>
+  </si>
+  <si>
+    <t>Rate of Change</t>
+  </si>
+  <si>
+    <t>Input</t>
+  </si>
+  <si>
+    <t>Output</t>
+  </si>
+  <si>
+    <t>Subscribers (millions)</t>
+  </si>
+  <si>
+    <t>Estimated Subscribers</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Error Perentage (EP)</t>
+  </si>
+  <si>
+    <t>Absolute EP (AEP)</t>
+  </si>
+  <si>
+    <t>Mean APE (MAPE)</t>
+  </si>
+  <si>
+    <t>Year (Since 1994)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -67,6 +110,13 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -91,10 +141,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -105,22 +156,232 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="22">
     <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -190,7 +451,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$B$1</c:f>
+              <c:f>'Employee Turnover'!$B$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -341,7 +602,7 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$5</c:f>
+              <c:f>'Employee Turnover'!$A$2:$A$5</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -362,7 +623,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$B$2:$B$5</c:f>
+              <c:f>'Employee Turnover'!$B$2:$B$5</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -710,7 +971,7 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$A$38:$A$42</c:f>
+              <c:f>'Employee Turnover'!$A$38:$A$42</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -734,7 +995,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$B$38:$B$42</c:f>
+              <c:f>'Employee Turnover'!$B$38:$B$42</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -950,6 +1211,2010 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>DirectTV!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v> Subscribers </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-6.6083434975360941E-2"/>
+                  <c:y val="-0.10149776732453898"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr>
+                      <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1">
+                            <a:lumMod val="65000"/>
+                            <a:lumOff val="35000"/>
+                          </a:schemeClr>
+                        </a:solidFill>
+                        <a:latin typeface="+mn-lt"/>
+                        <a:ea typeface="+mn-ea"/>
+                        <a:cs typeface="+mn-cs"/>
+                      </a:defRPr>
+                    </a:pPr>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="1500" baseline="0"/>
+                      <a:t>y = 1E+06x - 2E+09</a:t>
+                    </a:r>
+                    <a:endParaRPr lang="en-US" sz="1500"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>DirectTV!$A$4:$A$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>1994</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1995</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1996</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1997</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1998</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2002</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2003</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2004</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2014</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>DirectTV!$B$4:$B$22</c:f>
+              <c:numCache>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>320000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1200000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2300000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3301000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4458000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6679000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>9554000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>10218000</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>11181000</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>12290000</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>13000000</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>15000000</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>15950000</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>16830000</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>17620000</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>18081000</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>19200000</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>19900000</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>20265000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-6B31-4A85-B932-1CA7AF59FF53}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="246165840"/>
+        <c:axId val="246167280"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="246165840"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="246167280"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="246167280"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="246165840"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'DirectTV (2)'!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Subscribers (millions)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-1.5906870252464216E-2"/>
+                  <c:y val="-0.11906279689355168"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr>
+                      <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1">
+                            <a:lumMod val="65000"/>
+                            <a:lumOff val="35000"/>
+                          </a:schemeClr>
+                        </a:solidFill>
+                        <a:latin typeface="+mn-lt"/>
+                        <a:ea typeface="+mn-ea"/>
+                        <a:cs typeface="+mn-cs"/>
+                      </a:defRPr>
+                    </a:pPr>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="1500" baseline="0"/>
+                      <a:t>y = 1.116x - 2224</a:t>
+                    </a:r>
+                    <a:endParaRPr lang="en-US" sz="1500"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'DirectTV (2)'!$A$4:$A$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>1994</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1995</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1996</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1997</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1998</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2002</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2003</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2004</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2014</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'DirectTV (2)'!$B$4:$B$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>0.32</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.2999999999999998</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.3010000000000002</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.4580000000000002</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6.6790000000000003</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>9.5540000000000003</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>10.218</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>11.180999999999999</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>12.29</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>15.95</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>16.829999999999998</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>17.62</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>18.081</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>19.2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>19.899999999999999</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>20.265000000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-A69A-4D78-8471-3EA33FD5CAAC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'DirectTV (2)'!$C$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Estimated Subscribers</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'DirectTV (2)'!$A$4:$A$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>1994</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1995</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1996</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1997</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1998</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2002</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2003</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2004</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2014</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'DirectTV (2)'!$C$4:$C$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>1.3040000000000873</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.4200000000000728</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.5360000000000582</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.6520000000000437</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.7680000000000291</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6.8840000000000146</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9.1159999999999854</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10.232000000000426</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>11.348000000000411</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>12.464000000000397</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>13.580000000000382</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>14.696000000000367</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>15.812000000000353</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>16.928000000000338</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>18.044000000000324</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>19.160000000000309</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>21.39200000000028</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>23.624000000000251</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-A69A-4D78-8471-3EA33FD5CAAC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'DirectTV (2)'!$D$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v> Error Perentage (EP)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'DirectTV (2)'!$A$4:$A$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>1994</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1995</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1996</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1997</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1998</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2002</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2003</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2004</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2014</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'DirectTV (2)'!$D$4:$D$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>-3.0750000000002724</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-1.0166666666667274</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-0.53739130434785154</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-0.40926991820661723</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-0.29385374607447934</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-3.0693217547539193E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.16265438559765547</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.10784889410843751</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8.4876129147623075E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>7.6647681041463633E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4.1230769230738727E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>9.4666666666641197E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>7.8620689655149331E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>6.0487225193086483E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3.9273552780911616E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2.046346994064252E-3</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2.0833333333171908E-3</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-7.4974874371873446E-2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-0.16575376264496672</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-A69A-4D78-8471-3EA33FD5CAAC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'DirectTV (2)'!$E$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Absolute EP (AEP)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'DirectTV (2)'!$A$4:$A$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>1994</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1995</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1996</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1997</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1998</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2002</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2003</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2004</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2014</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'DirectTV (2)'!$E$4:$E$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>3.0750000000002724</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.0166666666667274</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.53739130434785154</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.40926991820661723</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.29385374607447934</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.0693217547539193E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.16265438559765547</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.10784889410843751</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8.4876129147623075E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>7.6647681041463633E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4.1230769230738727E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>9.4666666666641197E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>7.8620689655149331E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>6.0487225193086483E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3.9273552780911616E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2.046346994064252E-3</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2.0833333333171908E-3</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>7.4974874371873446E-2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.16575376264496672</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-A69A-4D78-8471-3EA33FD5CAAC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="246165840"/>
+        <c:axId val="246167280"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="246165840"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="246167280"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="246167280"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="246165840"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0.18233945756780404"/>
+                  <c:y val="-0.15782407407407406"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr>
+                      <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1">
+                            <a:lumMod val="65000"/>
+                            <a:lumOff val="35000"/>
+                          </a:schemeClr>
+                        </a:solidFill>
+                        <a:latin typeface="+mn-lt"/>
+                        <a:ea typeface="+mn-ea"/>
+                        <a:cs typeface="+mn-cs"/>
+                      </a:defRPr>
+                    </a:pPr>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="1500" baseline="0"/>
+                      <a:t>y = 1.116x + 1.2194</a:t>
+                    </a:r>
+                    <a:endParaRPr lang="en-US" sz="1500"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'DirectTV (3)'!$A$4:$A$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'DirectTV (3)'!$B$4:$B$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>0.32</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.2999999999999998</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.3010000000000002</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.4580000000000002</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6.6790000000000003</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>9.5540000000000003</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>10.218</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>11.180999999999999</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>12.29</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>15.95</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>16.829999999999998</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>17.62</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>18.081</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>19.2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>19.899999999999999</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>20.265000000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-12D4-4758-8491-9D20107A280F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="429548112"/>
+        <c:axId val="772604992"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="429548112"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="772604992"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="772604992"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="429548112"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -1030,6 +3295,126 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -1547,6 +3932,1554 @@
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -2139,12 +6072,1428 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>42403</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>99909</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>147638</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>137853</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A52EE70A-C839-6E69-FA54-C0A2336B3B1D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10667541" y="5710134"/>
+          <a:ext cx="2048335" cy="6191094"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>257173</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{036C7B38-33F8-393B-912A-6F9D57B2AF04}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>197048</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>65471</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>317648</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>489</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="5" name="Ink 4">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EC3306CA-ABD6-D539-1FA9-12919B457DBB}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="6923618" y="427273"/>
+            <a:ext cx="120600" cy="115920"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="5" name="Ink 4">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EC3306CA-ABD6-D539-1FA9-12919B457DBB}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="6869618" y="319633"/>
+              <a:ext cx="228240" cy="331560"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>349812</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>61151</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>369612</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>162671</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="6" name="Ink 5">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5A213713-7069-78A2-4CBE-6976845FF836}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="7722458" y="422953"/>
+            <a:ext cx="19800" cy="101520"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="6" name="Ink 5">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5A213713-7069-78A2-4CBE-6976845FF836}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7668818" y="315313"/>
+              <a:ext cx="127440" cy="317160"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>493004</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>160330</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>349834</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>50054</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="9" name="Ink 8">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{09019AD6-9CAE-4D24-7741-FC6B0E6AEDAF}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="7234088" y="524160"/>
+            <a:ext cx="1152720" cy="71640"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="9" name="Ink 8">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{09019AD6-9CAE-4D24-7741-FC6B0E6AEDAF}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7216448" y="506431"/>
+              <a:ext cx="1188360" cy="107460"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>464361</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>21199</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>54710</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>7478</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="21" name="Ink 20">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8BB2DA6-DA2E-81AC-DE18-1975D21C58E9}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="9781543" y="203040"/>
+            <a:ext cx="883440" cy="168120"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="21" name="Ink 20">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8BB2DA6-DA2E-81AC-DE18-1975D21C58E9}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="9763903" y="185362"/>
+              <a:ext cx="919080" cy="203836"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>298430</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>115879</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>435230</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>10358</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="24" name="Ink 23">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E40A12E3-C469-CE28-F938-A03F1F22EF26}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="10908703" y="297720"/>
+            <a:ext cx="136800" cy="76320"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="24" name="Ink 23">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E40A12E3-C469-CE28-F938-A03F1F22EF26}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="10891063" y="280080"/>
+              <a:ext cx="172440" cy="111960"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>43565</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>72679</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>48965</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>6758</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId13">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="26" name="Ink 25">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4294FE82-4DCE-4638-2B63-64F1E517CEEE}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="11300383" y="254520"/>
+            <a:ext cx="5400" cy="115920"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="26" name="Ink 25">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4294FE82-4DCE-4638-2B63-64F1E517CEEE}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="11282743" y="236880"/>
+              <a:ext cx="41040" cy="151560"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>123125</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>67279</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>416899</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>68678</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="39" name="Ink 38">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E0D011B-16EE-F0DF-7F63-BC4D3A4BA89C}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="11379943" y="249120"/>
+            <a:ext cx="940320" cy="183240"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="39" name="Ink 38">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E0D011B-16EE-F0DF-7F63-BC4D3A4BA89C}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="11361950" y="231445"/>
+              <a:ext cx="975946" cy="218950"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>457521</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>66477</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>97896</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>41596</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId17">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="45" name="Ink 44">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1FC16C68-2AF7-EA73-9264-E2DA4561E091}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="9774703" y="612000"/>
+            <a:ext cx="286920" cy="156960"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="45" name="Ink 44">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1FC16C68-2AF7-EA73-9264-E2DA4561E091}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="9756703" y="594000"/>
+              <a:ext cx="322560" cy="192600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>305616</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>38037</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>84950</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>44116</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId19">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="50" name="Ink 49">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{80442C08-BFB5-BCE5-2F31-242CAF9B2F06}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="10269343" y="583560"/>
+            <a:ext cx="425880" cy="187920"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="50" name="Ink 49">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{80442C08-BFB5-BCE5-2F31-242CAF9B2F06}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="10251343" y="565560"/>
+              <a:ext cx="461520" cy="223560"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>296270</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>118317</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>410390</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>3796</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId21">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="53" name="Ink 52">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C4F1D1C-A507-2348-86A0-08478E3882E8}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="10906543" y="663840"/>
+            <a:ext cx="114120" cy="67320"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="53" name="Ink 52">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C4F1D1C-A507-2348-86A0-08478E3882E8}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId22"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="10897543" y="654888"/>
+              <a:ext cx="131760" cy="84866"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>599750</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>80157</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>138274</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>44476</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId23">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="71" name="Ink 70">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F60FA78-9871-903B-E640-912525CD3CA8}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="11210023" y="625680"/>
+            <a:ext cx="1478160" cy="146160"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="71" name="Ink 70">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F60FA78-9871-903B-E640-912525CD3CA8}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId24"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="11201023" y="617040"/>
+              <a:ext cx="1495800" cy="163800"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>42403</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>99909</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>147638</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>137853</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1204A2FB-3B86-4353-AEC8-6223D9446EF6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10924716" y="5710134"/>
+          <a:ext cx="2048335" cy="6191094"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>261280</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>154536</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>544391</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>114923</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{95782C05-CACE-4D52-84AB-DE5CE253B8B3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>42403</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>99909</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>147639</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>137853</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AA47E284-55DF-4A08-89DA-02813C2C30FE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15577678" y="5710134"/>
+          <a:ext cx="2048335" cy="6191094"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>607009</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>161589</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>646279</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>30579</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E027086-ED90-01FB-FAD8-2101C349284F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/ink/ink1.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+          <inkml:channel name="OA" type="integer" max="360" units="deg"/>
+          <inkml:channel name="OE" type="integer" max="90" units="deg"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+          <inkml:channelProperty channel="OA" name="resolution" value="1000" units="1/deg"/>
+          <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2025-02-11T19:42:27.356"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.3" units="cm"/>
+      <inkml:brushProperty name="height" value="0.6" units="cm"/>
+      <inkml:brushProperty name="color" value="#FFFC00"/>
+      <inkml:brushProperty name="tip" value="rectangle"/>
+      <inkml:brushProperty name="rasterOp" value="maskPen"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">29 203 7711 0 0,'-24'2'175'0'0,"24"-2"-159"0"0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 1 0 0,0-1-1 0 0,-1 1 1 0 0,1 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0-1 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,-1 0-1 0 0,1-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0-1-1 0 0,1 1 1 0 0,-1-1-1 0 0,4-13 76 0 0,-4 14-85 0 0,4-9 149 0 0,0-1 0 0 0,1 1 1 0 0,0 1-1 0 0,0-1 0 0 0,1 1 0 0 0,0 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 1 1 0 0,0 0-1 0 0,1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,14-7 0 0 0,-8 6-139 0 0,0 0 0 0 0,1 1-1 0 0,0 0 1 0 0,0 1 0 0 0,0 1-1 0 0,1 1 1 0 0,-1 0-1 0 0,25-2 1 0 0,-37 5 9 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,1 0 0 0 0,-1-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 1 0 0 0,1-1 1 0 0,0 0-1 0 0,-1 1 0 0 0,1 0 1 0 0,0-1-1 0 0,-1 1 0 0 0,2 3 0 0 0,-1-2-10 0 0,0 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,-1 8 0 0 0,-1-2 82 0 0,-1-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,-1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,-1-1 0 0 0,-11 16 1 0 0,12-18-91 0 0,-1-1 1 0 0,0 1-1 0 0,0-1 0 0 0,-1 0 1 0 0,1-1-1 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,-1-1 0 0 0,-7 3 1 0 0,5-2 107 0 0,-1-1 1 0 0,1 0-1 0 0,-1-1 1 0 0,1 0-1 0 0,-1-1 1 0 0,0 1-1 0 0,-17-2 1 0 0,25 0-80 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,1-1 1 0 0,0 1-1 0 0,-1-1 0 0 0,1 0 1 0 0,0 0-1 0 0,-1 1 0 0 0,1-2 1 0 0,0 1-1 0 0,0 0 0 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,-2-3 1 0 0,2 2 26 0 0,1 0 1 0 0,-1 0 0 0 0,1-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1-1 0 0,1-1 1 0 0,-1 1 0 0 0,1-1-1 0 0,0 0 1 0 0,0 1 0 0 0,1-7 0 0 0,1-1-71 0 0,0 0 0 0 0,0 1 0 0 0,1-1 0 0 0,1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,1 1 0 0 0,6-9 0 0 0,-7 12-1 0 0,0 1 0 0 0,0 0 0 0 0,1 0 0 0 0,0 1 0 0 0,1-1 1 0 0,-1 1-1 0 0,1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0 0 0 0 0,1 0 0 0 0,11-6 0 0 0,-14 9 4 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,6 2 0 0 0,-7-2 2 0 0,-1 1-1 0 0,1-1 0 0 0,-1 1 1 0 0,0-1-1 0 0,0 1 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 1 0 0,-1 1-1 0 0,1-1 0 0 0,-1 1 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 1 0 0,0-1-1 0 0,-1 1 0 0 0,1 0 1 0 0,0 0-1 0 0,-1 4 0 0 0,1 7 26 0 0,0 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,-2-1 0 0 0,-3 22 0 0 0,3-28-9 0 0,0-1 0 0 0,0 0 1 0 0,0 1-1 0 0,-1-1 0 0 0,0-1 1 0 0,0 1-1 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 1 0 0,0-1-1 0 0,-1 0 0 0 0,1-1 0 0 0,-10 9 1 0 0,3-6 49 0 0,0 0 1 0 0,-1 0 0 0 0,1-1-1 0 0,-1 0 1 0 0,-1-1 0 0 0,-13 3 0 0 0,3-1 437 0 0,0-2 0 0 0,-36 4 1 0 0,57-9-459 0 0,0 0 1 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,1-1-1 0 0,-4 0 1 0 0,4 0-40 0 0,0 1 0 0 0,1 0 1 0 0,-1-1-1 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 1 0 0,-1 1-1 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 1 0 0,0 0-1 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 1 0 0 0,0-1 0 0 0,0-1 0 0 0,1-5-5 0 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink10.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+          <inkml:channel name="OA" type="integer" max="360" units="deg"/>
+          <inkml:channel name="OE" type="integer" max="90" units="deg"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+          <inkml:channelProperty channel="OA" name="resolution" value="1000" units="1/deg"/>
+          <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2025-02-11T19:45:27.870"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.05" units="cm"/>
+      <inkml:brushProperty name="height" value="0.05" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">14 59 9095 0 0,'-14'10'9414'0'0,"22"-11"-7386"0"0,136-39 1141 0 0,-100 28-3036 0 0,18-4-3218 0 0,-54 17-824 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="319.81">9 187 14623 0 0,'10'0'5202'0'0,"17"-1"-3385"0"0,72-3 75 0 0,41-4-176 0 0,-118 3-1478 0 0,-13 2-7476 0 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink11.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+          <inkml:channel name="OA" type="integer" max="360" units="deg"/>
+          <inkml:channel name="OE" type="integer" max="90" units="deg"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+          <inkml:channelProperty channel="OA" name="resolution" value="1000" units="1/deg"/>
+          <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2025-02-11T19:45:29.446"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.05" units="cm"/>
+      <inkml:brushProperty name="height" value="0.05" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 25 10591 0 0,'5'-8'1704'0'0,"1"5"-1264"0"0,0 1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 1 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 1-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 1 1 0 0,8 2-1 0 0,-12-2-281 0 0,1 0-1 0 0,-1 1 0 0 0,1 0 1 0 0,-1-1-1 0 0,1 1 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,3 5 0 0 0,-1-1-23 0 0,0 0-1 0 0,0 1 0 0 0,3 7 0 0 0,-5-9-115 0 0,0 1-1 0 0,-1-1 1 0 0,1 1-1 0 0,-1 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,0-1 1 0 0,1 1-1 0 0,-2 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 0 0 0,-1-1 1 0 0,0 1-1 0 0,-1-1 1 0 0,0 0-1 0 0,1 0 1 0 0,-7 9-1 0 0,-34 44-21 0 0,43-58 16 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,10 2 550 0 0,11-2 788 0 0,-21 0-1243 0 0,4-1 240 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 0 0 0 0,7-4 0 0 0,-6 4-288 0 0,-1-1 0 0 0,1 1-1 0 0,0 0 1 0 0,6-2 0 0 0,-8 4-613 0 0,-1-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,3 1 0 0 0,3 1-1491 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="666.29">477 276 16583 0 0,'1'0'102'0'0,"-1"0"-1"0"0,1 0 1 0 0,-1 1 0 0 0,0-1-1 0 0,1 0 1 0 0,-1 1 0 0 0,0-1-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 1 1 0 0,1-1 0 0 0,-1 1-1 0 0,0-1 1 0 0,0 0-1 0 0,1 1 1 0 0,-1-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,1 1-1 0 0,-1-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1-1 0 0,0 1 1 0 0,-2 17 1941 0 0,-1-11-1737 0 0,1 0 0 0 0,-1 0 0 0 0,-3 6 0 0 0,-7 8-2854 0 0,8-14 1557 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1317.64">849 68 11167 0 0,'-3'-19'2726'0'0,"3"15"-2300"0"0,-1 0-1 0 0,1 1 1 0 0,-1-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 1 0 0 0,-1 0-1 0 0,-2-5 1 0 0,4 8-422 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,-1-1-1 0 0,1 0 1 0 0,-6 8 213 0 0,-3 10 222 0 0,9-18-422 0 0,-7 16 463 0 0,-1 0 0 0 0,0-1 0 0 0,-1 0 0 0 0,-1 0-1 0 0,0-1 1 0 0,-1 0 0 0 0,-22 22 0 0 0,30-34-434 0 0,1 1 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,0 1 1 0 0,1-1-1 0 0,-1 1 0 0 0,1-1 1 0 0,0 1-1 0 0,1 0 1 0 0,-1-1-1 0 0,0 1 1 0 0,1 0-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,1-1 1 0 0,0 1-1 0 0,2 3 0 0 0,-2-4-58 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,1-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 1 0 0 0,1-1-1 0 0,-1 0 1 0 0,1-1 0 0 0,-1 1 0 0 0,1 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0 0 0 0,1-1-1 0 0,-1 1 1 0 0,0-1 0 0 0,0 1-1 0 0,6-1 1 0 0,-1-1-32 0 0,0 0 0 0 0,-1-1 1 0 0,1 0-1 0 0,0 0 0 0 0,-1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,8-12 0 0 0,-9 11 189 0 0,-1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,-2-9 0 0 0,2 12-149 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 1 0 0 0,-7-4 0 0 0,-11-10-3387 0 0,17 13 1557 0 0,3-1-20 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1860.78">1214 46 13703 0 0,'-1'-3'437'0'0,"-1"0"0"0"0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1-1 0 0,-3-2 1 0 0,-5-7 384 0 0,10 12-825 0 0,-1-1-1 0 0,1 0 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,1-1 0 0 0,-1 0 1 0 0,1 1-1 0 0,-1-1 1 0 0,0 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,0 0 1 0 0,1-1-1 0 0,-1 1 1 0 0,0 0-1 0 0,0-1 0 0 0,1 1 1 0 0,-1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,0 0 39 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,-1 3 0 0 0,-4 2 329 0 0,1 1 0 0 0,0 1 0 0 0,-7 11 0 0 0,-53 95 1720 0 0,64-111-2036 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 1 0 0,1 0-1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 1 0 0,1 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,1 3-1 0 0,0-3-37 0 0,-1 0 0 0 0,1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,5-1-1 0 0,-4 0-9 0 0,1 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,4-5 0 0 0,-5 4 211 0 0,0 1-1 0 0,0 0 1 0 0,0-1 0 0 0,-1 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0-8 1 0 0,-2 10-146 0 0,1 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,-3-4 0 0 0,2 3-557 0 0,0 0 1 0 0,0-1 0 0 0,1 1-1 0 0,-1 0 1 0 0,0-5 0 0 0,1 2-501 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2417.79">1475 42 11399 0 0,'-1'-2'524'0'0,"0"0"-1"0"0,0 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,-2-3 1 0 0,3 5-327 0 0,0-1 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 1-1 0 0,0-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,0 0-1 0 0,0 1 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,-3 1 188 0 0,1 1-1 0 0,0-1 1 0 0,0 1-1 0 0,1 0 1 0 0,-1 1-1 0 0,0-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 1 0 0,0 0 0 0 0,-3 5-1 0 0,-6 7-481 0 0,-15 26 0 0 0,8-10 492 0 0,16-27-358 0 0,0 1 1 0 0,1-1-1 0 0,0 1 0 0 0,-1 0 1 0 0,2 0-1 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 1 0 0,1 0-1 0 0,1 0 0 0 0,-1 1 1 0 0,1-1-1 0 0,1 11 0 0 0,-1-13-33 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 1 0 0,1 0-1 0 0,-1-1 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,4 0 0 0 0,1 1-13 0 0,1-1-1 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0-1 1 0 0,-1 0-1 0 0,1 0 1 0 0,0-1-1 0 0,0 0 0 0 0,-1 0 1 0 0,1-1-1 0 0,-1 0 1 0 0,0-1-1 0 0,0 0 1 0 0,0 0-1 0 0,10-8 0 0 0,-15 9 81 0 0,0 1-1 0 0,0-1 0 0 0,0 0 1 0 0,-1 0-1 0 0,0-1 0 0 0,1 1 1 0 0,-1 0-1 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 0 0 0 0,-1-5 1 0 0,0 4 36 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,-1 1 0 0 0,0-1-1 0 0,0 1 1 0 0,-1 0 0 0 0,0 0 0 0 0,1-1 0 0 0,-2 1-1 0 0,-4-9 1 0 0,-5-2-1651 0 0,9 13 878 0 0,0-1 0 0 0,0 1-1 0 0,1 0 1 0 0,0-1 0 0 0,-1 0-1 0 0,1 1 1 0 0,-1-6 0 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2783.82">1756 296 15431 0 0,'2'2'1512'0'0,"0"-1"-1352"0"0,-1 0-160 0 0,-2-1 0 0 0,-2 3 1160 0 0,2 0 200 0 0,-1 3 40 0 0,-2 2 8 0 0,-2-1-696 0 0,1 2-136 0 0,-2-1-24 0 0,-2 0-8 0 0,3-1-920 0 0,-1 0-184 0 0,-1 1-40 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3455.38">2211 73 7943 0 0,'-3'-4'555'0'0,"3"3"-472"0"0,0 1 0 0 0,-1-1 0 0 0,1 1-1 0 0,0-1 1 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1-1 0 0,-1 0 1 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,-2 0 0 0 0,1-1 152 0 0,-1 1 0 0 0,1 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,-2 2 0 0 0,0 1 85 0 0,-1 1 0 0 0,1 0 1 0 0,0 0-1 0 0,-5 10 0 0 0,6-9-166 0 0,-1-1 0 0 0,0 0 0 0 0,0 1-1 0 0,-4 4 1 0 0,-29 23 1615 0 0,27-25-1347 0 0,0-1 0 0 0,1 2 0 0 0,0-1 0 0 0,0 1 0 0 0,-11 17 0 0 0,17-23-416 0 0,1-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,2 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,0 0 0 0 0,-1-1 0 0 0,4 4 0 0 0,-3-4-28 0 0,1 0-1 0 0,-1-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0-1-1 0 0,1 0 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,-1-1 1 0 0,1 1-1 0 0,0-1 1 0 0,0 1-1 0 0,-1-1 1 0 0,1 0 0 0 0,0 0-1 0 0,2-1 1 0 0,4 1-53 0 0,-1-1 1 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,8-4 0 0 0,-5 2 13 0 0,-1 0 1 0 0,0-1-1 0 0,-1-1 1 0 0,1 0-1 0 0,-1 0 1 0 0,0-1-1 0 0,16-15 1 0 0,-20 17 253 0 0,0-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,3-13-1 0 0,-6 17-94 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1-1 0 0,-1 0 1 0 0,1 1 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1-1 0 0,-2-2 1 0 0,-7-11-1840 0 0,10 9-1844 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3875.66">2542 91 13703 0 0,'-3'-11'799'0'0,"3"9"-585"0"0,0 1-1 0 0,-1-1 0 0 0,1 0 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,1 1 0 0 0,-1-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 1 0 0,-3-1-1 0 0,3 1-156 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-2 0 0 0 0,-21 19 161 0 0,19-15-166 0 0,-19 16 367 0 0,-44 33-1 0 0,64-52-348 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 5-1 0 0,1-6-118 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,1-1 1 0 0,-1 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,1-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0-1 0 0,1 1 1 0 0,-1-1 0 0 0,1 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,0 1 1 0 0,1-1 0 0 0,2 0-1 0 0,1 1-246 0 0,1-1-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1-1 1 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1-1-1 0 0,1 0 1 0 0,-1 0-1 0 0,0-1 1 0 0,9-3 0 0 0,-8 3 398 0 0,0-1 0 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 1 0 0,1 0-1 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 1 0 0,5-7-1 0 0,-7 7 453 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-9 0 0 0,-2 11-697 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0-1 0 0 0,-1 1 1 0 0,-1-6-1 0 0,1 8-995 0 0,2-1-13 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4190.02">2830 28 14167 0 0,'0'0'69'0'0,"0"-1"-1"0"0,1 1 1 0 0,-1 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,-1-1-1 0 0,1 1 1 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,-1 0 1 0 0,1-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0 0-1 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 1 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1-1-1 0 0,0 1 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-14 4 1621 0 0,-14 16-303 0 0,27-19-1366 0 0,-15 13 596 0 0,-27 29-1 0 0,36-35-452 0 0,1 0 0 0 0,0 0-1 0 0,1 1 1 0 0,0-1-1 0 0,0 1 1 0 0,-4 11-1 0 0,8-18-163 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,4 2 0 0 0,-1-1-165 0 0,1-1 0 0 0,-1 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,1-1 0 0 0,0-1 0 0 0,0 1-1 0 0,-1-1 1 0 0,1 1 0 0 0,0-1 0 0 0,0-1-1 0 0,0 1 1 0 0,5-2 0 0 0,-4 1 59 0 0,0-1 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,7-8-1 0 0,-9 9 360 0 0,-1-1-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,-1-1 0 0 0,1 1 1 0 0,-1 0-1 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,-1 1-1 0 0,0-1 0 0 0,0 0 1 0 0,-1-5-1 0 0,0 1 517 0 0,0 0 0 0 0,-6-15 0 0 0,-2 5-1535 0 0,-2 3-5994 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4475.44">2996 314 15551 0 0,'0'7'344'0'0,"-1"-4"72"0"0,1 0 8 0 0,0-1 8 0 0,-2 0-344 0 0,0 0-88 0 0,1 0 0 0 0,-3 2 0 0 0,-2 3 528 0 0,-1 1 88 0 0,-1 2 24 0 0,0-2 0 0 0,-1 0-928 0 0,3 0-176 0 0,-1-1-40 0 0,-1 4-8 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4966.65">3526 30 11519 0 0,'0'0'25'0'0,"0"-1"1"0"0,0 1-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0-1 0 0 0,-9 7 870 0 0,-2 5-82 0 0,7-6-346 0 0,2-4-441 0 0,-21 28 772 0 0,-2-2-1 0 0,-30 25 1 0 0,48-46-335 0 0,-1 1 0 0 0,1-1 1 0 0,1 1-1 0 0,-1 1 0 0 0,1-1 0 0 0,-7 12 0 0 0,12-17-417 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0-1 0 0,1 0 1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,0-1 0 0 0,1 1-1 0 0,-1 0 1 0 0,0 0 0 0 0,0-1 0 0 0,1 1-1 0 0,-1-1 1 0 0,1 0 0 0 0,-1 1 0 0 0,1-1-1 0 0,3 2 1 0 0,0 0-445 0 0,1 0 1 0 0,-1 0-1 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 0 0 0,0-2 0 0 0,0 1 1 0 0,-1-1-1 0 0,1 1 0 0 0,0-2 0 0 0,-1 1 0 0 0,0 0 0 0 0,1-1 1 0 0,-1 0-1 0 0,6-5 0 0 0,-7 5 555 0 0,0-1 1 0 0,0 0-1 0 0,0 0 1 0 0,5-6-1 0 0,-6 6 706 0 0,0 0 1 0 0,-1-1-1 0 0,1 1 0 0 0,3-11 1 0 0,-5 12-399 0 0,1-1 0 0 0,-1 0 1 0 0,0 1-1 0 0,0-1 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1-3 1 0 0,0 3-340 0 0,-1 0 1 0 0,1 1 0 0 0,0-1-1 0 0,-1 1 1 0 0,0-1 0 0 0,-3-5-1 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5340.85">3773 111 13703 0 0,'0'-6'457'0'0,"0"3"47"0"0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,0-3 1 0 0,0 6-419 0 0,1-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0-1-1 0 0,-1 1 1 0 0,1 0-1 0 0,0-1 1 0 0,0 1-1 0 0,-1 0 1 0 0,1-1-1 0 0,0 1 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0-1-1 0 0,0 1-25 0 0,0 0 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,-2 0 1 0 0,-7 5 110 0 0,0 0 1 0 0,1 1 0 0 0,-10 9 0 0 0,-9 6 32 0 0,12-11-12 0 0,4-4-69 0 0,0 2-1 0 0,1-1 1 0 0,0 1-1 0 0,0 1 1 0 0,-14 17-1 0 0,24-27-97 0 0,1 1 0 0 0,-1 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,1 1 0 0 0,0-1-27 0 0,-1 1 1 0 0,1-1-1 0 0,0 0 1 0 0,0 1-1 0 0,0-1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,2 1 1 0 0,3 0-189 0 0,-1 0 1 0 0,0 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1-1 0 0 0,1 0-1 0 0,6 0 1 0 0,-6 0-177 0 0,1-1 1 0 0,0 0-1 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 1 0 0,1 0-1 0 0,-1 0 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1-1 0 0 0,-1 0 0 0 0,8-8 0 0 0,-9 8 439 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,4-7 0 0 0,-5 7 583 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 0-1 0 0,0-9 1 0 0,-2 13-502 0 0,0 0 0 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 1 0 0,-2-2-1 0 0,-3-2-4805 0 0,11 9 2955 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5700.92">4067 41 14623 0 0,'0'0'715'0'0,"-6"8"178"0"0,-50 52 1128 0 0,-7 8-514 0 0,61-65-1455 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 1 0 0 0,1-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1-1 0 0,0 5 1 0 0,1-6-28 0 0,1 1 1 0 0,-1-1-1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 1 0 0,0 1-1 0 0,-1-1 0 0 0,1 0 0 0 0,2 1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,5-3 0 0 0,-7 3 8 0 0,1-1-1 0 0,-1 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,-1-1-1 0 0,1 1 0 0 0,-1-1 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,-1 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0-1-1 0 0,-1 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,0 0 1 0 0,0-3-1 0 0,-1 1 446 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,-3-8-1 0 0,-2-6 1016 0 0,8 9-518 0 0,0 8-2189 0 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink2.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+          <inkml:channel name="OA" type="integer" max="360" units="deg"/>
+          <inkml:channel name="OE" type="integer" max="90" units="deg"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+          <inkml:channelProperty channel="OA" name="resolution" value="1000" units="1/deg"/>
+          <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2025-02-11T19:42:28.663"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.3" units="cm"/>
+      <inkml:brushProperty name="height" value="0.6" units="cm"/>
+      <inkml:brushProperty name="color" value="#FFFC00"/>
+      <inkml:brushProperty name="tip" value="rectangle"/>
+      <inkml:brushProperty name="rasterOp" value="maskPen"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">23 143 6911 0 0,'0'-1'10'0'0,"-1"1"-1"0"0,1 0 0 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 1 0 0,-1-1-1 0 0,1 1 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1-1 0 0 0,1 1 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1-1 0 0 0,1 1 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 1 1 0 0,1-1-1 0 0,-1 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 1 0 0 0,1-1 1 0 0,-1 0-1 0 0,1 1 0 0 0,-1 0 38 0 0,0 1-1 0 0,1 0 1 0 0,0-1-1 0 0,-1 1 0 0 0,1 0 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,0 2 0 0 0,0 8-41 0 0,-3 96 1856 0 0,3-108-1855 0 0,0 0 7 0 0,0 0 0 0 0,0 0-7 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,1 0 1 0 0,-1 1 127 0 0,0-1-128 0 0,1 0 7 0 0,-1 0-7 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 1 1 0 0,4-9 323 0 0,5-11 267 0 0,4-44 223 0 0,9-89-1 0 0,-19 137-547 0 0,-4 25 167 0 0,-7 20-74 0 0,4-12-331 0 0,-11 28-1 0 0,-5-2 52 0 0,20-44-83 0 0,-1 0 0 0 0,1-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,-1-13 48 0 0,1 1 24 0 0,1-1-1 0 0,0 1 1 0 0,1-1-1 0 0,0 1 1 0 0,2 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,1 0-1 0 0,0 1 1 0 0,12-20 303 0 0,-30 42 1071 0 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink3.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+          <inkml:channel name="OA" type="integer" max="360" units="deg"/>
+          <inkml:channel name="OE" type="integer" max="90" units="deg"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+          <inkml:channelProperty channel="OA" name="resolution" value="1000" units="1/deg"/>
+          <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2025-02-11T19:43:08.602"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.1" units="cm"/>
+      <inkml:brushProperty name="height" value="0.1" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 97 4607 0 0,'41'-5'1812'0'0,"3"-2"-265"0"0,-27 5-1339 0 0,-1-1 1 0 0,0 0-1 0 0,21-8 0 0 0,-21 7-14 0 0,-1 0-1 0 0,1 0 1 0 0,0 2-1 0 0,-1 0 1 0 0,1 1-1 0 0,24 1 0 0 0,21-2 115 0 0,-13-5-153 0 0,-33 5-1 0 0,-1-1 0 0 0,1 2 0 0 0,-1 0 0 0 0,22 2 0 0 0,-31-1-124 0 0,-1 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 1-1 0 0,0 0 1 0 0,0-1-1 0 0,-1 2 1 0 0,1-1 0 0 0,0 0-1 0 0,-1 1 1 0 0,0-1-1 0 0,1 1 1 0 0,-1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 1-1 0 0,-1-1 1 0 0,3 4-1 0 0,29 62-9 0 0,-25-51 88 0 0,-8-16-86 0 0,0 0 154 0 0,0 1-1 0 0,0 0 0 0 0,0 0 1 0 0,1-1-1 0 0,0 1 0 0 0,-1-1 1 0 0,1 1-1 0 0,4 3 0 0 0,-6-9-41 0 0,1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,3-5 0 0 0,4-2-150 0 0,-1 0-1 0 0,1 1 1 0 0,1-1-1 0 0,0 1 1 0 0,0 1-1 0 0,0 0 1 0 0,1 0-1 0 0,0 1 1 0 0,0 0-1 0 0,1 1 1 0 0,0 0-1 0 0,0 1 1 0 0,0 0-1 0 0,0 0 1 0 0,1 1-1 0 0,-1 1 1 0 0,1 0-1 0 0,16 0 1 0 0,-22 2 76 0 0,-1 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,11 4 0 0 0,9 1 44 0 0,40 2-87 0 0,-58-7 46 0 0,0-1-1 0 0,-1 0 1 0 0,1-1-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,11-4-1 0 0,-16 5-72 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0-1 0 0,1-1 1 0 0,-1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 0 0 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1584.34">1836 120 7023 0 0,'3'0'140'0'0,"0"-1"-1"0"0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,4-3 0 0 0,6-3 119 0 0,9 0 127 0 0,-1 1-1 0 0,1 0 1 0 0,0 2 0 0 0,34-2-1 0 0,-27 3 301 0 0,55-14-1 0 0,-67 13-613 0 0,0 1-1 0 0,1 0 1 0 0,-1 1-1 0 0,0 1 0 0 0,1 1 1 0 0,0 0-1 0 0,-1 1 1 0 0,0 1-1 0 0,33 7 0 0 0,-43-6-39 0 0,0 0-1 0 0,0 0 1 0 0,0 1-1 0 0,0 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,1 1 1 0 0,-2 0-1 0 0,8 7 0 0 0,5 7 138 0 0,20 28 0 0 0,-37-47-136 0 0,-1 1 1 0 0,1-1-1 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 69 0 0,1-1 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,0-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,1 0-1 0 0,-1 1 1 0 0,0-1-1 0 0,0 0 1 0 0,1 0-1 0 0,-1 1 0 0 0,0-1 1 0 0,1 0-1 0 0,-3 0 1 0 0,41-14 1087 0 0,-29 9-1093 0 0,1 0-1 0 0,-1 0 0 0 0,0-1 1 0 0,0 0-1 0 0,15-14 0 0 0,-18 13-21 0 0,1 1-1 0 0,1 0 1 0 0,-1 1 0 0 0,1-1-1 0 0,0 2 1 0 0,0-1 0 0 0,0 1-1 0 0,17-6 1 0 0,-12 7-17 0 0,0 1 1 0 0,0 0-1 0 0,0 1 1 0 0,0 1-1 0 0,19 1 0 0 0,64 13-971 0 0,2 1 2063 0 0,-82-14-1174 0 0,-1 0 0 0 0,1-1 0 0 0,0 0 0 0 0,0-1 1 0 0,0-1-1 0 0,0-1 0 0 0,-1 0 0 0 0,1-1 0 0 0,14-6 1 0 0,-19 6 127 0 0,-4 2 10 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,10-10 1 0 0,-15 13-142 0 0,0 0-1 0 0,-1 0 1 0 0,0 1 0 0 0,1-1-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,0 0-1 0 0,-1-1 1 0 0,0-1-606 0 0,4 2-5 0 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink4.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+          <inkml:channel name="OA" type="integer" max="360" units="deg"/>
+          <inkml:channel name="OE" type="integer" max="90" units="deg"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+          <inkml:channelProperty channel="OA" name="resolution" value="1000" units="1/deg"/>
+          <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2025-02-11T19:43:17.618"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.1" units="cm"/>
+      <inkml:brushProperty name="height" value="0.1" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 92 8751 0 0,'3'0'2294'0'0,"-3"0"-2261"0"0,1 10 3271 0 0,-1 3-2911 0 0,14 173 2783 0 0,-12-160-2963 0 0,0-9-251 0 0,-1-1-1 0 0,-1 1 1 0 0,0 0 0 0 0,-2 0 0 0 0,-3 23 0 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1032.68">317 108 11863 0 0,'20'-1'4431'0'0,"-18"19"-2617"0"0,-1-17-1571 0 0,2 66-71 0 0,-5 93 0 0 0,1-151-450 0 0,1 0-1 0 0,0 0 0 0 0,0 0 1 0 0,3 14-1 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1359.96">348 76 11863 0 0,'-1'-6'4298'0'0,"9"-1"-3149"0"0,-2 4-926 0 0,1-1 0 0 0,0 1 1 0 0,-1 1-1 0 0,1 0 0 0 0,0 0 0 0 0,11-2 1 0 0,8-2 137 0 0,73-16-320 0 0,-55 15-4119 0 0,-39 7 2054 0 0,1 1-22 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1701.43">366 254 16127 0 0,'2'-1'314'0'0,"0"0"1"0"0,0 1-1 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,2 0 0 0 0,2-2 53 0 0,78-16 159 0 0,44-3-1008 0 0,-125 21 349 0 0,7-1-1156 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2059.68">377 466 15775 0 0,'-1'-1'37'0'0,"1"1"-1"0"0,0 0 1 0 0,0-1 0 0 0,0 1-1 0 0,-1-1 1 0 0,1 1-1 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,0 1 0 0 0,0-1-1 0 0,0 1 1 0 0,1 0-1 0 0,-1-1 1 0 0,13-2 1997 0 0,-1 1-1323 0 0,10-2 997 0 0,-1 1-1 0 0,35 0 0 0 0,11 5-2716 0 0,-56-2 31 0 0,1-1-13 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3163.26">1052 298 14311 0 0,'0'1'73'0'0,"0"-1"0"0"0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,-1 0 1 0 0,1 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 1-1 0 0,1-1 1 0 0,-1 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 0-1 0 0,0 1 1 0 0,1-1 0 0 0,-1 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 1-1 0 0,0-1 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 1 0 0 0,0-1-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,0 1 1 0 0,1-1-1 0 0,-1 0 1 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0-1 0 0,1-1 1 0 0,23-3 2890 0 0,-20 3-2615 0 0,61-11 3501 0 0,-29 6-3453 0 0,66-21 0 0 0,-69 14-4096 0 0,-1-4-3689 0 0,-28 14 5501 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3490.7">1194 88 11631 0 0,'2'0'260'0'0,"0"1"-1"0"0,-1-1 0 0 0,1 1 1 0 0,-1-1-1 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 1 0 0,-1 0-1 0 0,0 0 0 0 0,1-1 1 0 0,-1 1-1 0 0,0 0 0 0 0,0 0 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 1 0 0 0,1-1 1 0 0,0 0-1 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 1 0 0,0-1-1 0 0,-1 1 0 0 0,0-1 1 0 0,1 3-1 0 0,1 5 253 0 0,0-1 1 0 0,-1 1-1 0 0,1 16 1 0 0,-4 39 1006 0 0,1-42-1401 0 0,1 0 0 0 0,0-1-1 0 0,6 31 1 0 0,-4-21-2779 0 0,-5-11-2895 0 0,0-15 3605 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4666.52">1960 66 10247 0 0,'0'0'1026'0'0,"-5"0"-572"0"0,0 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,0 1 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,1 1-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,-1 0 1 0 0,1 1-1 0 0,0-1 1 0 0,-4 4-1 0 0,4-2-358 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,-1 6 0 0 0,-3 23 51 0 0,1 1 0 0 0,-1 38-1 0 0,6-69-122 0 0,1 0 1 0 0,-1-1-1 0 0,1 1 0 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,1 0 0 0 0,-1-1 0 0 0,1 0 1 0 0,0 1-1 0 0,0-1 0 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 0 0 0,0-1 1 0 0,1 0-1 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,1 0 0 0 0,0-1 1 0 0,0 1-1 0 0,-1-1 0 0 0,1 0 0 0 0,0 0 1 0 0,0-1-1 0 0,-1 0 0 0 0,1 1 0 0 0,0-2 1 0 0,6-1-1 0 0,-5 1-46 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,7-7 0 0 0,-10 8 12 0 0,-1 0 1 0 0,0-1-1 0 0,1 1 0 0 0,-1 0 0 0 0,0-1 1 0 0,-1 1-1 0 0,1-1 0 0 0,0 1 1 0 0,-1-1-1 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,1-5 0 0 0,3-17 24 0 0,-1 10 12 0 0,-2 0 0 0 0,0 0 0 0 0,0-23 0 0 0,-2 7 47 0 0,1 19 57 0 0,-1 0 0 0 0,0 0 0 0 0,-1 1 0 0 0,-1-1 0 0 0,-5-21 0 0 0,6 31-91 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 1 0 0,-1 0-1 0 0,1 1 0 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,-4-1 0 0 0,-4-1-332 0 0,0 0 0 0 0,-20 0 0 0 0,25 2-33 0 0,-5 0-1030 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5243.38">2454 1 12671 0 0,'-20'4'3576'0'0,"18"-4"-3497"0"0,1 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,-1 1-1 0 0,0-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,1 1-1 0 0,-1 0 1 0 0,1 0-1 0 0,0-1 0 0 0,-1 1 1 0 0,1 0-1 0 0,0 0 1 0 0,0 1-1 0 0,0-1 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,1 1 0 0 0,-2 1 1 0 0,-17 30 1208 0 0,9-19-853 0 0,2 1 0 0 0,0 0 0 0 0,1 1 0 0 0,-10 29 0 0 0,10-18-250 0 0,0-1 81 0 0,1 0-1 0 0,-3 35 0 0 0,9-57-247 0 0,0 1 0 0 0,0-1-1 0 0,1 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,0 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,3 6 1 0 0,-1-4-4 0 0,0 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,6 5 0 0 0,-9-8-80 0 0,0-1 1 0 0,0 0-1 0 0,-1 1 0 0 0,1-1 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,0-1 0 0 0,0 0 1 0 0,1 1-1 0 0,-1-1 1 0 0,0-1-1 0 0,1 1 0 0 0,-1 0 1 0 0,0 0-1 0 0,0-1 1 0 0,1 1-1 0 0,-1-1 0 0 0,2-1 1 0 0,-1 1 26 0 0,-1 0 1 0 0,1-1-1 0 0,-1 0 1 0 0,0 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0-1 1 0 0,-1 1 0 0 0,1 0-1 0 0,-1-1 1 0 0,0 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,-1 1 1 0 0,2-5-1 0 0,-2 5 62 0 0,1 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0-1-1 0 0,-1 1 1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,-2 0 0 0 0,-5-1 99 0 0,1 1 0 0 0,-1 0 1 0 0,1 1-1 0 0,-1 0 1 0 0,1 0-1 0 0,-10 3 1 0 0,-15 1-2531 0 0,22-3 1205 0 0,2 1-11 0 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink5.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+          <inkml:channel name="OA" type="integer" max="360" units="deg"/>
+          <inkml:channel name="OE" type="integer" max="90" units="deg"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+          <inkml:channelProperty channel="OA" name="resolution" value="1000" units="1/deg"/>
+          <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2025-02-11T19:43:23.756"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.1" units="cm"/>
+      <inkml:brushProperty name="height" value="0.1" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">47 21 9791 0 0,'-8'4'4408'0'0,"8"-3"-4286"0"0,10 3 1713 0 0,19 0-749 0 0,9-1-154 0 0,-3-1-195 0 0,58-3-1 0 0,-82 0-516 0 0,0 0-1 0 0,0-1 0 0 0,0-1 1 0 0,-1 0-1 0 0,1 0 1 0 0,16-9-1 0 0,-1 3-107 0 0,-8 6-3940 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="344.66">3 211 13591 0 0,'-2'-8'550'0'0,"5"9"714"0"0,11 1 14 0 0,183-8 3555 0 0,-127 2-2215 0 0,-64 4-2208 0 0,-4 0-137 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,5-3 0 0 0,-6 2-898 0 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink6.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+          <inkml:channel name="OA" type="integer" max="360" units="deg"/>
+          <inkml:channel name="OE" type="integer" max="90" units="deg"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+          <inkml:channelProperty channel="OA" name="resolution" value="1000" units="1/deg"/>
+          <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2025-02-11T19:44:48.354"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.1" units="cm"/>
+      <inkml:brushProperty name="height" value="0.1" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">13 12 8063 0 0,'-5'-11'10848'0'0,"5"11"-10786"0"0,1 0-1 0 0,-1 1 1 0 0,0-1 0 0 0,1 1-1 0 0,-1-1 1 0 0,0 1-1 0 0,1-1 1 0 0,-1 1 0 0 0,0-1-1 0 0,1 1 1 0 0,-1-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1-1 0 0,1 0 1 0 0,-1-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 2-1 0 0,1 38 1114 0 0,-3 50-1 0 0,-1-54-1237 0 0,5 69 0 0 0,-1-99 140 0 0,1 12 91 0 0,-1-17-134 0 0,-1 0 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,-1 0 0 0 0,1-1 1 0 0,0 1-1 0 0,0 0 1 0 0,-1-1-1 0 0,1 1 1 0 0,0 0-1 0 0,-1-1 1 0 0,0 2-1 0 0,1-2-87 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 1 0 0,-1-1-1 0 0,1 1 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 0 0 0,0-2 0 0 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink7.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+          <inkml:channel name="OA" type="integer" max="360" units="deg"/>
+          <inkml:channel name="OE" type="integer" max="90" units="deg"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+          <inkml:channelProperty channel="OA" name="resolution" value="1000" units="1/deg"/>
+          <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2025-02-11T19:44:53.438"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.1" units="cm"/>
+      <inkml:brushProperty name="height" value="0.1" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1770 101 12551 0 0,'-1'-3'165'0'0,"0"-1"259"0"0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 1-1 0 0,-1-1 1 0 0,0 1 0 0 0,0 0 0 0 0,-5-6 0 0 0,7 9-396 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 1 0 0 0,1-1 1 0 0,-1 0-1 0 0,0 1 0 0 0,0-1 1 0 0,1 0-1 0 0,-1 1 0 0 0,0-1 1 0 0,1 1-1 0 0,-1-1 0 0 0,0 1 1 0 0,1 0-1 0 0,-1-1 0 0 0,1 1 1 0 0,-1 1-1 0 0,-18 21 210 0 0,15-18-126 0 0,-20 25 636 0 0,-1-2 1 0 0,-32 28 0 0 0,52-52-676 0 0,1 0-1 0 0,0 0 1 0 0,1 1-1 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,-1 8-1 0 0,4-10-76 0 0,-1-1-1 0 0,1 1 1 0 0,-1 0 0 0 0,1-1-1 0 0,0 1 1 0 0,0 0-1 0 0,1-1 1 0 0,-1 1 0 0 0,0 0-1 0 0,1-1 1 0 0,0 1 0 0 0,-1-1-1 0 0,1 1 1 0 0,0-1 0 0 0,0 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,0-1 1 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,3 2 1 0 0,1 0-149 0 0,1-1 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,0-1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0-1 0 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 1 0 0,-1 0-1 0 0,0-1 0 0 0,0 0 0 0 0,7-5 0 0 0,-7 2 418 0 0,-1 0 0 0 0,0-1 0 0 0,0 1-1 0 0,-1-1 1 0 0,0 0 0 0 0,-1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0-1 0 0 0,-1 1 0 0 0,1-13-1 0 0,-3 17-45 0 0,0 0 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,-3-5 0 0 0,3 6-246 0 0,1-1 1 0 0,-1 1-1 0 0,0-1 1 0 0,1 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 1 0 0,0 0-1 0 0,0-7 1 0 0,2 10-100 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,5-4-1057 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="495.13">2123 73 13359 0 0,'0'0'85'0'0,"0"-1"-1"0"0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 1 0 0,-1 1-1 0 0,1-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 1 0 0,-1-1-1 0 0,1 1 0 0 0,0-1 0 0 0,-1 1 1 0 0,0-1-1 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1 0 1 0 0,0-1-1 0 0,0 1 0 0 0,-1 0 48 0 0,1-1-1 0 0,0 1 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1-1-1 0 0,1 1 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 1-1 0 0,-1-1 1 0 0,-1 0-1 0 0,-7 6 157 0 0,0 1-1 0 0,1-1 1 0 0,0 1-1 0 0,0 1 1 0 0,0 0 0 0 0,-9 12-1 0 0,-20 17 344 0 0,15-20-252 0 0,12-9-159 0 0,0 0-1 0 0,1 1 1 0 0,0 0 0 0 0,-16 20 0 0 0,24-27-207 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,1 1 0 0 0,1 1 0 0 0,1 1-141 0 0,0-1 1 0 0,0 0-1 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 1 0 0,1 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,0-1 0 0 0,1 0 1 0 0,-1-1-1 0 0,1 0 0 0 0,-1 1 0 0 0,6-1 1 0 0,-1 0-193 0 0,-1 0 0 0 0,0-1 0 0 0,0 0-1 0 0,0-1 1 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 0 0 0 0,11-5 0 0 0,-14 4 458 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,6-10-1 0 0,-4 6 645 0 0,-1-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,0 0-1 0 0,-2 0 1 0 0,3-13 0 0 0,-5 19-587 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-1 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 1-1 0 0,-3-8 1 0 0,1 6-178 0 0,2 0 0 0 0,-1 0 0 0 0,-1-13 0 0 0,3 19-108 0 0,0-1 0 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,1 0 0 0 0,-1 1-1 0 0,0-1 1 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,1-1-1 0 0,-1 1 1 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1-1-1 0 0,-1 1 1 0 0,1 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,9 3-1220 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="839.72">2528 13 15431 0 0,'-1'-1'102'0'0,"0"0"-1"0"0,0 1 0 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 0 0 0,0 0 1 0 0,-2 1-1 0 0,-19 10 954 0 0,12-5-752 0 0,2 2 1 0 0,-1-1-1 0 0,1 1 1 0 0,0 1 0 0 0,1-1-1 0 0,-8 12 1 0 0,-3 3-131 0 0,-16 14 264 0 0,-6 6 387 0 0,39-41-812 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,1 1 1 0 0,-1-1-1 0 0,1 1 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,1 0 1 0 0,-1 1-1 0 0,1-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,3 3-1 0 0,-1-1-102 0 0,0-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 0 0 0 0,1 1 0 0 0,7-1 0 0 0,-4-1-99 0 0,1 0 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1-1 1 0 0,1-1-1 0 0,-1 1 0 0 0,1-2 0 0 0,-1 1 0 0 0,0-1 0 0 0,12-8 0 0 0,-15 8 569 0 0,0 1 0 0 0,-1-2 0 0 0,1 1 0 0 0,-1 0 1 0 0,0-1-1 0 0,0 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,2-8 0 0 0,-3 6-10 0 0,-1-1-1 0 0,0 1 1 0 0,0-1-1 0 0,-1 1 1 0 0,-1 0-1 0 0,-2-13 1 0 0,-3-24-85 0 0,6 20-1241 0 0,4 8-2414 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="-1929.66">391 44 10711 0 0,'0'0'157'0'0,"-1"-1"0"0"0,1 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1-1 0 0,1 0 1 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1-1 0 0,-1-1 1 0 0,1 1 0 0 0,-1-2 0 0 0,1 2-101 0 0,0-1 0 0 0,0 1-1 0 0,-1-1 1 0 0,1 1 0 0 0,0 0-1 0 0,0-1 1 0 0,-1 1 0 0 0,1-1-1 0 0,0 1 1 0 0,-1 0 0 0 0,1-1-1 0 0,-1 1 1 0 0,1 0 0 0 0,0-1-1 0 0,-1 1 1 0 0,1 0 0 0 0,-1 0-1 0 0,1-1 1 0 0,0 1 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1-1-1 0 0,1 1 1 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 1 0 0 0,-1-1-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 1 0 0 0,-3 1 101 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,1 1 1 0 0,0 0-1 0 0,0 0 1 0 0,-3 4-1 0 0,-3 7 227 0 0,-11 25 0 0 0,0 1-110 0 0,13-28-142 0 0,0 0-1 0 0,0 0 1 0 0,-5 20 0 0 0,10-28-74 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,4 10 0 0 0,-4-11-59 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,7-4 0 0 0,-4 3-18 0 0,0-2 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0-1 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,6-12 0 0 0,-5 7 327 0 0,-1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1-20 0 0 0,-4 28-191 0 0,0 1-1 0 0,-1-1 1 0 0,1 0-1 0 0,0 1 1 0 0,-1 0 0 0 0,1-1-1 0 0,-1 1 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0-1 0 0,-1 0 1 0 0,-2-3-1 0 0,-2-2-42 0 0,0 1-1 0 0,-1 0 0 0 0,-7-6 0 0 0,-9-7-4019 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="-1265.9">760 68 11167 0 0,'-10'-22'2680'0'0,"9"21"-2647"0"0,0 1-1 0 0,0-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0-1 0 0,1-1 1 0 0,-1 1-1 0 0,0 0 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,-8-1 877 0 0,9 1-805 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 1-1 0 0,0-1 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,1 1 1 0 0,-1-1-1 0 0,0 1 1 0 0,0-1-1 0 0,1 1 1 0 0,-1 0-1 0 0,0-1 1 0 0,1 1-1 0 0,-1 0 1 0 0,1-1-1 0 0,-1 1 1 0 0,0 1-1 0 0,-14 23 626 0 0,13-21-490 0 0,-20 45 496 0 0,15-32-537 0 0,0-1 1 0 0,-12 19 0 0 0,15-30-113 0 0,1 0 0 0 0,0 0 0 0 0,1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1 8 0 0 0,1-11-87 0 0,1 1 1 0 0,0 0 0 0 0,1-1 0 0 0,-1 1-1 0 0,1 0 1 0 0,-1-1 0 0 0,1 1 0 0 0,0-1-1 0 0,0 1 1 0 0,1-1 0 0 0,-1 1 0 0 0,1-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,2 3 1 0 0,0-1-1 0 0,-1-1-1 0 0,1 0 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1-1 0 0,1 0 1 0 0,8 5-1 0 0,-11-7-7 0 0,1 0 0 0 0,0 0-1 0 0,-1-1 1 0 0,1 1 0 0 0,0-1-1 0 0,0 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,-1 0 0 0 0,1-1-1 0 0,0 0 1 0 0,-1 1 0 0 0,1-1-1 0 0,0 0 1 0 0,4-3 0 0 0,2-1-4 0 0,0 0 0 0 0,0-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-2-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,-1 0 0 0 0,3-13 0 0 0,-5 21 79 0 0,0-1 1 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 1 1 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,-2-2 0 0 0,-10-5-188 0 0,-9-5 247 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="-742.93">1106 49 13359 0 0,'0'-2'140'0'0,"0"0"-1"0"0,-1 0 1 0 0,0 0 0 0 0,1 1-1 0 0,-1-1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,-3-2-1 0 0,4 4-92 0 0,-1-1-1 0 0,1 1 1 0 0,-1-1 0 0 0,1 1-1 0 0,-1-1 1 0 0,1 1 0 0 0,-1 0-1 0 0,1-1 1 0 0,-1 1-1 0 0,0 0 1 0 0,1 0 0 0 0,-1-1-1 0 0,0 1 1 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,1 0-1 0 0,-1 1 1 0 0,1-1-1 0 0,-1 0 1 0 0,0 1 0 0 0,1-1-1 0 0,-1 0 1 0 0,1 1 0 0 0,-1-1-1 0 0,1 0 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,0 0 0 0 0,-5 8 409 0 0,1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,-6 16 0 0 0,-3 6 545 0 0,-12 10-152 0 0,19-32-626 0 0,1 1 0 0 0,0-1 0 0 0,-9 20 0 0 0,14-26-207 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1 0 1 0 0,-1-1-1 0 0,1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,2 0 1 0 0,-1 0-1 0 0,0 1 0 0 0,0-2 0 0 0,4 4 0 0 0,-2-3-25 0 0,-1 0 0 0 0,0 0-1 0 0,0-1 1 0 0,1 1 0 0 0,-1-1-1 0 0,1 1 1 0 0,0-1 0 0 0,-1 0-1 0 0,1 0 1 0 0,0-1 0 0 0,-1 1-1 0 0,1-1 1 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0-1-1 0 0,0 0 1 0 0,-1 1 0 0 0,1-1-1 0 0,0-1 1 0 0,-1 1 0 0 0,5-2 0 0 0,-3-1 82 0 0,1 1 1 0 0,-1-1 0 0 0,0-1-1 0 0,0 1 1 0 0,-1 0 0 0 0,1-1 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-1-1-1 0 0,1 1 1 0 0,-1-1 0 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,3-9 0 0 0,-4 8 10 0 0,1 0 1 0 0,-1-1 0 0 0,0 1-1 0 0,-1 0 1 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,-1 0-1 0 0,0-1 1 0 0,-1 1 0 0 0,1 0-1 0 0,-1 0 1 0 0,-1 0 0 0 0,-3-7-1 0 0,5 11-143 0 0,-7-16-1470 0 0,7 18 1477 0 0,1 1 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1 0 0 0,0 0 0 0 0,1-1 0 0 0,6 2-1131 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1800.81">51 363 16007 0 0,'-3'-4'352'0'0,"3"7"64"0"0,1 1 24 0 0,-1-1 16 0 0,0 1-360 0 0,0 0-96 0 0,-1 1 0 0 0,0 3 0 0 0,-2 6 424 0 0,-1 3 72 0 0,0 0 16 0 0,-3 0 0 0 0,-1-1-1184 0 0,2-2-224 0 0,-2-2-56 0 0,1-1-8 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2442.66">1390 350 20271 0 0,'4'0'448'0'0,"-2"1"88"0"0,-2 2 16 0 0,-1-1 24 0 0,1-1-464 0 0,-1 2-112 0 0,-1-1 0 0 0,-2 4 0 0 0,-4 3 536 0 0,-2 2 80 0 0,-2 2 24 0 0,-3 0 0 0 0,1-1-1256 0 0,0-1-248 0 0,-2 0-56 0 0,6 2-8 0 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink8.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+          <inkml:channel name="OA" type="integer" max="360" units="deg"/>
+          <inkml:channel name="OE" type="integer" max="90" units="deg"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+          <inkml:channelProperty channel="OA" name="resolution" value="1000" units="1/deg"/>
+          <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2025-02-11T19:45:12.301"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.1" units="cm"/>
+      <inkml:brushProperty name="height" value="0.1" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">4 82 8287 0 0,'-4'-4'3425'0'0,"4"4"-3349"0"0,5-9 2629 0 0,11-11 538 0 0,-13 18-2837 0 0,0-2-279 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,1 1-1 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 0 0 0,1 0 0 0 0,6 0 0 0 0,-9 1-122 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1-1 0 0,1 0 1 0 0,-1 1 0 0 0,1 0 0 0 0,-1-1-1 0 0,2 4 1 0 0,-2-3 1 0 0,1 0 1 0 0,-1 1-1 0 0,0-1 0 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 1 0 0,-1-1-1 0 0,1 1 0 0 0,-1 0 0 0 0,0-1 1 0 0,0 1-1 0 0,-1 3 0 0 0,-3 9-63 0 0,-2 0 0 0 0,1-1 0 0 0,-2 0-1 0 0,0 0 1 0 0,-17 25 0 0 0,15-25-4 0 0,0 1 0 0 0,1 0 0 0 0,0 0 0 0 0,-9 28 0 0 0,15-36 90 0 0,0 1-1 0 0,1-1 1 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,1-1-1 0 0,1 10 1 0 0,-1-15 205 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,3 1 0 0 0,0 0-504 0 0,-1 0-1 0 0,0-1 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,0 0-1 0 0,5-2 1 0 0,15-3-3438 0 0,-6 4 1886 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="386.22">477 31 12551 0 0,'-2'-1'1766'0'0,"6"2"133"0"0,10 7 456 0 0,-10-4-2300 0 0,-1 1 1 0 0,1-1-1 0 0,-1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0-1 1 0 0,0 1-1 0 0,-1 10 0 0 0,0-5 112 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 1 0 0,-2 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,-6 12 0 0 0,6-16-267 0 0,-2 6 443 0 0,0 0 1 0 0,-5 20-1 0 0,9-30-587 0 0,1 0-1 0 0,-1 1 1 0 0,1-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,2 2 0 0 0,0-1-1131 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="621.15">542 52 13935 0 0,'0'0'90'0'0,"-1"0"-1"0"0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0-1 1 0 0,1 1-1 0 0,-1 0 0 0 0,1 0 1 0 0,-1-1-1 0 0,1 1 0 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,-1-1 0 0 0,1 1 1 0 0,0-1-1 0 0,-1 1 0 0 0,1-1 1 0 0,0 0 28 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 1 0 0,1-1-1 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,0-1 1 0 0,1 1-1 0 0,-1 0 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,14-8 2230 0 0,-6 5-2418 0 0,79-11 1514 0 0,-47 9-2943 0 0,0-2-6430 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="915.24">547 224 17279 0 0,'21'4'4783'0'0,"19"-2"-3283"0"0,-20-3-1161 0 0,32-6 1 0 0,-32 4-870 0 0,30-1 1 0 0,-40 6-1448 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1154.09">493 412 17047 0 0,'3'2'423'0'0,"1"0"0"0"0,-1 0-1 0 0,1-1 1 0 0,0 1 0 0 0,-1-1-1 0 0,1 0 1 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0-1 0 0 0,5 0-1 0 0,6 1 323 0 0,19 4 940 0 0,46-1-1 0 0,-65-4-2139 0 0,0-1 0 0 0,0 0-1 0 0,0-2 1 0 0,0 0 0 0 0,22-7 0 0 0,-25 5-536 0 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink9.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+          <inkml:channel name="OA" type="integer" max="360" units="deg"/>
+          <inkml:channel name="OE" type="integer" max="90" units="deg"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+          <inkml:channelProperty channel="OA" name="resolution" value="1000" units="1/deg"/>
+          <inkml:channelProperty channel="OE" name="resolution" value="1000" units="1/deg"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2025-02-11T19:45:15.560"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.1" units="cm"/>
+      <inkml:brushProperty name="height" value="0.1" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 310 16351 0 0,'22'6'5823'0'0,"-7"-5"-5317"0"0,-1-2 1 0 0,1 0-1 0 0,0 0 1 0 0,24-6-1 0 0,4-1-840 0 0,6 2-486 0 0,2 0-3769 0 0,-35 4-2447 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="311.04">80 131 14743 0 0,'0'-1'69'0'0,"0"1"0"0"0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 1 0 0,0 0-1 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 1 0 0,1 0-1 0 0,0-1 0 0 0,0 1 95 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,1 0-1 0 0,1 1 131 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 1 0 0 0,-1-1 1 0 0,3 5-1 0 0,-2-2-121 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 1 0 0 0,0-1-1 0 0,0 1 1 0 0,-1-1 0 0 0,0 1-1 0 0,0 0 1 0 0,-1 0 0 0 0,0-1-1 0 0,1 1 1 0 0,-2 0 0 0 0,0 7-1 0 0,-3 5 89 0 0,0 0-1 0 0,-1-1 0 0 0,-9 21 0 0 0,4-2-912 0 0,8-11-2724 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1165.48">777 49 16007 0 0,'-1'-3'334'0'0,"-1"0"-1"0"0,1 1 0 0 0,0-1 1 0 0,-1 1-1 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,-3-4 0 0 0,4 6-235 0 0,0-1-1 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,1 0 1 0 0,-1-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,1-1 0 0 0,-1 1 1 0 0,-1 1-1 0 0,-3 2-46 0 0,1 0-1 0 0,0 0 1 0 0,0 1-1 0 0,0 0 1 0 0,0-1-1 0 0,1 1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 0-1 0 0,-3 12 1 0 0,-2 7 271 0 0,-6 29 0 0 0,14-52-319 0 0,-7 29 307 0 0,-6 61 1 0 0,13-88-325 0 0,0 0-1 0 0,0 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,1 0 1 0 0,0 0-1 0 0,0-1 1 0 0,-1 1-1 0 0,2 0 0 0 0,-1-1 1 0 0,0 0-1 0 0,0 1 0 0 0,1-1 1 0 0,-1 0-1 0 0,1 0 0 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 1 0 0,0-1-1 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,1-1 0 0 0,-1 1 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,1-1 1 0 0,-1 1-1 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,5-3-1 0 0,5-4-229 0 0,0 0-1 0 0,11-11 1 0 0,-19 15 253 0 0,0 0 1 0 0,0-1 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0-1 0 0,4-8 1 0 0,-7 8 73 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,-1 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,-3-8 0 0 0,1 4 342 0 0,-1 0-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,-9-12-1 0 0,7 13-545 0 0,-8-9-770 0 0,15 15 719 0 0,-1 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,1-1 0 0 0,-1 1-1 0 0,1-1 1 0 0,-1 0 0 0 0,1 1-1 0 0,0-1 1 0 0,0 0 0 0 0,-1 1-1 0 0,1-1 1 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0-2 0 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1754.07">1125 49 15775 0 0,'-5'-12'1505'0'0,"3"8"-922"0"0,1 0-1 0 0,-1 1 1 0 0,0-1 0 0 0,0 0 0 0 0,-1 1 0 0 0,-4-6 0 0 0,7 8-562 0 0,-1 0 1 0 0,0 1-1 0 0,0-1 0 0 0,1 1 1 0 0,-1 0-1 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,1 0-1 0 0,-1 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 1 0 0,1 1-1 0 0,-1-1 0 0 0,0 1 1 0 0,0-1-1 0 0,1 1 0 0 0,-1-1 1 0 0,0 1-1 0 0,1 0 0 0 0,-1-1 1 0 0,0 2-1 0 0,-6 5 139 0 0,0 1 0 0 0,0-1 0 0 0,1 1 0 0 0,0 1 0 0 0,1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,-5 14 0 0 0,8-18-55 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,3 5 0 0 0,-4-8-62 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,1 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,4 1 0 0 0,-4-2-53 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 1 0 0,2-2-1 0 0,1 0-155 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,3-7 0 0 0,1-8-306 0 0,0-1 0 0 0,-2 0 0 0 0,0 0-1 0 0,3-31 1 0 0,-6 47 1403 0 0,2 15 367 0 0,-2-4-1161 0 0,1 8-3 0 0,1-1-1 0 0,-2 0 1 0 0,0 1-1 0 0,0 0 0 0 0,-1 17 1 0 0,-7 70 160 0 0,0-18-109 0 0,6-36 5 0 0,2 0-1 0 0,10 61 0 0 0</inkml:trace>
+</inkml:ink>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E6D15679-D858-4527-8283-B4B42C1414B9}" name="Table2" displayName="Table2" ref="A1:B5" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E6D15679-D858-4527-8283-B4B42C1414B9}" name="Table2" displayName="Table2" ref="A1:B5" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
   <autoFilter ref="A1:B5" xr:uid="{E6D15679-D858-4527-8283-B4B42C1414B9}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{8629E529-313D-4838-9A18-8F4D9DEDBC37}" name="E (Employee Turnover)" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{45EEE4C9-DE3C-48DA-A4B9-25C529470FBA}" name="C (Cost)" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{8629E529-313D-4838-9A18-8F4D9DEDBC37}" name="E (Employee Turnover)" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{45EEE4C9-DE3C-48DA-A4B9-25C529470FBA}" name="C (Cost)" dataDxfId="18"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{7CFA2F95-808A-484E-AC8A-156AA0AD95D0}" name="Table3" displayName="Table3" ref="A3:B22" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
+  <autoFilter ref="A3:B22" xr:uid="{7CFA2F95-808A-484E-AC8A-156AA0AD95D0}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{85A2810F-F2BD-4D1F-AAD8-D080B665BB69}" name="Year" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{8A889B43-50FE-45BD-8362-8FCED90B7DAD}" name="Subscribers" dataDxfId="14" dataCellStyle="Comma"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FBF7C4E9-741F-496F-9AF6-DBB5384BCF75}" name="Table35" displayName="Table35" ref="A3:E22" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
+  <autoFilter ref="A3:E22" xr:uid="{7CFA2F95-808A-484E-AC8A-156AA0AD95D0}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{EE0863F1-0667-4497-A78F-92FB972CFEE8}" name="Year" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{543E7141-D11A-4833-A371-DA4A41F4DA75}" name="Subscribers (millions)" dataDxfId="10" dataCellStyle="Comma"/>
+    <tableColumn id="4" xr3:uid="{E8CDE139-DB2D-4495-82A0-915A1E981714}" name="Estimated Subscribers" dataDxfId="9" dataCellStyle="Comma">
+      <calculatedColumnFormula>Table35[[#This Row],[Year]]*1.116-2224</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{034FA064-EA3A-4068-AFB5-6E920ADE75DC}" name=" Error Perentage (EP)" dataDxfId="8">
+      <calculatedColumnFormula>(Table35[[#This Row],[Subscribers (millions)]]-Table35[[#This Row],[Estimated Subscribers]])/Table35[[#This Row],[Subscribers (millions)]]</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{BCF6A397-D0DF-4C5C-B372-BC31BED89A8D}" name="Absolute EP (AEP)" dataDxfId="7">
+      <calculatedColumnFormula>ABS(Table35[[#This Row],[ Error Perentage (EP)]])</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{DFA4B38D-74A5-4DE7-9E71-875097A4E376}" name="Table357" displayName="Table357" ref="A3:E22" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+  <autoFilter ref="A3:E22" xr:uid="{7CFA2F95-808A-484E-AC8A-156AA0AD95D0}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{249CB777-9A5F-4021-84E0-B3256ADAD6D3}" name="Year (Since 1994)" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{0D9AE47D-B0C0-474F-AD29-87EE0219A136}" name="Subscribers (millions)" dataDxfId="3" dataCellStyle="Comma"/>
+    <tableColumn id="4" xr3:uid="{2E42A1D7-31F0-4CBD-B8AD-92DD42230E78}" name="Estimated Subscribers" dataDxfId="0" dataCellStyle="Comma">
+      <calculatedColumnFormula>Table357[[#This Row],[Year (Since 1994)]]*1.116+1.2194</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{D04571DA-69F3-4913-9111-6E9D34198F63}" name=" Error Perentage (EP)" dataDxfId="2">
+      <calculatedColumnFormula>(Table357[[#This Row],[Subscribers (millions)]]-Table357[[#This Row],[Estimated Subscribers]])/Table357[[#This Row],[Subscribers (millions)]]</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{1C9CDF07-ABBF-4FF1-91F5-E5466F814DB0}" name="Absolute EP (AEP)" dataDxfId="1">
+      <calculatedColumnFormula>ABS(Table357[[#This Row],[ Error Perentage (EP)]])</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2468,14 +7817,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5A9607E-9A5C-4B27-AFA2-8620C6540D98}">
   <dimension ref="A1:G42"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="25.109375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="19.77734375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="11.21875" customWidth="1"/>
+    <col min="1" max="1" width="25.1328125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="19.796875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="11.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2483,7 +7832,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A2" s="2">
         <v>10</v>
       </c>
@@ -2491,7 +7840,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A3" s="2">
         <v>20</v>
       </c>
@@ -2499,7 +7848,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A4" s="2">
         <v>30</v>
       </c>
@@ -2507,7 +7856,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A5" s="2">
         <v>40</v>
       </c>
@@ -2515,7 +7864,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="E23" t="s">
         <v>3</v>
       </c>
@@ -2523,7 +7872,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="E24" t="s">
         <v>4</v>
       </c>
@@ -2531,7 +7880,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="E26" t="s">
         <v>0</v>
       </c>
@@ -2539,7 +7888,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="E27" t="s">
         <v>2</v>
       </c>
@@ -2548,7 +7897,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31" s="2">
         <v>2012</v>
       </c>
@@ -2560,7 +7909,7 @@
         <v>27.87</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A32" s="2">
         <v>2013</v>
       </c>
@@ -2572,7 +7921,7 @@
         <v>29.004000000000001</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A33" s="2">
         <v>2014</v>
       </c>
@@ -2584,7 +7933,7 @@
         <v>30.138000000000002</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A34" s="2">
         <v>2015</v>
       </c>
@@ -2596,7 +7945,7 @@
         <v>31.271999999999998</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A35" s="2">
         <v>2016</v>
       </c>
@@ -2608,7 +7957,7 @@
         <v>32.405999999999999</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A38" s="2">
         <v>2012</v>
       </c>
@@ -2616,7 +7965,7 @@
         <v>27.87</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A39" s="2">
         <v>2013</v>
       </c>
@@ -2624,7 +7973,7 @@
         <v>29.004000000000001</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A40" s="2">
         <v>2014</v>
       </c>
@@ -2632,7 +7981,7 @@
         <v>30.138000000000002</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A41" s="2">
         <v>2015</v>
       </c>
@@ -2640,7 +7989,7 @@
         <v>31.271999999999998</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A42" s="2">
         <v>2016</v>
       </c>
@@ -2656,4 +8005,1151 @@
     <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F65FCA1E-5734-4D0D-AF28-2EC54BB91DFC}">
+  <dimension ref="A1:P35"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="15.9296875" customWidth="1"/>
+    <col min="2" max="2" width="18.53125" style="5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A4" s="2">
+        <v>1994</v>
+      </c>
+      <c r="B4" s="7">
+        <v>320000</v>
+      </c>
+      <c r="P4" s="8"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A5" s="2">
+        <v>1995</v>
+      </c>
+      <c r="B5" s="7">
+        <v>1200000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A6" s="2">
+        <v>1996</v>
+      </c>
+      <c r="B6" s="7">
+        <v>2300000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A7" s="2">
+        <v>1997</v>
+      </c>
+      <c r="B7" s="7">
+        <v>3301000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A8" s="2">
+        <v>1998</v>
+      </c>
+      <c r="B8" s="7">
+        <v>4458000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A9" s="2">
+        <v>1999</v>
+      </c>
+      <c r="B9" s="7">
+        <v>6679000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A10" s="2">
+        <v>2000</v>
+      </c>
+      <c r="B10" s="7">
+        <v>9554000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A11" s="2">
+        <v>2001</v>
+      </c>
+      <c r="B11" s="7">
+        <v>10218000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A12" s="2">
+        <v>2002</v>
+      </c>
+      <c r="B12" s="7">
+        <v>11181000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A13" s="2">
+        <v>2003</v>
+      </c>
+      <c r="B13" s="7">
+        <v>12290000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A14" s="2">
+        <v>2004</v>
+      </c>
+      <c r="B14" s="7">
+        <v>13000000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A15" s="2">
+        <v>2005</v>
+      </c>
+      <c r="B15" s="7">
+        <v>15000000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A16" s="2">
+        <v>2006</v>
+      </c>
+      <c r="B16" s="7">
+        <v>15950000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A17" s="2">
+        <v>2007</v>
+      </c>
+      <c r="B17" s="7">
+        <v>16830000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A18" s="2">
+        <v>2008</v>
+      </c>
+      <c r="B18" s="7">
+        <v>17620000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A19" s="2">
+        <v>2009</v>
+      </c>
+      <c r="B19" s="7">
+        <v>18081000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A20" s="2">
+        <v>2010</v>
+      </c>
+      <c r="B20" s="7">
+        <v>19200000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A21" s="2">
+        <v>2012</v>
+      </c>
+      <c r="B21" s="7">
+        <v>19900000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A22" s="2">
+        <v>2014</v>
+      </c>
+      <c r="B22" s="7">
+        <v>20265000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A30" t="s">
+        <v>8</v>
+      </c>
+      <c r="B30" s="5">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A31" t="s">
+        <v>4</v>
+      </c>
+      <c r="B31" s="9">
+        <v>-2000000000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A34" t="s">
+        <v>9</v>
+      </c>
+      <c r="B34" s="9">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A35" t="s">
+        <v>10</v>
+      </c>
+      <c r="B35" s="5">
+        <f xml:space="preserve"> B30*B34+B31</f>
+        <v>15000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DDFEA2A-9460-4A6A-8E23-2BD955ED7A3F}">
+  <dimension ref="A1:Q36"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="15.9296875" customWidth="1"/>
+    <col min="2" max="3" width="23.46484375" style="9" customWidth="1"/>
+    <col min="4" max="4" width="34.06640625" customWidth="1"/>
+    <col min="5" max="5" width="20.796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A4" s="2">
+        <v>1994</v>
+      </c>
+      <c r="B4" s="10">
+        <v>0.32</v>
+      </c>
+      <c r="C4" s="10">
+        <f>Table35[[#This Row],[Year]]*1.116-2224</f>
+        <v>1.3040000000000873</v>
+      </c>
+      <c r="D4" s="2">
+        <f>(Table35[[#This Row],[Subscribers (millions)]]-Table35[[#This Row],[Estimated Subscribers]])/Table35[[#This Row],[Subscribers (millions)]]</f>
+        <v>-3.0750000000002724</v>
+      </c>
+      <c r="E4" s="2">
+        <f>ABS(Table35[[#This Row],[ Error Perentage (EP)]])</f>
+        <v>3.0750000000002724</v>
+      </c>
+      <c r="Q4" s="8"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A5" s="2">
+        <v>1995</v>
+      </c>
+      <c r="B5" s="10">
+        <v>1.2</v>
+      </c>
+      <c r="C5" s="10">
+        <f>Table35[[#This Row],[Year]]*1.116-2224</f>
+        <v>2.4200000000000728</v>
+      </c>
+      <c r="D5" s="2">
+        <f>(Table35[[#This Row],[Subscribers (millions)]]-Table35[[#This Row],[Estimated Subscribers]])/Table35[[#This Row],[Subscribers (millions)]]</f>
+        <v>-1.0166666666667274</v>
+      </c>
+      <c r="E5" s="2">
+        <f>ABS(Table35[[#This Row],[ Error Perentage (EP)]])</f>
+        <v>1.0166666666667274</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A6" s="2">
+        <v>1996</v>
+      </c>
+      <c r="B6" s="10">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="C6" s="10">
+        <f>Table35[[#This Row],[Year]]*1.116-2224</f>
+        <v>3.5360000000000582</v>
+      </c>
+      <c r="D6" s="2">
+        <f>(Table35[[#This Row],[Subscribers (millions)]]-Table35[[#This Row],[Estimated Subscribers]])/Table35[[#This Row],[Subscribers (millions)]]</f>
+        <v>-0.53739130434785154</v>
+      </c>
+      <c r="E6" s="2">
+        <f>ABS(Table35[[#This Row],[ Error Perentage (EP)]])</f>
+        <v>0.53739130434785154</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A7" s="2">
+        <v>1997</v>
+      </c>
+      <c r="B7" s="10">
+        <v>3.3010000000000002</v>
+      </c>
+      <c r="C7" s="10">
+        <f>Table35[[#This Row],[Year]]*1.116-2224</f>
+        <v>4.6520000000000437</v>
+      </c>
+      <c r="D7" s="2">
+        <f>(Table35[[#This Row],[Subscribers (millions)]]-Table35[[#This Row],[Estimated Subscribers]])/Table35[[#This Row],[Subscribers (millions)]]</f>
+        <v>-0.40926991820661723</v>
+      </c>
+      <c r="E7" s="2">
+        <f>ABS(Table35[[#This Row],[ Error Perentage (EP)]])</f>
+        <v>0.40926991820661723</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A8" s="2">
+        <v>1998</v>
+      </c>
+      <c r="B8" s="10">
+        <v>4.4580000000000002</v>
+      </c>
+      <c r="C8" s="10">
+        <f>Table35[[#This Row],[Year]]*1.116-2224</f>
+        <v>5.7680000000000291</v>
+      </c>
+      <c r="D8" s="2">
+        <f>(Table35[[#This Row],[Subscribers (millions)]]-Table35[[#This Row],[Estimated Subscribers]])/Table35[[#This Row],[Subscribers (millions)]]</f>
+        <v>-0.29385374607447934</v>
+      </c>
+      <c r="E8" s="2">
+        <f>ABS(Table35[[#This Row],[ Error Perentage (EP)]])</f>
+        <v>0.29385374607447934</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A9" s="2">
+        <v>1999</v>
+      </c>
+      <c r="B9" s="10">
+        <v>6.6790000000000003</v>
+      </c>
+      <c r="C9" s="10">
+        <f>Table35[[#This Row],[Year]]*1.116-2224</f>
+        <v>6.8840000000000146</v>
+      </c>
+      <c r="D9" s="2">
+        <f>(Table35[[#This Row],[Subscribers (millions)]]-Table35[[#This Row],[Estimated Subscribers]])/Table35[[#This Row],[Subscribers (millions)]]</f>
+        <v>-3.0693217547539193E-2</v>
+      </c>
+      <c r="E9" s="2">
+        <f>ABS(Table35[[#This Row],[ Error Perentage (EP)]])</f>
+        <v>3.0693217547539193E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A10" s="2">
+        <v>2000</v>
+      </c>
+      <c r="B10" s="10">
+        <v>9.5540000000000003</v>
+      </c>
+      <c r="C10" s="10">
+        <f>Table35[[#This Row],[Year]]*1.116-2224</f>
+        <v>8</v>
+      </c>
+      <c r="D10" s="2">
+        <f>(Table35[[#This Row],[Subscribers (millions)]]-Table35[[#This Row],[Estimated Subscribers]])/Table35[[#This Row],[Subscribers (millions)]]</f>
+        <v>0.16265438559765547</v>
+      </c>
+      <c r="E10" s="2">
+        <f>ABS(Table35[[#This Row],[ Error Perentage (EP)]])</f>
+        <v>0.16265438559765547</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A11" s="2">
+        <v>2001</v>
+      </c>
+      <c r="B11" s="10">
+        <v>10.218</v>
+      </c>
+      <c r="C11" s="10">
+        <f>Table35[[#This Row],[Year]]*1.116-2224</f>
+        <v>9.1159999999999854</v>
+      </c>
+      <c r="D11" s="2">
+        <f>(Table35[[#This Row],[Subscribers (millions)]]-Table35[[#This Row],[Estimated Subscribers]])/Table35[[#This Row],[Subscribers (millions)]]</f>
+        <v>0.10784889410843751</v>
+      </c>
+      <c r="E11" s="2">
+        <f>ABS(Table35[[#This Row],[ Error Perentage (EP)]])</f>
+        <v>0.10784889410843751</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A12" s="2">
+        <v>2002</v>
+      </c>
+      <c r="B12" s="10">
+        <v>11.180999999999999</v>
+      </c>
+      <c r="C12" s="10">
+        <f>Table35[[#This Row],[Year]]*1.116-2224</f>
+        <v>10.232000000000426</v>
+      </c>
+      <c r="D12" s="2">
+        <f>(Table35[[#This Row],[Subscribers (millions)]]-Table35[[#This Row],[Estimated Subscribers]])/Table35[[#This Row],[Subscribers (millions)]]</f>
+        <v>8.4876129147623075E-2</v>
+      </c>
+      <c r="E12" s="2">
+        <f>ABS(Table35[[#This Row],[ Error Perentage (EP)]])</f>
+        <v>8.4876129147623075E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A13" s="2">
+        <v>2003</v>
+      </c>
+      <c r="B13" s="10">
+        <v>12.29</v>
+      </c>
+      <c r="C13" s="10">
+        <f>Table35[[#This Row],[Year]]*1.116-2224</f>
+        <v>11.348000000000411</v>
+      </c>
+      <c r="D13" s="2">
+        <f>(Table35[[#This Row],[Subscribers (millions)]]-Table35[[#This Row],[Estimated Subscribers]])/Table35[[#This Row],[Subscribers (millions)]]</f>
+        <v>7.6647681041463633E-2</v>
+      </c>
+      <c r="E13" s="2">
+        <f>ABS(Table35[[#This Row],[ Error Perentage (EP)]])</f>
+        <v>7.6647681041463633E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A14" s="2">
+        <v>2004</v>
+      </c>
+      <c r="B14" s="10">
+        <v>13</v>
+      </c>
+      <c r="C14" s="10">
+        <f>Table35[[#This Row],[Year]]*1.116-2224</f>
+        <v>12.464000000000397</v>
+      </c>
+      <c r="D14" s="2">
+        <f>(Table35[[#This Row],[Subscribers (millions)]]-Table35[[#This Row],[Estimated Subscribers]])/Table35[[#This Row],[Subscribers (millions)]]</f>
+        <v>4.1230769230738727E-2</v>
+      </c>
+      <c r="E14" s="2">
+        <f>ABS(Table35[[#This Row],[ Error Perentage (EP)]])</f>
+        <v>4.1230769230738727E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A15" s="2">
+        <v>2005</v>
+      </c>
+      <c r="B15" s="10">
+        <v>15</v>
+      </c>
+      <c r="C15" s="10">
+        <f>Table35[[#This Row],[Year]]*1.116-2224</f>
+        <v>13.580000000000382</v>
+      </c>
+      <c r="D15" s="2">
+        <f>(Table35[[#This Row],[Subscribers (millions)]]-Table35[[#This Row],[Estimated Subscribers]])/Table35[[#This Row],[Subscribers (millions)]]</f>
+        <v>9.4666666666641197E-2</v>
+      </c>
+      <c r="E15" s="2">
+        <f>ABS(Table35[[#This Row],[ Error Perentage (EP)]])</f>
+        <v>9.4666666666641197E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A16" s="2">
+        <v>2006</v>
+      </c>
+      <c r="B16" s="10">
+        <v>15.95</v>
+      </c>
+      <c r="C16" s="10">
+        <f>Table35[[#This Row],[Year]]*1.116-2224</f>
+        <v>14.696000000000367</v>
+      </c>
+      <c r="D16" s="2">
+        <f>(Table35[[#This Row],[Subscribers (millions)]]-Table35[[#This Row],[Estimated Subscribers]])/Table35[[#This Row],[Subscribers (millions)]]</f>
+        <v>7.8620689655149331E-2</v>
+      </c>
+      <c r="E16" s="2">
+        <f>ABS(Table35[[#This Row],[ Error Perentage (EP)]])</f>
+        <v>7.8620689655149331E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A17" s="2">
+        <v>2007</v>
+      </c>
+      <c r="B17" s="10">
+        <v>16.829999999999998</v>
+      </c>
+      <c r="C17" s="10">
+        <f>Table35[[#This Row],[Year]]*1.116-2224</f>
+        <v>15.812000000000353</v>
+      </c>
+      <c r="D17" s="2">
+        <f>(Table35[[#This Row],[Subscribers (millions)]]-Table35[[#This Row],[Estimated Subscribers]])/Table35[[#This Row],[Subscribers (millions)]]</f>
+        <v>6.0487225193086483E-2</v>
+      </c>
+      <c r="E17" s="2">
+        <f>ABS(Table35[[#This Row],[ Error Perentage (EP)]])</f>
+        <v>6.0487225193086483E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A18" s="2">
+        <v>2008</v>
+      </c>
+      <c r="B18" s="10">
+        <v>17.62</v>
+      </c>
+      <c r="C18" s="10">
+        <f>Table35[[#This Row],[Year]]*1.116-2224</f>
+        <v>16.928000000000338</v>
+      </c>
+      <c r="D18" s="2">
+        <f>(Table35[[#This Row],[Subscribers (millions)]]-Table35[[#This Row],[Estimated Subscribers]])/Table35[[#This Row],[Subscribers (millions)]]</f>
+        <v>3.9273552780911616E-2</v>
+      </c>
+      <c r="E18" s="2">
+        <f>ABS(Table35[[#This Row],[ Error Perentage (EP)]])</f>
+        <v>3.9273552780911616E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A19" s="2">
+        <v>2009</v>
+      </c>
+      <c r="B19" s="10">
+        <v>18.081</v>
+      </c>
+      <c r="C19" s="10">
+        <f>Table35[[#This Row],[Year]]*1.116-2224</f>
+        <v>18.044000000000324</v>
+      </c>
+      <c r="D19" s="2">
+        <f>(Table35[[#This Row],[Subscribers (millions)]]-Table35[[#This Row],[Estimated Subscribers]])/Table35[[#This Row],[Subscribers (millions)]]</f>
+        <v>2.046346994064252E-3</v>
+      </c>
+      <c r="E19" s="2">
+        <f>ABS(Table35[[#This Row],[ Error Perentage (EP)]])</f>
+        <v>2.046346994064252E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A20" s="2">
+        <v>2010</v>
+      </c>
+      <c r="B20" s="10">
+        <v>19.2</v>
+      </c>
+      <c r="C20" s="10">
+        <f>Table35[[#This Row],[Year]]*1.116-2224</f>
+        <v>19.160000000000309</v>
+      </c>
+      <c r="D20" s="2">
+        <f>(Table35[[#This Row],[Subscribers (millions)]]-Table35[[#This Row],[Estimated Subscribers]])/Table35[[#This Row],[Subscribers (millions)]]</f>
+        <v>2.0833333333171908E-3</v>
+      </c>
+      <c r="E20" s="2">
+        <f>ABS(Table35[[#This Row],[ Error Perentage (EP)]])</f>
+        <v>2.0833333333171908E-3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A21" s="2">
+        <v>2012</v>
+      </c>
+      <c r="B21" s="10">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="C21" s="10">
+        <f>Table35[[#This Row],[Year]]*1.116-2224</f>
+        <v>21.39200000000028</v>
+      </c>
+      <c r="D21" s="2">
+        <f>(Table35[[#This Row],[Subscribers (millions)]]-Table35[[#This Row],[Estimated Subscribers]])/Table35[[#This Row],[Subscribers (millions)]]</f>
+        <v>-7.4974874371873446E-2</v>
+      </c>
+      <c r="E21" s="2">
+        <f>ABS(Table35[[#This Row],[ Error Perentage (EP)]])</f>
+        <v>7.4974874371873446E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A22" s="2">
+        <v>2014</v>
+      </c>
+      <c r="B22" s="10">
+        <v>20.265000000000001</v>
+      </c>
+      <c r="C22" s="10">
+        <f>Table35[[#This Row],[Year]]*1.116-2224</f>
+        <v>23.624000000000251</v>
+      </c>
+      <c r="D22" s="2">
+        <f>(Table35[[#This Row],[Subscribers (millions)]]-Table35[[#This Row],[Estimated Subscribers]])/Table35[[#This Row],[Subscribers (millions)]]</f>
+        <v>-0.16575376264496672</v>
+      </c>
+      <c r="E22" s="2">
+        <f>ABS(Table35[[#This Row],[ Error Perentage (EP)]])</f>
+        <v>0.16575376264496672</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="E25" t="s">
+        <v>15</v>
+      </c>
+      <c r="F25">
+        <f xml:space="preserve"> AVERAGE(Table35[Absolute EP (AEP)])</f>
+        <v>0.33442311387417972</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A31" t="s">
+        <v>8</v>
+      </c>
+      <c r="B31" s="9">
+        <v>1.1160000000000001</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A32" t="s">
+        <v>4</v>
+      </c>
+      <c r="B32" s="9">
+        <v>-2224</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A35" t="s">
+        <v>9</v>
+      </c>
+      <c r="B35" s="9">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A36" t="s">
+        <v>10</v>
+      </c>
+      <c r="B36" s="9">
+        <f xml:space="preserve"> B31*B35+B32</f>
+        <v>24.740000000000236</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1464571-2D35-49CE-ADA1-D3B0803893CC}">
+  <dimension ref="A1:Q36"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="17.59765625" customWidth="1"/>
+    <col min="2" max="3" width="23.46484375" style="9" customWidth="1"/>
+    <col min="4" max="4" width="34.06640625" customWidth="1"/>
+    <col min="5" max="5" width="20.796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A4" s="2">
+        <v>0</v>
+      </c>
+      <c r="B4" s="10">
+        <v>0.32</v>
+      </c>
+      <c r="C4" s="10">
+        <f>Table357[[#This Row],[Year (Since 1994)]]*1.116+1.2194</f>
+        <v>1.2194</v>
+      </c>
+      <c r="D4" s="2">
+        <f>(Table357[[#This Row],[Subscribers (millions)]]-Table357[[#This Row],[Estimated Subscribers]])/Table357[[#This Row],[Subscribers (millions)]]</f>
+        <v>-2.8106249999999999</v>
+      </c>
+      <c r="E4" s="2">
+        <f>ABS(Table357[[#This Row],[ Error Perentage (EP)]])</f>
+        <v>2.8106249999999999</v>
+      </c>
+      <c r="Q4" s="8"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A5" s="2">
+        <v>1</v>
+      </c>
+      <c r="B5" s="10">
+        <v>1.2</v>
+      </c>
+      <c r="C5" s="10">
+        <f>Table357[[#This Row],[Year (Since 1994)]]*1.116+1.2194</f>
+        <v>2.3353999999999999</v>
+      </c>
+      <c r="D5" s="2">
+        <f>(Table357[[#This Row],[Subscribers (millions)]]-Table357[[#This Row],[Estimated Subscribers]])/Table357[[#This Row],[Subscribers (millions)]]</f>
+        <v>-0.94616666666666671</v>
+      </c>
+      <c r="E5" s="2">
+        <f>ABS(Table357[[#This Row],[ Error Perentage (EP)]])</f>
+        <v>0.94616666666666671</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A6" s="2">
+        <v>2</v>
+      </c>
+      <c r="B6" s="10">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="C6" s="10">
+        <f>Table357[[#This Row],[Year (Since 1994)]]*1.116+1.2194</f>
+        <v>3.4514000000000005</v>
+      </c>
+      <c r="D6" s="2">
+        <f>(Table357[[#This Row],[Subscribers (millions)]]-Table357[[#This Row],[Estimated Subscribers]])/Table357[[#This Row],[Subscribers (millions)]]</f>
+        <v>-0.50060869565217425</v>
+      </c>
+      <c r="E6" s="2">
+        <f>ABS(Table357[[#This Row],[ Error Perentage (EP)]])</f>
+        <v>0.50060869565217425</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A7" s="2">
+        <v>3</v>
+      </c>
+      <c r="B7" s="10">
+        <v>3.3010000000000002</v>
+      </c>
+      <c r="C7" s="10">
+        <f>Table357[[#This Row],[Year (Since 1994)]]*1.116+1.2194</f>
+        <v>4.5674000000000001</v>
+      </c>
+      <c r="D7" s="2">
+        <f>(Table357[[#This Row],[Subscribers (millions)]]-Table357[[#This Row],[Estimated Subscribers]])/Table357[[#This Row],[Subscribers (millions)]]</f>
+        <v>-0.38364132081187519</v>
+      </c>
+      <c r="E7" s="2">
+        <f>ABS(Table357[[#This Row],[ Error Perentage (EP)]])</f>
+        <v>0.38364132081187519</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A8" s="2">
+        <v>4</v>
+      </c>
+      <c r="B8" s="10">
+        <v>4.4580000000000002</v>
+      </c>
+      <c r="C8" s="10">
+        <f>Table357[[#This Row],[Year (Since 1994)]]*1.116+1.2194</f>
+        <v>5.6834000000000007</v>
+      </c>
+      <c r="D8" s="2">
+        <f>(Table357[[#This Row],[Subscribers (millions)]]-Table357[[#This Row],[Estimated Subscribers]])/Table357[[#This Row],[Subscribers (millions)]]</f>
+        <v>-0.27487662628981618</v>
+      </c>
+      <c r="E8" s="2">
+        <f>ABS(Table357[[#This Row],[ Error Perentage (EP)]])</f>
+        <v>0.27487662628981618</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A9" s="2">
+        <v>5</v>
+      </c>
+      <c r="B9" s="10">
+        <v>6.6790000000000003</v>
+      </c>
+      <c r="C9" s="10">
+        <f>Table357[[#This Row],[Year (Since 1994)]]*1.116+1.2194</f>
+        <v>6.7994000000000003</v>
+      </c>
+      <c r="D9" s="2">
+        <f>(Table357[[#This Row],[Subscribers (millions)]]-Table357[[#This Row],[Estimated Subscribers]])/Table357[[#This Row],[Subscribers (millions)]]</f>
+        <v>-1.8026650696212017E-2</v>
+      </c>
+      <c r="E9" s="2">
+        <f>ABS(Table357[[#This Row],[ Error Perentage (EP)]])</f>
+        <v>1.8026650696212017E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A10" s="2">
+        <v>6</v>
+      </c>
+      <c r="B10" s="10">
+        <v>9.5540000000000003</v>
+      </c>
+      <c r="C10" s="10">
+        <f>Table357[[#This Row],[Year (Since 1994)]]*1.116+1.2194</f>
+        <v>7.9154000000000009</v>
+      </c>
+      <c r="D10" s="2">
+        <f>(Table357[[#This Row],[Subscribers (millions)]]-Table357[[#This Row],[Estimated Subscribers]])/Table357[[#This Row],[Subscribers (millions)]]</f>
+        <v>0.17150931546996015</v>
+      </c>
+      <c r="E10" s="2">
+        <f>ABS(Table357[[#This Row],[ Error Perentage (EP)]])</f>
+        <v>0.17150931546996015</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A11" s="2">
+        <v>7</v>
+      </c>
+      <c r="B11" s="10">
+        <v>10.218</v>
+      </c>
+      <c r="C11" s="10">
+        <f>Table357[[#This Row],[Year (Since 1994)]]*1.116+1.2194</f>
+        <v>9.0314000000000014</v>
+      </c>
+      <c r="D11" s="2">
+        <f>(Table357[[#This Row],[Subscribers (millions)]]-Table357[[#This Row],[Estimated Subscribers]])/Table357[[#This Row],[Subscribers (millions)]]</f>
+        <v>0.11612840086122515</v>
+      </c>
+      <c r="E11" s="2">
+        <f>ABS(Table357[[#This Row],[ Error Perentage (EP)]])</f>
+        <v>0.11612840086122515</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A12" s="2">
+        <v>8</v>
+      </c>
+      <c r="B12" s="10">
+        <v>11.180999999999999</v>
+      </c>
+      <c r="C12" s="10">
+        <f>Table357[[#This Row],[Year (Since 1994)]]*1.116+1.2194</f>
+        <v>10.147400000000001</v>
+      </c>
+      <c r="D12" s="2">
+        <f>(Table357[[#This Row],[Subscribers (millions)]]-Table357[[#This Row],[Estimated Subscribers]])/Table357[[#This Row],[Subscribers (millions)]]</f>
+        <v>9.2442536445756035E-2</v>
+      </c>
+      <c r="E12" s="2">
+        <f>ABS(Table357[[#This Row],[ Error Perentage (EP)]])</f>
+        <v>9.2442536445756035E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A13" s="2">
+        <v>9</v>
+      </c>
+      <c r="B13" s="10">
+        <v>12.29</v>
+      </c>
+      <c r="C13" s="10">
+        <f>Table357[[#This Row],[Year (Since 1994)]]*1.116+1.2194</f>
+        <v>11.263400000000001</v>
+      </c>
+      <c r="D13" s="2">
+        <f>(Table357[[#This Row],[Subscribers (millions)]]-Table357[[#This Row],[Estimated Subscribers]])/Table357[[#This Row],[Subscribers (millions)]]</f>
+        <v>8.353132628152958E-2</v>
+      </c>
+      <c r="E13" s="2">
+        <f>ABS(Table357[[#This Row],[ Error Perentage (EP)]])</f>
+        <v>8.353132628152958E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A14" s="2">
+        <v>10</v>
+      </c>
+      <c r="B14" s="10">
+        <v>13</v>
+      </c>
+      <c r="C14" s="10">
+        <f>Table357[[#This Row],[Year (Since 1994)]]*1.116+1.2194</f>
+        <v>12.3794</v>
+      </c>
+      <c r="D14" s="2">
+        <f>(Table357[[#This Row],[Subscribers (millions)]]-Table357[[#This Row],[Estimated Subscribers]])/Table357[[#This Row],[Subscribers (millions)]]</f>
+        <v>4.7738461538461507E-2</v>
+      </c>
+      <c r="E14" s="2">
+        <f>ABS(Table357[[#This Row],[ Error Perentage (EP)]])</f>
+        <v>4.7738461538461507E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A15" s="2">
+        <v>11</v>
+      </c>
+      <c r="B15" s="10">
+        <v>15</v>
+      </c>
+      <c r="C15" s="10">
+        <f>Table357[[#This Row],[Year (Since 1994)]]*1.116+1.2194</f>
+        <v>13.495400000000002</v>
+      </c>
+      <c r="D15" s="2">
+        <f>(Table357[[#This Row],[Subscribers (millions)]]-Table357[[#This Row],[Estimated Subscribers]])/Table357[[#This Row],[Subscribers (millions)]]</f>
+        <v>0.10030666666666654</v>
+      </c>
+      <c r="E15" s="2">
+        <f>ABS(Table357[[#This Row],[ Error Perentage (EP)]])</f>
+        <v>0.10030666666666654</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A16" s="2">
+        <v>12</v>
+      </c>
+      <c r="B16" s="10">
+        <v>15.95</v>
+      </c>
+      <c r="C16" s="10">
+        <f>Table357[[#This Row],[Year (Since 1994)]]*1.116+1.2194</f>
+        <v>14.611400000000001</v>
+      </c>
+      <c r="D16" s="2">
+        <f>(Table357[[#This Row],[Subscribers (millions)]]-Table357[[#This Row],[Estimated Subscribers]])/Table357[[#This Row],[Subscribers (millions)]]</f>
+        <v>8.3924764890282E-2</v>
+      </c>
+      <c r="E16" s="2">
+        <f>ABS(Table357[[#This Row],[ Error Perentage (EP)]])</f>
+        <v>8.3924764890282E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A17" s="2">
+        <v>13</v>
+      </c>
+      <c r="B17" s="10">
+        <v>16.829999999999998</v>
+      </c>
+      <c r="C17" s="10">
+        <f>Table357[[#This Row],[Year (Since 1994)]]*1.116+1.2194</f>
+        <v>15.727400000000001</v>
+      </c>
+      <c r="D17" s="2">
+        <f>(Table357[[#This Row],[Subscribers (millions)]]-Table357[[#This Row],[Estimated Subscribers]])/Table357[[#This Row],[Subscribers (millions)]]</f>
+        <v>6.5513963161021815E-2</v>
+      </c>
+      <c r="E17" s="2">
+        <f>ABS(Table357[[#This Row],[ Error Perentage (EP)]])</f>
+        <v>6.5513963161021815E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A18" s="2">
+        <v>14</v>
+      </c>
+      <c r="B18" s="10">
+        <v>17.62</v>
+      </c>
+      <c r="C18" s="10">
+        <f>Table357[[#This Row],[Year (Since 1994)]]*1.116+1.2194</f>
+        <v>16.843400000000003</v>
+      </c>
+      <c r="D18" s="2">
+        <f>(Table357[[#This Row],[Subscribers (millions)]]-Table357[[#This Row],[Estimated Subscribers]])/Table357[[#This Row],[Subscribers (millions)]]</f>
+        <v>4.4074914869466422E-2</v>
+      </c>
+      <c r="E18" s="2">
+        <f>ABS(Table357[[#This Row],[ Error Perentage (EP)]])</f>
+        <v>4.4074914869466422E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A19" s="2">
+        <v>15</v>
+      </c>
+      <c r="B19" s="10">
+        <v>18.081</v>
+      </c>
+      <c r="C19" s="10">
+        <f>Table357[[#This Row],[Year (Since 1994)]]*1.116+1.2194</f>
+        <v>17.959400000000002</v>
+      </c>
+      <c r="D19" s="2">
+        <f>(Table357[[#This Row],[Subscribers (millions)]]-Table357[[#This Row],[Estimated Subscribers]])/Table357[[#This Row],[Subscribers (millions)]]</f>
+        <v>6.7252917427131943E-3</v>
+      </c>
+      <c r="E19" s="2">
+        <f>ABS(Table357[[#This Row],[ Error Perentage (EP)]])</f>
+        <v>6.7252917427131943E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A20" s="2">
+        <v>16</v>
+      </c>
+      <c r="B20" s="10">
+        <v>19.2</v>
+      </c>
+      <c r="C20" s="10">
+        <f>Table357[[#This Row],[Year (Since 1994)]]*1.116+1.2194</f>
+        <v>19.075400000000002</v>
+      </c>
+      <c r="D20" s="2">
+        <f>(Table357[[#This Row],[Subscribers (millions)]]-Table357[[#This Row],[Estimated Subscribers]])/Table357[[#This Row],[Subscribers (millions)]]</f>
+        <v>6.4895833333331971E-3</v>
+      </c>
+      <c r="E20" s="2">
+        <f>ABS(Table357[[#This Row],[ Error Perentage (EP)]])</f>
+        <v>6.4895833333331971E-3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A21" s="2">
+        <v>18</v>
+      </c>
+      <c r="B21" s="10">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="C21" s="10">
+        <f>Table357[[#This Row],[Year (Since 1994)]]*1.116+1.2194</f>
+        <v>21.307400000000001</v>
+      </c>
+      <c r="D21" s="2">
+        <f>(Table357[[#This Row],[Subscribers (millions)]]-Table357[[#This Row],[Estimated Subscribers]])/Table357[[#This Row],[Subscribers (millions)]]</f>
+        <v>-7.0723618090452398E-2</v>
+      </c>
+      <c r="E21" s="2">
+        <f>ABS(Table357[[#This Row],[ Error Perentage (EP)]])</f>
+        <v>7.0723618090452398E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A22" s="2">
+        <v>20</v>
+      </c>
+      <c r="B22" s="10">
+        <v>20.265000000000001</v>
+      </c>
+      <c r="C22" s="10">
+        <f>Table357[[#This Row],[Year (Since 1994)]]*1.116+1.2194</f>
+        <v>23.539400000000001</v>
+      </c>
+      <c r="D22" s="2">
+        <f>(Table357[[#This Row],[Subscribers (millions)]]-Table357[[#This Row],[Estimated Subscribers]])/Table357[[#This Row],[Subscribers (millions)]]</f>
+        <v>-0.16157907722674561</v>
+      </c>
+      <c r="E22" s="2">
+        <f>ABS(Table357[[#This Row],[ Error Perentage (EP)]])</f>
+        <v>0.16157907722674561</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="E25" t="s">
+        <v>15</v>
+      </c>
+      <c r="F25">
+        <f xml:space="preserve"> AVERAGE(Table357[Absolute EP (AEP)])</f>
+        <v>0.31498067793128204</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A31" t="s">
+        <v>8</v>
+      </c>
+      <c r="B31" s="9">
+        <v>1.1160000000000001</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A32" t="s">
+        <v>4</v>
+      </c>
+      <c r="B32" s="9">
+        <v>1.2194</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A35" t="s">
+        <v>9</v>
+      </c>
+      <c r="B35" s="9">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A36" t="s">
+        <v>10</v>
+      </c>
+      <c r="B36" s="9">
+        <f xml:space="preserve"> B31*B35+B32</f>
+        <v>24.655400000000004</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/class1/excel/linear_model.xlsx
+++ b/class1/excel/linear_model.xlsx
@@ -5,18 +5,19 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sonou\Dropbox\git\math110\class1\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\snguyen4\Dropbox\git\math110\class1\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7672C4FF-F281-48D1-B145-C98FDDF2D5F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{674DC1B3-748F-4448-9C48-B6CCD2152946}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-156" yWindow="-156" windowWidth="31032" windowHeight="17592" activeTab="1" xr2:uid="{4FAC78D1-5AA2-459B-93EB-3E606E562966}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" activeTab="4" xr2:uid="{4FAC78D1-5AA2-459B-93EB-3E606E562966}"/>
   </bookViews>
   <sheets>
     <sheet name="Employee Turnover" sheetId="1" r:id="rId1"/>
     <sheet name="DirectTV" sheetId="2" r:id="rId2"/>
     <sheet name="DirectTV (2)" sheetId="3" r:id="rId3"/>
     <sheet name="DirectTV (3)" sheetId="6" r:id="rId4"/>
+    <sheet name="Assignment 5" sheetId="7" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="31">
   <si>
     <t>E (Employee Turnover)</t>
   </si>
@@ -91,6 +92,48 @@
   <si>
     <t>Year (Since 1994)</t>
   </si>
+  <si>
+    <t>Some ideas for Data</t>
+  </si>
+  <si>
+    <t>World Temperature by years</t>
+  </si>
+  <si>
+    <t>Houses Prices of California by years</t>
+  </si>
+  <si>
+    <t>Houses Prices of some regions by years</t>
+  </si>
+  <si>
+    <t>Car sales/prices by years</t>
+  </si>
+  <si>
+    <t>College Tuition by years</t>
+  </si>
+  <si>
+    <t>2. Plot the scatter plot of the two variables with the linear equation</t>
+  </si>
+  <si>
+    <t>3. Calculate the MAPE of the linear model.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. Convert a variable or both variables into different unit and redo 1-3 in a second sheet. </t>
+  </si>
+  <si>
+    <t>5. Compare the MAPE of the two models to decide the better.</t>
+  </si>
+  <si>
+    <t>6. Using the best model, to make some estimations/predictions</t>
+  </si>
+  <si>
+    <t>5. Submit the Excel file to Canvas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Find a dataset. Include the source of the data. Specify the input variable and output variable. </t>
+  </si>
+  <si>
+    <t>Assignment 5</t>
+  </si>
 </sst>
 </file>
 
@@ -98,7 +141,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -145,7 +188,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -159,14 +202,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -180,6 +222,14 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="22">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -197,14 +247,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -343,7 +385,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -6167,8 +6209,8 @@
       <xdr:row>3</xdr:row>
       <xdr:rowOff>489</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="5" name="Ink 4">
@@ -6187,7 +6229,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="5" name="Ink 4">
@@ -6232,8 +6274,8 @@
       <xdr:row>2</xdr:row>
       <xdr:rowOff>162671</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="6" name="Ink 5">
@@ -6252,7 +6294,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="6" name="Ink 5">
@@ -6297,8 +6339,8 @@
       <xdr:row>3</xdr:row>
       <xdr:rowOff>50054</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="9" name="Ink 8">
@@ -6317,7 +6359,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="9" name="Ink 8">
@@ -6362,8 +6404,8 @@
       <xdr:row>2</xdr:row>
       <xdr:rowOff>7478</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="21" name="Ink 20">
@@ -6382,7 +6424,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="21" name="Ink 20">
@@ -6427,8 +6469,8 @@
       <xdr:row>2</xdr:row>
       <xdr:rowOff>10358</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="24" name="Ink 23">
@@ -6447,7 +6489,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="24" name="Ink 23">
@@ -6492,8 +6534,8 @@
       <xdr:row>2</xdr:row>
       <xdr:rowOff>6758</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId13">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="26" name="Ink 25">
@@ -6512,7 +6554,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="26" name="Ink 25">
@@ -6557,8 +6599,8 @@
       <xdr:row>2</xdr:row>
       <xdr:rowOff>68678</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="39" name="Ink 38">
@@ -6577,7 +6619,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="39" name="Ink 38">
@@ -6622,8 +6664,8 @@
       <xdr:row>4</xdr:row>
       <xdr:rowOff>41596</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId17">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="45" name="Ink 44">
@@ -6642,7 +6684,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="45" name="Ink 44">
@@ -6687,8 +6729,8 @@
       <xdr:row>4</xdr:row>
       <xdr:rowOff>44116</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId19">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="50" name="Ink 49">
@@ -6707,7 +6749,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="50" name="Ink 49">
@@ -6752,8 +6794,8 @@
       <xdr:row>4</xdr:row>
       <xdr:rowOff>3796</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId21">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="53" name="Ink 52">
@@ -6772,7 +6814,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="53" name="Ink 52">
@@ -6817,8 +6859,8 @@
       <xdr:row>4</xdr:row>
       <xdr:rowOff>44476</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId23">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="71" name="Ink 70">
@@ -6837,7 +6879,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="71" name="Ink 70">
@@ -7139,19 +7181,19 @@
       <inkml:brushProperty name="color" value="#E71224"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 25 10591 0 0,'5'-8'1704'0'0,"1"5"-1264"0"0,0 1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 1 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 1-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 1 1 0 0,8 2-1 0 0,-12-2-281 0 0,1 0-1 0 0,-1 1 0 0 0,1 0 1 0 0,-1-1-1 0 0,1 1 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,3 5 0 0 0,-1-1-23 0 0,0 0-1 0 0,0 1 0 0 0,3 7 0 0 0,-5-9-115 0 0,0 1-1 0 0,-1-1 1 0 0,1 1-1 0 0,-1 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,0-1 1 0 0,1 1-1 0 0,-2 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 0 0 0,-1-1 1 0 0,0 1-1 0 0,-1-1 1 0 0,0 0-1 0 0,1 0 1 0 0,-7 9-1 0 0,-34 44-21 0 0,43-58 16 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,10 2 550 0 0,11-2 788 0 0,-21 0-1243 0 0,4-1 240 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 0 0 0 0,7-4 0 0 0,-6 4-288 0 0,-1-1 0 0 0,1 1-1 0 0,0 0 1 0 0,6-2 0 0 0,-8 4-613 0 0,-1-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,3 1 0 0 0,3 1-1491 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="666.29">477 276 16583 0 0,'1'0'102'0'0,"-1"0"-1"0"0,1 0 1 0 0,-1 1 0 0 0,0-1-1 0 0,1 0 1 0 0,-1 1 0 0 0,0-1-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 1 1 0 0,1-1 0 0 0,-1 1-1 0 0,0-1 1 0 0,0 0-1 0 0,1 1 1 0 0,-1-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,1 1-1 0 0,-1-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1-1 0 0,0 1 1 0 0,-2 17 1941 0 0,-1-11-1737 0 0,1 0 0 0 0,-1 0 0 0 0,-3 6 0 0 0,-7 8-2854 0 0,8-14 1557 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1317.64">849 68 11167 0 0,'-3'-19'2726'0'0,"3"15"-2300"0"0,-1 0-1 0 0,1 1 1 0 0,-1-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 1 0 0 0,-1 0-1 0 0,-2-5 1 0 0,4 8-422 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,-1-1-1 0 0,1 0 1 0 0,-6 8 213 0 0,-3 10 222 0 0,9-18-422 0 0,-7 16 463 0 0,-1 0 0 0 0,0-1 0 0 0,-1 0 0 0 0,-1 0-1 0 0,0-1 1 0 0,-1 0 0 0 0,-22 22 0 0 0,30-34-434 0 0,1 1 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,0 1 1 0 0,1-1-1 0 0,-1 1 0 0 0,1-1 1 0 0,0 1-1 0 0,1 0 1 0 0,-1-1-1 0 0,0 1 1 0 0,1 0-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,1-1 1 0 0,0 1-1 0 0,2 3 0 0 0,-2-4-58 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,1-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 1 0 0 0,1-1-1 0 0,-1 0 1 0 0,1-1 0 0 0,-1 1 0 0 0,1 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0 0 0 0,1-1-1 0 0,-1 1 1 0 0,0-1 0 0 0,0 1-1 0 0,6-1 1 0 0,-1-1-32 0 0,0 0 0 0 0,-1-1 1 0 0,1 0-1 0 0,0 0 0 0 0,-1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,8-12 0 0 0,-9 11 189 0 0,-1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,-2-9 0 0 0,2 12-149 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 1 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 1 0 0 0,-7-4 0 0 0,-11-10-3387 0 0,17 13 1557 0 0,3-1-20 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1860.78">1214 46 13703 0 0,'-1'-3'437'0'0,"-1"0"0"0"0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1-1 0 0,-3-2 1 0 0,-5-7 384 0 0,10 12-825 0 0,-1-1-1 0 0,1 0 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,1-1 0 0 0,-1 0 1 0 0,1 1-1 0 0,-1-1 1 0 0,0 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,0 0 1 0 0,1-1-1 0 0,-1 1 1 0 0,0 0-1 0 0,0-1 0 0 0,1 1 1 0 0,-1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,0 0 39 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,-1 3 0 0 0,-4 2 329 0 0,1 1 0 0 0,0 1 0 0 0,-7 11 0 0 0,-53 95 1720 0 0,64-111-2036 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 1 0 0,1 0-1 0 0,0 1 0 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 1 0 0,1 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,1 3-1 0 0,0-3-37 0 0,-1 0 0 0 0,1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,5-1-1 0 0,-4 0-9 0 0,1 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,4-5 0 0 0,-5 4 211 0 0,0 1-1 0 0,0 0 1 0 0,0-1 0 0 0,-1 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0-8 1 0 0,-2 10-146 0 0,1 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,-3-4 0 0 0,2 3-557 0 0,0 0 1 0 0,0-1 0 0 0,1 1-1 0 0,-1 0 1 0 0,0-5 0 0 0,1 2-501 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2417.79">1475 42 11399 0 0,'-1'-2'524'0'0,"0"0"-1"0"0,0 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,-2-3 1 0 0,3 5-327 0 0,0-1 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 1-1 0 0,0-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,0 0-1 0 0,0 1 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,-3 1 188 0 0,1 1-1 0 0,0-1 1 0 0,0 1-1 0 0,1 0 1 0 0,-1 1-1 0 0,0-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 1 0 0,0 0 0 0 0,-3 5-1 0 0,-6 7-481 0 0,-15 26 0 0 0,8-10 492 0 0,16-27-358 0 0,0 1 1 0 0,1-1-1 0 0,0 1 0 0 0,-1 0 1 0 0,2 0-1 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 1 0 0,1 0-1 0 0,1 0 0 0 0,-1 1 1 0 0,1-1-1 0 0,1 11 0 0 0,-1-13-33 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 1 0 0,1 0-1 0 0,-1-1 0 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,4 0 0 0 0,1 1-13 0 0,1-1-1 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0-1 1 0 0,-1 0-1 0 0,1 0 1 0 0,0-1-1 0 0,0 0 0 0 0,-1 0 1 0 0,1-1-1 0 0,-1 0 1 0 0,0-1-1 0 0,0 0 1 0 0,0 0-1 0 0,10-8 0 0 0,-15 9 81 0 0,0 1-1 0 0,0-1 0 0 0,0 0 1 0 0,-1 0-1 0 0,0-1 0 0 0,1 1 1 0 0,-1 0-1 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 0 0 0 0,-1-5 1 0 0,0 4 36 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,-1 1 0 0 0,0-1-1 0 0,0 1 1 0 0,-1 0 0 0 0,0 0 0 0 0,1-1 0 0 0,-2 1-1 0 0,-4-9 1 0 0,-5-2-1651 0 0,9 13 878 0 0,0-1 0 0 0,0 1-1 0 0,1 0 1 0 0,0-1 0 0 0,-1 0-1 0 0,1 1 1 0 0,-1-6 0 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2783.82">1756 296 15431 0 0,'2'2'1512'0'0,"0"-1"-1352"0"0,-1 0-160 0 0,-2-1 0 0 0,-2 3 1160 0 0,2 0 200 0 0,-1 3 40 0 0,-2 2 8 0 0,-2-1-696 0 0,1 2-136 0 0,-2-1-24 0 0,-2 0-8 0 0,3-1-920 0 0,-1 0-184 0 0,-1 1-40 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3455.38">2211 73 7943 0 0,'-3'-4'555'0'0,"3"3"-472"0"0,0 1 0 0 0,-1-1 0 0 0,1 1-1 0 0,0-1 1 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1-1 0 0,-1 0 1 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,-2 0 0 0 0,1-1 152 0 0,-1 1 0 0 0,1 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,-2 2 0 0 0,0 1 85 0 0,-1 1 0 0 0,1 0 1 0 0,0 0-1 0 0,-5 10 0 0 0,6-9-166 0 0,-1-1 0 0 0,0 0 0 0 0,0 1-1 0 0,-4 4 1 0 0,-29 23 1615 0 0,27-25-1347 0 0,0-1 0 0 0,1 2 0 0 0,0-1 0 0 0,0 1 0 0 0,-11 17 0 0 0,17-23-416 0 0,1-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,2 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,0 0 0 0 0,-1-1 0 0 0,4 4 0 0 0,-3-4-28 0 0,1 0-1 0 0,-1-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0-1-1 0 0,1 0 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,-1-1 1 0 0,1 1-1 0 0,0-1 1 0 0,0 1-1 0 0,-1-1 1 0 0,1 0 0 0 0,0 0-1 0 0,2-1 1 0 0,4 1-53 0 0,-1-1 1 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,8-4 0 0 0,-5 2 13 0 0,-1 0 1 0 0,0-1-1 0 0,-1-1 1 0 0,1 0-1 0 0,-1 0 1 0 0,0-1-1 0 0,16-15 1 0 0,-20 17 253 0 0,0-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,3-13-1 0 0,-6 17-94 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1-1 0 0,-1 0 1 0 0,1 1 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1-1 0 0,-2-2 1 0 0,-7-11-1840 0 0,10 9-1844 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3875.66">2542 91 13703 0 0,'-3'-11'799'0'0,"3"9"-585"0"0,0 1-1 0 0,-1-1 0 0 0,1 0 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,1 1 0 0 0,-1-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 1 0 0,-3-1-1 0 0,3 1-156 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-2 0 0 0 0,-21 19 161 0 0,19-15-166 0 0,-19 16 367 0 0,-44 33-1 0 0,64-52-348 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 5-1 0 0,1-6-118 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,1-1 1 0 0,-1 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,1-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0-1 0 0,1 1 1 0 0,-1-1 0 0 0,1 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,0 1 1 0 0,1-1 0 0 0,2 0-1 0 0,1 1-246 0 0,1-1-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1-1 1 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1-1-1 0 0,1 0 1 0 0,-1 0-1 0 0,0-1 1 0 0,9-3 0 0 0,-8 3 398 0 0,0-1 0 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 1 0 0,1 0-1 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 1 0 0,5-7-1 0 0,-7 7 453 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-9 0 0 0,-2 11-697 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0-1 0 0 0,-1 1 1 0 0,-1-6-1 0 0,1 8-995 0 0,2-1-13 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4190.02">2830 28 14167 0 0,'0'0'69'0'0,"0"-1"-1"0"0,1 1 1 0 0,-1 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,-1-1-1 0 0,1 1 1 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,-1 0 1 0 0,1-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0 0-1 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 1 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1-1-1 0 0,0 1 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-14 4 1621 0 0,-14 16-303 0 0,27-19-1366 0 0,-15 13 596 0 0,-27 29-1 0 0,36-35-452 0 0,1 0 0 0 0,0 0-1 0 0,1 1 1 0 0,0-1-1 0 0,0 1 1 0 0,-4 11-1 0 0,8-18-163 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,4 2 0 0 0,-1-1-165 0 0,1-1 0 0 0,-1 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,1-1 0 0 0,0-1 0 0 0,0 1-1 0 0,-1-1 1 0 0,1 1 0 0 0,0-1 0 0 0,0-1-1 0 0,0 1 1 0 0,5-2 0 0 0,-4 1 59 0 0,0-1 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,7-8-1 0 0,-9 9 360 0 0,-1-1-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,-1-1 0 0 0,1 1 1 0 0,-1 0-1 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,-1 1-1 0 0,0-1 0 0 0,0 0 1 0 0,-1-5-1 0 0,0 1 517 0 0,0 0 0 0 0,-6-15 0 0 0,-2 5-1535 0 0,-2 3-5994 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4475.44">2996 314 15551 0 0,'0'7'344'0'0,"-1"-4"72"0"0,1 0 8 0 0,0-1 8 0 0,-2 0-344 0 0,0 0-88 0 0,1 0 0 0 0,-3 2 0 0 0,-2 3 528 0 0,-1 1 88 0 0,-1 2 24 0 0,0-2 0 0 0,-1 0-928 0 0,3 0-176 0 0,-1-1-40 0 0,-1 4-8 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4966.65">3526 30 11519 0 0,'0'0'25'0'0,"0"-1"1"0"0,0 1-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0-1 0 0 0,-9 7 870 0 0,-2 5-82 0 0,7-6-346 0 0,2-4-441 0 0,-21 28 772 0 0,-2-2-1 0 0,-30 25 1 0 0,48-46-335 0 0,-1 1 0 0 0,1-1 1 0 0,1 1-1 0 0,-1 1 0 0 0,1-1 0 0 0,-7 12 0 0 0,12-17-417 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0-1 0 0,1 0 1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,0-1 0 0 0,1 1-1 0 0,-1 0 1 0 0,0 0 0 0 0,0-1 0 0 0,1 1-1 0 0,-1-1 1 0 0,1 0 0 0 0,-1 1 0 0 0,1-1-1 0 0,3 2 1 0 0,0 0-445 0 0,1 0 1 0 0,-1 0-1 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 0 0 0,0-2 0 0 0,0 1 1 0 0,-1-1-1 0 0,1 1 0 0 0,0-2 0 0 0,-1 1 0 0 0,0 0 0 0 0,1-1 1 0 0,-1 0-1 0 0,6-5 0 0 0,-7 5 555 0 0,0-1 1 0 0,0 0-1 0 0,0 0 1 0 0,5-6-1 0 0,-6 6 706 0 0,0 0 1 0 0,-1-1-1 0 0,1 1 0 0 0,3-11 1 0 0,-5 12-399 0 0,1-1 0 0 0,-1 0 1 0 0,0 1-1 0 0,0-1 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1-3 1 0 0,0 3-340 0 0,-1 0 1 0 0,1 1 0 0 0,0-1-1 0 0,-1 1 1 0 0,0-1 0 0 0,-3-5-1 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5340.85">3773 111 13703 0 0,'0'-6'457'0'0,"0"3"47"0"0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,0-3 1 0 0,0 6-419 0 0,1-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0-1-1 0 0,-1 1 1 0 0,1 0-1 0 0,0-1 1 0 0,0 1-1 0 0,-1 0 1 0 0,1-1-1 0 0,0 1 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0-1-1 0 0,0 1-25 0 0,0 0 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,-2 0 1 0 0,-7 5 110 0 0,0 0 1 0 0,1 1 0 0 0,-10 9 0 0 0,-9 6 32 0 0,12-11-12 0 0,4-4-69 0 0,0 2-1 0 0,1-1 1 0 0,0 1-1 0 0,0 1 1 0 0,-14 17-1 0 0,24-27-97 0 0,1 1 0 0 0,-1 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,1 1 0 0 0,0-1-27 0 0,-1 1 1 0 0,1-1-1 0 0,0 0 1 0 0,0 1-1 0 0,0-1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,2 1 1 0 0,3 0-189 0 0,-1 0 1 0 0,0 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1-1 0 0 0,1 0-1 0 0,6 0 1 0 0,-6 0-177 0 0,1-1 1 0 0,0 0-1 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 1 0 0,1 0-1 0 0,-1 0 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1-1 0 0 0,-1 0 0 0 0,8-8 0 0 0,-9 8 439 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,4-7 0 0 0,-5 7 583 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 0-1 0 0,0-9 1 0 0,-2 13-502 0 0,0 0 0 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 1 0 0,-2-2-1 0 0,-3-2-4805 0 0,11 9 2955 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5700.92">4067 41 14623 0 0,'0'0'715'0'0,"-6"8"178"0"0,-50 52 1128 0 0,-7 8-514 0 0,61-65-1455 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 1 0 0 0,1-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1-1 0 0,0 5 1 0 0,1-6-28 0 0,1 1 1 0 0,-1-1-1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 1 0 0,0 1-1 0 0,-1-1 0 0 0,1 0 0 0 0,2 1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,5-3 0 0 0,-7 3 8 0 0,1-1-1 0 0,-1 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,-1-1-1 0 0,1 1 0 0 0,-1-1 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,-1 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0-1-1 0 0,-1 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,0 0 1 0 0,0-3-1 0 0,-1 1 446 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,-3-8-1 0 0,-2-6 1016 0 0,8 9-518 0 0,0 8-2189 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 26 10591 0 0,'5'-9'1704'0'0,"0"6"-1264"0"0,1 1-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 1 0 0 0,1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 1-1 0 0,2 0 1 0 0,-2 0-1 0 0,2 0 0 0 0,-2 1 1 0 0,8 2-1 0 0,-11-2-281 0 0,1 0-1 0 0,-1 1 0 0 0,0 0 1 0 0,0-1-1 0 0,1 1 1 0 0,-1 0-1 0 0,0 1 0 0 0,0-1 1 0 0,-1 0-1 0 0,4 5 0 0 0,-1-1-23 0 0,-1 0-1 0 0,1 1 0 0 0,3 8 0 0 0,-6-10-115 0 0,1 1-1 0 0,-1-1 1 0 0,1 1-1 0 0,-1 0 0 0 0,0 1 1 0 0,-1-1-1 0 0,0-1 1 0 0,1 1-1 0 0,-2 0 1 0 0,1 0-1 0 0,-1 1 1 0 0,0-1-1 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 0 0 0,0-1 1 0 0,-1 2-1 0 0,-1-2 1 0 0,0 0-1 0 0,1 0 1 0 0,-6 9-1 0 0,-32 46-21 0 0,40-60 16 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,9 2 550 0 0,11-2 788 0 0,-20 0-1243 0 0,4-1 240 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0-1 0 0,1-1 1 0 0,0 0 0 0 0,6-4 0 0 0,-6 4-288 0 0,0-1 0 0 0,1 1-1 0 0,-1-1 1 0 0,6-1 0 0 0,-7 4-613 0 0,-1-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,2 0-1 0 0,-1 0 1 0 0,3 1 0 0 0,2 1-1491 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="666.29">440 283 16583 0 0,'1'0'102'0'0,"-1"0"-1"0"0,1 0 1 0 0,-1 1 0 0 0,0-1-1 0 0,1 0 1 0 0,-1 2 0 0 0,0-2-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 1 1 0 0,1-1 0 0 0,-1 1-1 0 0,0-1 1 0 0,0 0-1 0 0,1 1 1 0 0,-1-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,1 1-1 0 0,-1-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1-1 0 0,0 1 1 0 0,-2 17 1941 0 0,-1-11-1737 0 0,1 1 0 0 0,-1-1 0 0 0,-2 6 0 0 0,-7 9-2854 0 0,7-15 1557 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1317.64">783 70 11167 0 0,'-3'-20'2726'0'0,"3"16"-2300"0"0,0 0-1 0 0,0 1 1 0 0,-1-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 1 0 0 0,-1-1-1 0 0,-2-4 1 0 0,4 8-422 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 1 0 0 0,-1-1-1 0 0,1 0 1 0 0,-6 8 213 0 0,-2 11 222 0 0,8-19-422 0 0,-6 16 463 0 0,-2 1 0 0 0,1-2 0 0 0,-1 1 0 0 0,-2-1-1 0 0,1-1 1 0 0,-1 1 0 0 0,-21 22 0 0 0,29-35-434 0 0,0 1 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 1-1 0 0,1-1 1 0 0,0 0-1 0 0,-1 1 1 0 0,1-1-1 0 0,-1 2 0 0 0,1-2 1 0 0,0 1-1 0 0,1 0 1 0 0,-1-1-1 0 0,0 1 1 0 0,1 0-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,1-1 1 0 0,0 1-1 0 0,2 3 0 0 0,-2-4-58 0 0,0 0 0 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,1-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1 0 0 0,0-1-1 0 0,-1 0 1 0 0,1 1 0 0 0,1-1-1 0 0,-1 0 1 0 0,1-1 0 0 0,-2 1 0 0 0,2 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1-1 0 0,-2 1 1 0 0,2-1 0 0 0,0 0 0 0 0,1-1-1 0 0,-2 1 1 0 0,1-1 0 0 0,0 1-1 0 0,5-1 1 0 0,0-1-32 0 0,-1 0 0 0 0,-1-1 1 0 0,2-1-1 0 0,-1 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 1 0 0,0 0-1 0 0,1 0 0 0 0,-2 0 0 0 0,1-1 0 0 0,0-1 0 0 0,-1 0 1 0 0,1 1-1 0 0,7-12 0 0 0,-9 11 189 0 0,0 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,-2-1 0 0 0,1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 1 0 0 0,0-2 0 0 0,0 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,-2-8 0 0 0,2 12-149 0 0,-1 0 1 0 0,1 0-1 0 0,-1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1 1 1 0 0,1-1-1 0 0,-1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 1 0 0 0,-6-5 0 0 0,-11-9-3387 0 0,17 13 1557 0 0,2-1-20 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1860.78">1120 47 13703 0 0,'-1'-3'437'0'0,"-1"0"0"0"0,1 0 0 0 0,-1 1 0 0 0,2-1 0 0 0,-2 1 0 0 0,0-1-1 0 0,-3-2 1 0 0,-4-8 384 0 0,9 13-825 0 0,-1-1-1 0 0,1 0 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,1-1 0 0 0,-1 0 1 0 0,1 1-1 0 0,-1-1 1 0 0,0 1-1 0 0,1-1 1 0 0,0 1-1 0 0,-1 0 1 0 0,1-1-1 0 0,-1 1 1 0 0,0 0-1 0 0,0-1 0 0 0,1 1 1 0 0,-1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 39 0 0,-1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 1 0 0,1 0-1 0 0,0 0 0 0 0,-1 0 0 0 0,-1 3 0 0 0,-3 3 329 0 0,0 0 0 0 0,1 1 0 0 0,-7 11 0 0 0,-49 99 1720 0 0,59-115-2036 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 1 0 0,1 0-1 0 0,0 1 0 0 0,0 0 0 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,1 1 0 0 0,-1-1 1 0 0,1 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 1 1 0 0,0 2-1 0 0,1-3-37 0 0,-1 0 0 0 0,1 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-2 1 0 0 0,2-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,1-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,6-1-1 0 0,-5 0-9 0 0,2 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,1 0 0 0 0,-2 0 0 0 0,2-1 0 0 0,-2 1 0 0 0,1-1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,1 0-1 0 0,-2 0 1 0 0,2-1 0 0 0,-1 0 0 0 0,-1 0 0 0 0,5-6 0 0 0,-6 5 211 0 0,1 1-1 0 0,0 0 1 0 0,0-1 0 0 0,-1 1-1 0 0,0-1 1 0 0,0 0-1 0 0,-1-1 1 0 0,1 1 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0-9 1 0 0,-2 11-146 0 0,1 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,-2-4 0 0 0,1 2-557 0 0,0 1 1 0 0,0-1 0 0 0,1 1-1 0 0,-1 0 1 0 0,0-5 0 0 0,1 2-501 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2417.79">1361 43 11399 0 0,'-1'-2'524'0'0,"0"0"-1"0"0,0 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,-1-3 1 0 0,2 5-327 0 0,0-1 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 1-1 0 0,0-2 1 0 0,1 2-1 0 0,-1-1 1 0 0,0 0-1 0 0,0 1 1 0 0,0 0-1 0 0,1-1 1 0 0,-1 1-1 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,-2 1 188 0 0,0 1-1 0 0,0-1 1 0 0,1 2-1 0 0,0-1 1 0 0,-1 1-1 0 0,0-1 1 0 0,2 1-1 0 0,-2-1 1 0 0,1 1-1 0 0,0 0 1 0 0,1 0 0 0 0,-4 5-1 0 0,-5 8-481 0 0,-14 26 0 0 0,8-10 492 0 0,14-28-358 0 0,0 1 1 0 0,1-1-1 0 0,0 1 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 1 0 0 0,1 0 0 0 0,-1-1 1 0 0,1 0-1 0 0,1 0 0 0 0,-1 1 1 0 0,1-1-1 0 0,1 12 0 0 0,-1-14-33 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0-1 0 0 0,0 2 0 0 0,0-2 0 0 0,1 1 0 0 0,-2-1 0 0 0,2 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 1 0 0,1 0-1 0 0,-1-1 0 0 0,0 0 0 0 0,1 1 0 0 0,-2-1 0 0 0,2 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,3 0 0 0 0,2 2-13 0 0,0-2-1 0 0,0-1 0 0 0,0 1 1 0 0,1-1-1 0 0,-1-1 1 0 0,-1 0-1 0 0,2-1 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0-1-1 0 0,-1 0 1 0 0,1-1-1 0 0,-1 0 1 0 0,1 0-1 0 0,8-8 0 0 0,-13 8 81 0 0,0 2-1 0 0,0-1 0 0 0,-1 0 1 0 0,0 0-1 0 0,0-1 0 0 0,1 1 1 0 0,-1 0-1 0 0,-2-1 0 0 0,2 1 0 0 0,0-1 1 0 0,-1-1-1 0 0,0 1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 0 0 0 0,-1-5 1 0 0,0 4 36 0 0,0-2-1 0 0,0 2 1 0 0,0-1 0 0 0,-1 1 0 0 0,0-1-1 0 0,0 1 1 0 0,-1 0 0 0 0,0-1 0 0 0,1 0 0 0 0,-1 1-1 0 0,-5-9 1 0 0,-4-3-1651 0 0,8 14 878 0 0,1-1 0 0 0,-1 1-1 0 0,1 0 1 0 0,0-1 0 0 0,-1 0-1 0 0,1 1 1 0 0,0-7 0 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2783.82">1620 304 15431 0 0,'2'2'1512'0'0,"0"-1"-1352"0"0,-1 0-160 0 0,-2-1 0 0 0,-2 3 1160 0 0,2 0 200 0 0,-1 3 40 0 0,-2 3 8 0 0,-1-2-696 0 0,0 2-136 0 0,-1-1-24 0 0,-2 1-8 0 0,2-2-920 0 0,0 0-184 0 0,-2 1-40 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3455.38">2040 75 7943 0 0,'-3'-4'555'0'0,"3"3"-472"0"0,0 1 0 0 0,-1-1 0 0 0,1 1-1 0 0,0-1 1 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1-1 0 0,-1 0 1 0 0,1-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,-2 0 0 0 0,1-1 152 0 0,-1 1 0 0 0,1 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,1 0 0 0 0,-2 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,-2 2 0 0 0,1 1 85 0 0,-2 1 0 0 0,1 0 1 0 0,0 0-1 0 0,-4 11 0 0 0,5-10-166 0 0,-1-1 0 0 0,1 0 0 0 0,-1 1-1 0 0,-3 5 1 0 0,-28 23 1615 0 0,26-26-1347 0 0,0-1 0 0 0,0 2 0 0 0,1-1 0 0 0,0 2 0 0 0,-11 16 0 0 0,16-23-416 0 0,1-1 0 0 0,0 2 0 0 0,-1-1 0 0 0,2 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,0-1 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,0 0 0 0 0,-1-1 0 0 0,3 5 0 0 0,-2-5-28 0 0,1 0-1 0 0,-1-1 1 0 0,0 1-1 0 0,-1 0 1 0 0,1-1-1 0 0,1 0 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,0 0 1 0 0,1 0-1 0 0,-1-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,1 0 0 0 0,0 0-1 0 0,1-1 1 0 0,5 1-53 0 0,-2-1 1 0 0,0-1 0 0 0,2 1 0 0 0,-2-1 0 0 0,8-4 0 0 0,-5 2 13 0 0,-1 0 1 0 0,0-2-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,0-1-1 0 0,16-16 1 0 0,-20 18 253 0 0,1-1 0 0 0,-1 0 0 0 0,0-1 0 0 0,1 1-1 0 0,-2 0 1 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,3-14-1 0 0,-6 18-94 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1-1 0 0,-1 0 1 0 0,1 1 0 0 0,0 0 0 0 0,-1-2 0 0 0,0 2-1 0 0,-2-2 1 0 0,-6-11-1840 0 0,9 9-1844 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3875.66">2345 93 13703 0 0,'-3'-11'799'0'0,"3"9"-585"0"0,0 1-1 0 0,-1-1 0 0 0,1 0 1 0 0,0 1-1 0 0,0-1 1 0 0,-1 0-1 0 0,1 1 0 0 0,-1-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0-2 0 0 0,0 2 1 0 0,-1 0-1 0 0,2 0 0 0 0,-1 0 1 0 0,-3-1-1 0 0,3 1-156 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,1 1 0 0 0,0 0 0 0 0,-2 0 0 0 0,-20 20 161 0 0,19-16-166 0 0,-18 17 367 0 0,-41 33-1 0 0,59-53-348 0 0,0 1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 1-1 0 0,0-1 1 0 0,1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 5-1 0 0,1-6-118 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0 1-1 0 0,1-2 1 0 0,-1 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,1-1-1 0 0,-1 1 1 0 0,1-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0-1 0 0,1 1 1 0 0,-1-1 0 0 0,1 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,0 1-1 0 0,1-1 1 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0-1 0 0,0 1 1 0 0,1-1 0 0 0,1 0-1 0 0,2 1-246 0 0,0-1-1 0 0,0 0 1 0 0,0 0-1 0 0,0-1 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0-1-1 0 0,0 0 1 0 0,0 0-1 0 0,-1-1 1 0 0,9-3 0 0 0,-7 3 398 0 0,-1-1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 1 0 0,5-8-1 0 0,-6 8 453 0 0,0-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-10 0 0 0,-2 12-697 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0-1 0 0 0,-1 1 1 0 0,-1-7-1 0 0,1 9-995 0 0,2-1-13 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4190.02">2611 29 14167 0 0,'0'0'69'0'0,"0"-1"-1"0"0,1 1 1 0 0,-1 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,-1-1-1 0 0,1 1 1 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,-1 0 1 0 0,1-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0 0-1 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 1 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1-1-1 0 0,0 1 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-13 4 1621 0 0,-13 16-303 0 0,26-19-1366 0 0,-15 14 596 0 0,-25 29-1 0 0,34-36-452 0 0,0 0 0 0 0,1 0-1 0 0,0 2 1 0 0,0-2-1 0 0,1 1 1 0 0,-5 12-1 0 0,9-19-163 0 0,0 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,4 2 0 0 0,-2-1-165 0 0,2-1 0 0 0,-1 1 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,1-2 0 0 0,0 1-1 0 0,-2-1 1 0 0,2 1 0 0 0,0-1 0 0 0,-1-1-1 0 0,1 1 1 0 0,4-3 0 0 0,-3 2 59 0 0,-1-1 0 0 0,1 0-1 0 0,-2 0 1 0 0,2 0 0 0 0,-1-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-2-1 0 0 0,1 1 0 0 0,6-8-1 0 0,-8 8 360 0 0,-2 0-1 0 0,2 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,-2-1 0 0 0,2 1 1 0 0,-1 0-1 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,-1 1-1 0 0,0-1 0 0 0,0 0 1 0 0,-1-5-1 0 0,0 0 517 0 0,0 1 0 0 0,-5-16 0 0 0,-3 6-1535 0 0,-1 3-5994 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4475.43">2764 322 15551 0 0,'0'8'344'0'0,"-1"-5"72"0"0,1 0 8 0 0,0-1 8 0 0,-2 0-344 0 0,0 0-88 0 0,1 0 0 0 0,-2 2 0 0 0,-3 3 528 0 0,0 2 88 0 0,-2 1 24 0 0,1-2 0 0 0,-1 0-928 0 0,2 0-176 0 0,0 0-40 0 0,-2 3-8 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4966.65">3253 31 11519 0 0,'0'0'25'0'0,"0"-1"1"0"0,0 1-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0-1 0 0 0,-8 7 870 0 0,-2 5-82 0 0,6-6-346 0 0,2-4-441 0 0,-19 29 772 0 0,-2-2-1 0 0,-28 25 1 0 0,45-47-335 0 0,-2 1 0 0 0,2 0 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 0 0 0,-6 13 0 0 0,11-18-417 0 0,0 0 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0-1 0 0,1 0 1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,1 0 0 0 0,0-1 0 0 0,1 1-1 0 0,-1 0 1 0 0,0 0 0 0 0,0-1 0 0 0,1 1-1 0 0,-1-1 1 0 0,1 0 0 0 0,-2 2 0 0 0,2-2-1 0 0,3 2 1 0 0,0 0-445 0 0,0 0 1 0 0,0 0-1 0 0,-1-1 0 0 0,2 1 0 0 0,-2-1 0 0 0,2-1 0 0 0,0 1 1 0 0,-1-1-1 0 0,1 0 0 0 0,-2 0 0 0 0,2-1 0 0 0,-1 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,1-1 0 0 0,-1 1 0 0 0,1-2 0 0 0,-1 1 1 0 0,0-1-1 0 0,1 1 0 0 0,-1-2 0 0 0,0 1 0 0 0,-1 0 0 0 0,2-1 1 0 0,-1 0-1 0 0,5-6 0 0 0,-7 6 555 0 0,1-1 1 0 0,0 0-1 0 0,-1 0 1 0 0,6-6-1 0 0,-6 6 706 0 0,-1 0 1 0 0,0-2-1 0 0,1 2 0 0 0,2-11 1 0 0,-4 12-399 0 0,1-1 0 0 0,-1 0 1 0 0,0 1-1 0 0,0-2 0 0 0,-1 1 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1-3 1 0 0,0 2-340 0 0,-1 1 1 0 0,1 1 0 0 0,0-1-1 0 0,0 1 1 0 0,-1-1 0 0 0,-3-5-1 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5340.85">3481 114 13703 0 0,'0'-6'457'0'0,"0"3"47"0"0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-2 0 0 0,0 2 0 0 0,-1-1 0 0 0,0-3 1 0 0,0 6-419 0 0,1-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0-1-1 0 0,-1 1 1 0 0,1 0-1 0 0,0-1 1 0 0,0 1-1 0 0,-1 0 1 0 0,1-1-1 0 0,0 1 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1-1-1 0 0,-1 1-25 0 0,0 0 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,-1 0 1 0 0,-8 5 110 0 0,1 0 1 0 0,1 2 0 0 0,-10 8 0 0 0,-7 7 32 0 0,10-12-12 0 0,4-4-69 0 0,0 2-1 0 0,0 0 1 0 0,1 0-1 0 0,0 1 1 0 0,-13 18-1 0 0,22-28-97 0 0,1 1 0 0 0,-1 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,1 1 0 0 0,-1 0-27 0 0,0 0 1 0 0,1-1-1 0 0,0 0 1 0 0,0 1-1 0 0,0-1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,1 1 1 0 0,4 0-189 0 0,-2 0 1 0 0,1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0-1 0 0 0,0 0-1 0 0,6 0 1 0 0,-5 0-177 0 0,0-1 1 0 0,1 0-1 0 0,-2-1 0 0 0,2 0 0 0 0,-2 0 0 0 0,2 0 0 0 0,-2-1 1 0 0,2 0-1 0 0,-2 0 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,-2 0 0 0 0,2-1 0 0 0,-2-1 0 0 0,8-7 0 0 0,-8 8 439 0 0,0-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0-1 0 0 0,3-6 0 0 0,-4 7 583 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0-1-1 0 0,-1-8 1 0 0,-1 13-502 0 0,0 0 0 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 1 0 0,0 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,0-1 1 0 0,1 1-1 0 0,-1 0 0 0 0,0 0 1 0 0,-2-2-1 0 0,-2-2-4805 0 0,9 9 2955 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5700.92">3752 42 14623 0 0,'0'0'715'0'0,"-6"8"178"0"0,-45 54 1128 0 0,-7 8-514 0 0,56-67-1455 0 0,-1 0 0 0 0,1 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 1 0 0 0,1 0 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1-1 0 0,0 5 1 0 0,1-6-28 0 0,1 1 1 0 0,-1-1-1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 1 0 0,0 1-1 0 0,-1-1 0 0 0,1 0 0 0 0,1 1 0 0 0,2 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,4-3 0 0 0,-6 3 8 0 0,1-2-1 0 0,-2 1 0 0 0,1 1 1 0 0,0-1-1 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 1 0 0,-1-1-1 0 0,1 1 0 0 0,-1-1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0-1 0 0 0,-1 0 1 0 0,0 1-1 0 0,0 0 1 0 0,0-1-1 0 0,0 1 1 0 0,0-1-1 0 0,-1 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,0-1 1 0 0,0-2-1 0 0,-1 1 446 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0-1 0 0 0,-4-7-1 0 0,-2-6 1016 0 0,8 8-518 0 0,0 9-2189 0 0</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -7217,8 +7259,8 @@
       <inkml:brushProperty name="color" value="#E71224"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 97 4607 0 0,'41'-5'1812'0'0,"3"-2"-265"0"0,-27 5-1339 0 0,-1-1 1 0 0,0 0-1 0 0,21-8 0 0 0,-21 7-14 0 0,-1 0-1 0 0,1 0 1 0 0,0 2-1 0 0,-1 0 1 0 0,1 1-1 0 0,24 1 0 0 0,21-2 115 0 0,-13-5-153 0 0,-33 5-1 0 0,-1-1 0 0 0,1 2 0 0 0,-1 0 0 0 0,22 2 0 0 0,-31-1-124 0 0,-1 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 1-1 0 0,0 0 1 0 0,0-1-1 0 0,-1 2 1 0 0,1-1 0 0 0,0 0-1 0 0,-1 1 1 0 0,0-1-1 0 0,1 1 1 0 0,-1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0 1-1 0 0,-1-1 1 0 0,3 4-1 0 0,29 62-9 0 0,-25-51 88 0 0,-8-16-86 0 0,0 0 154 0 0,0 1-1 0 0,0 0 0 0 0,0 0 1 0 0,1-1-1 0 0,0 1 0 0 0,-1-1 1 0 0,1 1-1 0 0,4 3 0 0 0,-6-9-41 0 0,1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,3-5 0 0 0,4-2-150 0 0,-1 0-1 0 0,1 1 1 0 0,1-1-1 0 0,0 1 1 0 0,0 1-1 0 0,0 0 1 0 0,1 0-1 0 0,0 1 1 0 0,0 0-1 0 0,1 1 1 0 0,0 0-1 0 0,0 1 1 0 0,0 0-1 0 0,0 0 1 0 0,1 1-1 0 0,-1 1 1 0 0,1 0-1 0 0,16 0 1 0 0,-22 2 76 0 0,-1 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,11 4 0 0 0,9 1 44 0 0,40 2-87 0 0,-58-7 46 0 0,0-1-1 0 0,-1 0 1 0 0,1-1-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,11-4-1 0 0,-16 5-72 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0-1 0 0,1-1 1 0 0,-1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 0 0 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1584.34">1836 120 7023 0 0,'3'0'140'0'0,"0"-1"-1"0"0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,4-3 0 0 0,6-3 119 0 0,9 0 127 0 0,-1 1-1 0 0,1 0 1 0 0,0 2 0 0 0,34-2-1 0 0,-27 3 301 0 0,55-14-1 0 0,-67 13-613 0 0,0 1-1 0 0,1 0 1 0 0,-1 1-1 0 0,0 1 0 0 0,1 1 1 0 0,0 0-1 0 0,-1 1 1 0 0,0 1-1 0 0,33 7 0 0 0,-43-6-39 0 0,0 0-1 0 0,0 0 1 0 0,0 1-1 0 0,0 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,1 1 1 0 0,-2 0-1 0 0,8 7 0 0 0,5 7 138 0 0,20 28 0 0 0,-37-47-136 0 0,-1 1 1 0 0,1-1-1 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 69 0 0,1-1 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,0-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,1 0-1 0 0,-1 1 1 0 0,0-1-1 0 0,0 0 1 0 0,1 0-1 0 0,-1 1 0 0 0,0-1 1 0 0,1 0-1 0 0,-3 0 1 0 0,41-14 1087 0 0,-29 9-1093 0 0,1 0-1 0 0,-1 0 0 0 0,0-1 1 0 0,0 0-1 0 0,15-14 0 0 0,-18 13-21 0 0,1 1-1 0 0,1 0 1 0 0,-1 1 0 0 0,1-1-1 0 0,0 2 1 0 0,0-1 0 0 0,0 1-1 0 0,17-6 1 0 0,-12 7-17 0 0,0 1 1 0 0,0 0-1 0 0,0 1 1 0 0,0 1-1 0 0,19 1 0 0 0,64 13-971 0 0,2 1 2063 0 0,-82-14-1174 0 0,-1 0 0 0 0,1-1 0 0 0,0 0 0 0 0,0-1 1 0 0,0-1-1 0 0,0-1 0 0 0,-1 0 0 0 0,1-1 0 0 0,14-6 1 0 0,-19 6 127 0 0,-4 2 10 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,10-10 1 0 0,-15 13-142 0 0,0 0-1 0 0,-1 0 1 0 0,0 1 0 0 0,1-1-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,0 0-1 0 0,-1-1 1 0 0,0-1-606 0 0,4 2-5 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 103 4607 0 0,'38'-5'1812'0'0,"3"-3"-265"0"0,-25 6-1339 0 0,-1-1 1 0 0,0 0-1 0 0,19-9 0 0 0,-19 8-14 0 0,-1-1-1 0 0,1 1 1 0 0,0 2-1 0 0,-1 0 1 0 0,1 1-1 0 0,22 1 0 0 0,20-2 115 0 0,-12-6-153 0 0,-31 6-1 0 0,-1-1 0 0 0,1 2 0 0 0,-1 0 0 0 0,20 2 0 0 0,-28-1-124 0 0,-2 1-1 0 0,1 0 1 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 1-1 0 0,0 1 1 0 0,0-2-1 0 0,-2 2 1 0 0,2-1 0 0 0,0 0-1 0 0,-1 1 1 0 0,-1-1-1 0 0,2 2 1 0 0,-1-1-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1 1-1 0 0,0-1 1 0 0,3 5-1 0 0,27 65-9 0 0,-24-54 88 0 0,-7-17-86 0 0,0 0 154 0 0,0 2-1 0 0,0-1 0 0 0,0 0 1 0 0,0-1-1 0 0,1 1 0 0 0,-1-1 1 0 0,1 2-1 0 0,4 2 0 0 0,-6-9-41 0 0,1 1 0 0 0,0-2 0 0 0,-1 1 0 0 0,1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,3-6 0 0 0,3-1-150 0 0,0-1-1 0 0,0 2 1 0 0,2-2-1 0 0,-1 2 1 0 0,1 0-1 0 0,-1 1 1 0 0,1 0-1 0 0,1 0 1 0 0,-1 1-1 0 0,1 1 1 0 0,0-1-1 0 0,1 2 1 0 0,-1 0-1 0 0,0-1 1 0 0,1 2-1 0 0,0 1 1 0 0,0 0-1 0 0,15 0 1 0 0,-21 2 76 0 0,0 1 0 0 0,1 0 0 0 0,-2 0 0 0 0,11 4 0 0 0,8 2 44 0 0,38 1-87 0 0,-55-7 46 0 0,1-1-1 0 0,-1 0 1 0 0,0-1-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,10-4-1 0 0,-15 5-72 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0-1 0 0,1-1 1 0 0,-1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,0-2 0 0 0,1 2 0 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 0 0 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1584.34">1710 127 7023 0 0,'3'0'140'0'0,"0"-1"-1"0"0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 1 0 0,-1 1-1 0 0,5-3 0 0 0,5-4 119 0 0,9 1 127 0 0,-2 0-1 0 0,2 1 1 0 0,-1 2 0 0 0,32-3-1 0 0,-25 4 301 0 0,51-15-1 0 0,-62 14-613 0 0,0 1-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 2 0 0 0,0 1 1 0 0,1 0-1 0 0,-1 1 1 0 0,0 2-1 0 0,30 6 0 0 0,-39-6-39 0 0,-1 0-1 0 0,1 1 1 0 0,-1 0-1 0 0,1 0 0 0 0,-2 0 1 0 0,1 1-1 0 0,1 0 1 0 0,-3 0-1 0 0,8 8 0 0 0,5 7 138 0 0,18 30 0 0 0,-34-50-136 0 0,-1 1 1 0 0,1-1-1 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 2 0 0 0,0-1 0 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 69 0 0,1-1 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,0-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,1 0-1 0 0,0 1 1 0 0,-1-1-1 0 0,0 0 1 0 0,1 0-1 0 0,-1 1 0 0 0,0-1 1 0 0,1 0-1 0 0,-3 0 1 0 0,38-15 1087 0 0,-26 10-1093 0 0,0 0-1 0 0,0-1 0 0 0,-1 0 1 0 0,0 0-1 0 0,15-15 0 0 0,-18 13-21 0 0,2 2-1 0 0,0-1 1 0 0,0 2 0 0 0,0-1-1 0 0,1 1 1 0 0,-1 0 0 0 0,1 1-1 0 0,15-7 1 0 0,-11 8-17 0 0,0 1 1 0 0,0 0-1 0 0,0 1 1 0 0,0 1-1 0 0,18 1 0 0 0,60 14-971 0 0,1 1 2063 0 0,-76-15-1174 0 0,-1 0 0 0 0,1-1 0 0 0,-1 0 0 0 0,1-1 1 0 0,0-1-1 0 0,0-2 0 0 0,-1 1 0 0 0,1-1 0 0 0,13-7 1 0 0,-18 7 127 0 0,-3 2 10 0 0,-1-1-1 0 0,1 0 1 0 0,-1-1 0 0 0,1 0 0 0 0,-2 0 0 0 0,2 0 0 0 0,-1-1-1 0 0,8-9 1 0 0,-13 13-142 0 0,0 0-1 0 0,-1-1 1 0 0,0 2 0 0 0,1-1-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0-1 0 0,1-1 1 0 0,0 1 0 0 0,0 0-1 0 0,-1-1 1 0 0,0-1-606 0 0,4 2-5 0 0</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -7250,15 +7292,15 @@
       <inkml:brushProperty name="color" value="#E71224"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 92 8751 0 0,'3'0'2294'0'0,"-3"0"-2261"0"0,1 10 3271 0 0,-1 3-2911 0 0,14 173 2783 0 0,-12-160-2963 0 0,0-9-251 0 0,-1-1-1 0 0,-1 1 1 0 0,0 0 0 0 0,-2 0 0 0 0,-3 23 0 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1032.68">317 108 11863 0 0,'20'-1'4431'0'0,"-18"19"-2617"0"0,-1-17-1571 0 0,2 66-71 0 0,-5 93 0 0 0,1-151-450 0 0,1 0-1 0 0,0 0 0 0 0,0 0 1 0 0,3 14-1 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1359.96">348 76 11863 0 0,'-1'-6'4298'0'0,"9"-1"-3149"0"0,-2 4-926 0 0,1-1 0 0 0,0 1 1 0 0,-1 1-1 0 0,1 0 0 0 0,0 0 0 0 0,11-2 1 0 0,8-2 137 0 0,73-16-320 0 0,-55 15-4119 0 0,-39 7 2054 0 0,1 1-22 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1701.43">366 254 16127 0 0,'2'-1'314'0'0,"0"0"1"0"0,0 1-1 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,2 0 0 0 0,2-2 53 0 0,78-16 159 0 0,44-3-1008 0 0,-125 21 349 0 0,7-1-1156 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2059.68">377 466 15775 0 0,'-1'-1'37'0'0,"1"1"-1"0"0,0 0 1 0 0,0-1 0 0 0,0 1-1 0 0,-1-1 1 0 0,1 1-1 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,0 1 0 0 0,0-1-1 0 0,0 1 1 0 0,1 0-1 0 0,-1-1 1 0 0,13-2 1997 0 0,-1 1-1323 0 0,10-2 997 0 0,-1 1-1 0 0,35 0 0 0 0,11 5-2716 0 0,-56-2 31 0 0,1-1-13 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3163.26">1052 298 14311 0 0,'0'1'73'0'0,"0"-1"0"0"0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,-1 0 1 0 0,1 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 1-1 0 0,1-1 1 0 0,-1 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 0-1 0 0,0 1 1 0 0,1-1 0 0 0,-1 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 1-1 0 0,0-1 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 1 0 0 0,0-1-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,0 1 1 0 0,1-1-1 0 0,-1 0 1 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0-1 0 0,1-1 1 0 0,23-3 2890 0 0,-20 3-2615 0 0,61-11 3501 0 0,-29 6-3453 0 0,66-21 0 0 0,-69 14-4096 0 0,-1-4-3689 0 0,-28 14 5501 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3490.7">1194 88 11631 0 0,'2'0'260'0'0,"0"1"-1"0"0,-1-1 0 0 0,1 1 1 0 0,-1-1-1 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 1 0 0,-1 0-1 0 0,0 0 0 0 0,1-1 1 0 0,-1 1-1 0 0,0 0 0 0 0,0 0 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 1 0 0 0,1-1 1 0 0,0 0-1 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 1 0 0,0-1-1 0 0,-1 1 0 0 0,0-1 1 0 0,1 3-1 0 0,1 5 253 0 0,0-1 1 0 0,-1 1-1 0 0,1 16 1 0 0,-4 39 1006 0 0,1-42-1401 0 0,1 0 0 0 0,0-1-1 0 0,6 31 1 0 0,-4-21-2779 0 0,-5-11-2895 0 0,0-15 3605 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4666.52">1960 66 10247 0 0,'0'0'1026'0'0,"-5"0"-572"0"0,0 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,0 1 1 0 0,0 0-1 0 0,1 0 0 0 0,-1 0 1 0 0,1 1-1 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,-1 0 1 0 0,1 1-1 0 0,0-1 1 0 0,-4 4-1 0 0,4-2-358 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,-1 6 0 0 0,-3 23 51 0 0,1 1 0 0 0,-1 38-1 0 0,6-69-122 0 0,1 0 1 0 0,-1-1-1 0 0,1 1 0 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,1 0 0 0 0,-1-1 0 0 0,1 0 1 0 0,0 1-1 0 0,0-1 0 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 0 0 0,0-1 1 0 0,1 0-1 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 1 0 0,1-1-1 0 0,-1 0 0 0 0,1 0 0 0 0,0-1 1 0 0,0 1-1 0 0,-1-1 0 0 0,1 0 0 0 0,0 0 1 0 0,0-1-1 0 0,-1 0 0 0 0,1 1 0 0 0,0-2 1 0 0,6-1-1 0 0,-5 1-46 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,7-7 0 0 0,-10 8 12 0 0,-1 0 1 0 0,0-1-1 0 0,1 1 0 0 0,-1 0 0 0 0,0-1 1 0 0,-1 1-1 0 0,1-1 0 0 0,0 1 1 0 0,-1-1-1 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,1-5 0 0 0,3-17 24 0 0,-1 10 12 0 0,-2 0 0 0 0,0 0 0 0 0,0-23 0 0 0,-2 7 47 0 0,1 19 57 0 0,-1 0 0 0 0,0 0 0 0 0,-1 1 0 0 0,-1-1 0 0 0,-5-21 0 0 0,6 31-91 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 1 0 0,-1 0-1 0 0,1 1 0 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,-4-1 0 0 0,-4-1-332 0 0,0 0 0 0 0,-20 0 0 0 0,25 2-33 0 0,-5 0-1030 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5243.38">2454 1 12671 0 0,'-20'4'3576'0'0,"18"-4"-3497"0"0,1 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,-1 1-1 0 0,0-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,1 1-1 0 0,-1 0 1 0 0,1 0-1 0 0,0-1 0 0 0,-1 1 1 0 0,1 0-1 0 0,0 0 1 0 0,0 1-1 0 0,0-1 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,1 1 0 0 0,-2 1 1 0 0,-17 30 1208 0 0,9-19-853 0 0,2 1 0 0 0,0 0 0 0 0,1 1 0 0 0,-10 29 0 0 0,10-18-250 0 0,0-1 81 0 0,1 0-1 0 0,-3 35 0 0 0,9-57-247 0 0,0 1 0 0 0,0-1-1 0 0,1 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,0 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,3 6 1 0 0,-1-4-4 0 0,0 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,6 5 0 0 0,-9-8-80 0 0,0-1 1 0 0,0 0-1 0 0,-1 1 0 0 0,1-1 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,0-1 0 0 0,0 0 1 0 0,1 1-1 0 0,-1-1 1 0 0,0-1-1 0 0,1 1 0 0 0,-1 0 1 0 0,0 0-1 0 0,0-1 1 0 0,1 1-1 0 0,-1-1 0 0 0,2-1 1 0 0,-1 1 26 0 0,-1 0 1 0 0,1-1-1 0 0,-1 0 1 0 0,0 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,0-1 1 0 0,-1 1 0 0 0,1 0-1 0 0,-1-1 1 0 0,0 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,-1 1 1 0 0,2-5-1 0 0,-2 5 62 0 0,1 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0-1-1 0 0,-1 1 1 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,-2 0 0 0 0,-5-1 99 0 0,1 1 0 0 0,-1 0 1 0 0,1 1-1 0 0,-1 0 1 0 0,1 0-1 0 0,-10 3 1 0 0,-15 1-2531 0 0,22-3 1205 0 0,2 1-11 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 94 8751 0 0,'3'0'2294'0'0,"-3"0"-2261"0"0,1 11 3271 0 0,-1 2-2911 0 0,12 178 2783 0 0,-10-165-2963 0 0,0-8-251 0 0,-1-2-1 0 0,-1 2 1 0 0,0-1 0 0 0,-2 1 0 0 0,-2 23 0 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1032.67">290 111 11863 0 0,'18'-1'4431'0'0,"-16"19"-2617"0"0,-1-17-1571 0 0,1 68-71 0 0,-3 95 0 0 0,0-155-450 0 0,1 1-1 0 0,0-1 0 0 0,0 0 1 0 0,2 15-1 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1359.96">318 78 11863 0 0,'-1'-6'4298'0'0,"8"-1"-3149"0"0,-1 4-926 0 0,0-2 0 0 0,1 2 1 0 0,-2 1-1 0 0,2 0 0 0 0,-1 0 0 0 0,10-2 1 0 0,8-2 137 0 0,67-17-320 0 0,-51 16-4119 0 0,-36 7 2054 0 0,2 1-22 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1701.43">334 261 16127 0 0,'2'-2'314'0'0,"0"1"1"0"0,0 1-1 0 0,0-1 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 1 0 0 0,2 0 0 0 0,1-2 53 0 0,72-16 159 0 0,40-4-1008 0 0,-114 22 349 0 0,6-1-1156 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2059.67">345 478 15775 0 0,'-1'-1'37'0'0,"1"1"-1"0"0,0 0 1 0 0,0-1 0 0 0,0 1-1 0 0,-1-1 1 0 0,1 1-1 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,0 1 0 0 0,0-1-1 0 0,0 1 1 0 0,1 0-1 0 0,-1-1 1 0 0,11-2 1997 0 0,0 1-1323 0 0,9-3 997 0 0,0 2-1 0 0,31 0 0 0 0,10 5-2716 0 0,-51-2 31 0 0,1-1-13 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3163.26">961 306 14311 0 0,'0'1'73'0'0,"0"-1"0"0"0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,-1 0 1 0 0,1 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 1-1 0 0,1-1 1 0 0,-1 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 0-1 0 0,0 1 1 0 0,1-1 0 0 0,-1 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 1-1 0 0,0-1 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 1 0 0 0,0-1-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0-1 0 0,0 1 1 0 0,1-1-1 0 0,-1 0 1 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0-1 0 0,1-1 1 0 0,21-3 2890 0 0,-18 3-2615 0 0,55-12 3501 0 0,-26 7-3453 0 0,60-21 0 0 0,-63 13-4096 0 0,0-3-3689 0 0,-27 14 5501 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3490.7">1091 90 11631 0 0,'2'0'260'0'0,"0"1"-1"0"0,-1-1 0 0 0,0 1 1 0 0,0-1-1 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 1 0 0,-1 0-1 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0 0 0 0 0,0 2 1 0 0,1-2-1 0 0,-1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,-1 1 0 0 0,1-1 1 0 0,0 0-1 0 0,-1 1 0 0 0,0-1 0 0 0,1 1 1 0 0,0-1-1 0 0,-1 1 0 0 0,0-1 1 0 0,1 3-1 0 0,1 5 253 0 0,0 0 1 0 0,-1 0-1 0 0,1 16 1 0 0,-4 41 1006 0 0,1-43-1401 0 0,1-1 0 0 0,0 0-1 0 0,5 31 1 0 0,-3-21-2779 0 0,-5-12-2895 0 0,1-15 3605 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4666.52">1791 68 10247 0 0,'0'0'1026'0'0,"-5"0"-572"0"0,1 0 0 0 0,0 1 1 0 0,-1-1-1 0 0,1 1 1 0 0,-1 0-1 0 0,2 0 0 0 0,-2 0 1 0 0,1 1-1 0 0,0 0 1 0 0,0 0-1 0 0,1 0 0 0 0,-2 0 1 0 0,1 1-1 0 0,1-1 1 0 0,-5 4-1 0 0,5-2-358 0 0,-1 2 0 0 0,1-2 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,1 0 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 6 0 0 0,-4 24 51 0 0,2 1 0 0 0,-2 39-1 0 0,6-71-122 0 0,1 0 1 0 0,-1-1-1 0 0,1 1 0 0 0,0 1 0 0 0,0-2 1 0 0,0 1-1 0 0,0 0 0 0 0,0-1 0 0 0,1 0 1 0 0,0 1-1 0 0,0-1 0 0 0,1 0 0 0 0,-2 1 1 0 0,2-1-1 0 0,0 0 0 0 0,0-1 0 0 0,-1 1 1 0 0,2-1-1 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 1 0 0,0 0-1 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,1-1 0 0 0,-2 1 1 0 0,2-1-1 0 0,-2 0 0 0 0,2 0 0 0 0,0-1 1 0 0,-1 1-1 0 0,0-1 0 0 0,0 0 0 0 0,1 0 1 0 0,-1-1-1 0 0,0 0 0 0 0,1 1 0 0 0,-1-2 1 0 0,6-1-1 0 0,-4 1-46 0 0,-1-2 0 0 0,0 1 0 0 0,0 0 1 0 0,1 0-1 0 0,6-7 0 0 0,-10 8 12 0 0,0 0 1 0 0,0-1-1 0 0,1 1 0 0 0,-1 0 0 0 0,-1-1 1 0 0,0 1-1 0 0,1-2 0 0 0,0 2 1 0 0,-1-1-1 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,0-5 0 0 0,4-18 24 0 0,-1 11 12 0 0,-3-1 0 0 0,1 1 0 0 0,0-24 0 0 0,-2 7 47 0 0,1 20 57 0 0,-1 0 0 0 0,0-1 0 0 0,-1 2 0 0 0,-1-1 0 0 0,-4-22 0 0 0,5 32-91 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 1 0 0,-1 0-1 0 0,1 1 0 0 0,-1 0 0 0 0,0-2 0 0 0,1 2 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,1 1 0 0 0,-5-1 0 0 0,-3-1-332 0 0,0 0 0 0 0,-18 0 0 0 0,22 2-33 0 0,-4 0-1030 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="5243.38">2242 1 12671 0 0,'-18'4'3576'0'0,"16"-4"-3497"0"0,1 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,0 1-1 0 0,-1-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,1 1-1 0 0,-1 0 1 0 0,2 0-1 0 0,-1-1 0 0 0,-1 1 1 0 0,1 0-1 0 0,0 0 1 0 0,0 1-1 0 0,0-1 1 0 0,-1 0-1 0 0,1 0 1 0 0,0 0-1 0 0,1 2 0 0 0,-1 0 1 0 0,-17 30 1208 0 0,9-18-853 0 0,2 0 0 0 0,0 1 0 0 0,0 0 0 0 0,-8 30 0 0 0,8-18-250 0 0,1-1 81 0 0,0-1-1 0 0,-2 37 0 0 0,8-59-247 0 0,0 1 0 0 0,0-1-1 0 0,1 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,0 2-1 0 0,1-2 1 0 0,-1 0-1 0 0,0 0 1 0 0,1 0-1 0 0,3 6 1 0 0,-2-4-4 0 0,1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,6 5 0 0 0,-8-8-80 0 0,0-1 1 0 0,0 1-1 0 0,-1 0 0 0 0,1-1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 1 0 0,1 1-1 0 0,-2-1 1 0 0,1-1-1 0 0,1 1 0 0 0,-1 0 1 0 0,0 0-1 0 0,-1-1 1 0 0,2 1-1 0 0,-1-1 0 0 0,2-1 1 0 0,-2 1 26 0 0,0 0 1 0 0,1-1-1 0 0,-1-1 1 0 0,0 2-1 0 0,0-1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 0-1 0 0,-1-1 1 0 0,0 1 0 0 0,1 0-1 0 0,-1-1 1 0 0,0 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,-1 1 1 0 0,2-6-1 0 0,-2 6 62 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,1 0 0 0 0,-1 1-1 0 0,0-1 1 0 0,-1 1 0 0 0,1-2 0 0 0,0 2 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,-6-1 99 0 0,2 1 0 0 0,-1 0 1 0 0,0 1-1 0 0,0 0 1 0 0,0 1-1 0 0,-8 2 1 0 0,-14 1-2531 0 0,20-3 1205 0 0,1 1-11 0 0</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -7355,14 +7397,14 @@
       <inkml:brushProperty name="color" value="#E71224"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1770 101 12551 0 0,'-1'-3'165'0'0,"0"-1"259"0"0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 1-1 0 0,-1-1 1 0 0,0 1 0 0 0,0 0 0 0 0,-5-6 0 0 0,7 9-396 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 1 0 0 0,1-1 1 0 0,-1 0-1 0 0,0 1 0 0 0,0-1 1 0 0,1 0-1 0 0,-1 1 0 0 0,0-1 1 0 0,1 1-1 0 0,-1-1 0 0 0,0 1 1 0 0,1 0-1 0 0,-1-1 0 0 0,1 1 1 0 0,-1 1-1 0 0,-18 21 210 0 0,15-18-126 0 0,-20 25 636 0 0,-1-2 1 0 0,-32 28 0 0 0,52-52-676 0 0,1 0-1 0 0,0 0 1 0 0,1 1-1 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,-1 8-1 0 0,4-10-76 0 0,-1-1-1 0 0,1 1 1 0 0,-1 0 0 0 0,1-1-1 0 0,0 1 1 0 0,0 0-1 0 0,1-1 1 0 0,-1 1 0 0 0,0 0-1 0 0,1-1 1 0 0,0 1 0 0 0,-1-1-1 0 0,1 1 1 0 0,0-1 0 0 0,0 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,0-1 1 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,3 2 1 0 0,1 0-149 0 0,1-1 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 0 0 0 0,0-1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0-1 0 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 0 1 0 0,-1 0-1 0 0,0-1 0 0 0,0 0 0 0 0,7-5 0 0 0,-7 2 418 0 0,-1 0 0 0 0,0-1 0 0 0,0 1-1 0 0,-1-1 1 0 0,0 0 0 0 0,-1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0-1 0 0 0,-1 1 0 0 0,1-13-1 0 0,-3 17-45 0 0,0 0 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,-3-5 0 0 0,3 6-246 0 0,1-1 1 0 0,-1 1-1 0 0,0-1 1 0 0,1 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 1 0 0,0 0-1 0 0,0-7 1 0 0,2 10-100 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,5-4-1057 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="495.13">2123 73 13359 0 0,'0'0'85'0'0,"0"-1"-1"0"0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 1 0 0,-1 1-1 0 0,1-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 1 0 0,-1-1-1 0 0,1 1 0 0 0,0-1 0 0 0,-1 1 1 0 0,0-1-1 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1 0 1 0 0,0-1-1 0 0,0 1 0 0 0,-1 0 48 0 0,1-1-1 0 0,0 1 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1-1-1 0 0,1 1 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 1-1 0 0,-1-1 1 0 0,-1 0-1 0 0,-7 6 157 0 0,0 1-1 0 0,1-1 1 0 0,0 1-1 0 0,0 1 1 0 0,0 0 0 0 0,-9 12-1 0 0,-20 17 344 0 0,15-20-252 0 0,12-9-159 0 0,0 0-1 0 0,1 1 1 0 0,0 0 0 0 0,-16 20 0 0 0,24-27-207 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,1 1 0 0 0,1 1 0 0 0,1 1-141 0 0,0-1 1 0 0,0 0-1 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 1 0 0,1 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,0-1 0 0 0,1 0 1 0 0,-1-1-1 0 0,1 0 0 0 0,-1 1 0 0 0,6-1 1 0 0,-1 0-193 0 0,-1 0 0 0 0,0-1 0 0 0,0 0-1 0 0,0-1 1 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 0 0 0 0,11-5 0 0 0,-14 4 458 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,6-10-1 0 0,-4 6 645 0 0,-1-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,0 0-1 0 0,-2 0 1 0 0,3-13 0 0 0,-5 19-587 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-1 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 1-1 0 0,-3-8 1 0 0,1 6-178 0 0,2 0 0 0 0,-1 0 0 0 0,-1-13 0 0 0,3 19-108 0 0,0-1 0 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,1 0 0 0 0,-1 1-1 0 0,0-1 1 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,1-1-1 0 0,-1 1 1 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1-1-1 0 0,-1 1 1 0 0,1 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,9 3-1220 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="839.72">2528 13 15431 0 0,'-1'-1'102'0'0,"0"0"-1"0"0,0 1 0 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 0 0 0,0 0 1 0 0,-2 1-1 0 0,-19 10 954 0 0,12-5-752 0 0,2 2 1 0 0,-1-1-1 0 0,1 1 1 0 0,0 1 0 0 0,1-1-1 0 0,-8 12 1 0 0,-3 3-131 0 0,-16 14 264 0 0,-6 6 387 0 0,39-41-812 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,1 1 1 0 0,-1-1-1 0 0,1 1 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,1 0 1 0 0,-1 1-1 0 0,1-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,3 3-1 0 0,-1-1-102 0 0,0-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 0 0 0 0,1 1 0 0 0,7-1 0 0 0,-4-1-99 0 0,1 0 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1-1 1 0 0,1-1-1 0 0,-1 1 0 0 0,1-2 0 0 0,-1 1 0 0 0,0-1 0 0 0,12-8 0 0 0,-15 8 569 0 0,0 1 0 0 0,-1-2 0 0 0,1 1 0 0 0,-1 0 1 0 0,0-1-1 0 0,0 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,2-8 0 0 0,-3 6-10 0 0,-1-1-1 0 0,0 1 1 0 0,0-1-1 0 0,-1 1 1 0 0,-1 0-1 0 0,-2-13 1 0 0,-3-24-85 0 0,6 20-1241 0 0,4 8-2414 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="-1929.66">391 44 10711 0 0,'0'0'157'0'0,"-1"-1"0"0"0,1 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1-1 0 0,1 0 1 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1-1 0 0,-1-1 1 0 0,1 1 0 0 0,-1-2 0 0 0,1 2-101 0 0,0-1 0 0 0,0 1-1 0 0,-1-1 1 0 0,1 1 0 0 0,0 0-1 0 0,0-1 1 0 0,-1 1 0 0 0,1-1-1 0 0,0 1 1 0 0,-1 0 0 0 0,1-1-1 0 0,-1 1 1 0 0,1 0 0 0 0,0-1-1 0 0,-1 1 1 0 0,1 0 0 0 0,-1 0-1 0 0,1-1 1 0 0,0 1 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1-1-1 0 0,1 1 1 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 1 0 0 0,-1-1-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 1 0 0 0,-3 1 101 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,1 1 1 0 0,0 0-1 0 0,0 0 1 0 0,-3 4-1 0 0,-3 7 227 0 0,-11 25 0 0 0,0 1-110 0 0,13-28-142 0 0,0 0-1 0 0,0 0 1 0 0,-5 20 0 0 0,10-28-74 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,4 10 0 0 0,-4-11-59 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,7-4 0 0 0,-4 3-18 0 0,0-2 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0-1 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,6-12 0 0 0,-5 7 327 0 0,-1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1-20 0 0 0,-4 28-191 0 0,0 1-1 0 0,-1-1 1 0 0,1 0-1 0 0,0 1 1 0 0,-1 0 0 0 0,1-1-1 0 0,-1 1 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0-1 0 0,-1 0 1 0 0,-2-3-1 0 0,-2-2-42 0 0,0 1-1 0 0,-1 0 0 0 0,-7-6 0 0 0,-9-7-4019 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="-1265.9">760 68 11167 0 0,'-10'-22'2680'0'0,"9"21"-2647"0"0,0 1-1 0 0,0-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0-1 0 0,1-1 1 0 0,-1 1-1 0 0,0 0 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,-8-1 877 0 0,9 1-805 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 1-1 0 0,0-1 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,1 1 1 0 0,-1-1-1 0 0,0 1 1 0 0,0-1-1 0 0,1 1 1 0 0,-1 0-1 0 0,0-1 1 0 0,1 1-1 0 0,-1 0 1 0 0,1-1-1 0 0,-1 1 1 0 0,0 1-1 0 0,-14 23 626 0 0,13-21-490 0 0,-20 45 496 0 0,15-32-537 0 0,0-1 1 0 0,-12 19 0 0 0,15-30-113 0 0,1 0 0 0 0,0 0 0 0 0,1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1 8 0 0 0,1-11-87 0 0,1 1 1 0 0,0 0 0 0 0,1-1 0 0 0,-1 1-1 0 0,1 0 1 0 0,-1-1 0 0 0,1 1 0 0 0,0-1-1 0 0,0 1 1 0 0,1-1 0 0 0,-1 1 0 0 0,1-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,2 3 1 0 0,0-1-1 0 0,-1-1-1 0 0,1 0 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1-1 0 0,1 0 1 0 0,8 5-1 0 0,-11-7-7 0 0,1 0 0 0 0,0 0-1 0 0,-1-1 1 0 0,1 1 0 0 0,0-1-1 0 0,0 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,0 0 0 0 0,0-1-1 0 0,0 1 1 0 0,-1 0 0 0 0,1-1-1 0 0,0 0 1 0 0,-1 1 0 0 0,1-1-1 0 0,0 0 1 0 0,4-3 0 0 0,2-1-4 0 0,0 0 0 0 0,0-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-2-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,-1 0 0 0 0,3-13 0 0 0,-5 21 79 0 0,0-1 1 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 1 1 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,-2-2 0 0 0,-10-5-188 0 0,-9-5 247 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="-742.93">1106 49 13359 0 0,'0'-2'140'0'0,"0"0"-1"0"0,-1 0 1 0 0,0 0 0 0 0,1 1-1 0 0,-1-1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,-3-2-1 0 0,4 4-92 0 0,-1-1-1 0 0,1 1 1 0 0,-1-1 0 0 0,1 1-1 0 0,-1-1 1 0 0,1 1 0 0 0,-1 0-1 0 0,1-1 1 0 0,-1 1-1 0 0,0 0 1 0 0,1 0 0 0 0,-1-1-1 0 0,0 1 1 0 0,1 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,1 0-1 0 0,-1 1 1 0 0,1-1-1 0 0,-1 0 1 0 0,0 1 0 0 0,1-1-1 0 0,-1 0 1 0 0,1 1 0 0 0,-1-1-1 0 0,1 0 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,0 0 0 0 0,-5 8 409 0 0,1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,-6 16 0 0 0,-3 6 545 0 0,-12 10-152 0 0,19-32-626 0 0,1 1 0 0 0,0-1 0 0 0,-9 20 0 0 0,14-26-207 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1 0 1 0 0,-1-1-1 0 0,1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,2 0 1 0 0,-1 0-1 0 0,0 1 0 0 0,0-2 0 0 0,4 4 0 0 0,-2-3-25 0 0,-1 0 0 0 0,0 0-1 0 0,0-1 1 0 0,1 1 0 0 0,-1-1-1 0 0,1 1 1 0 0,0-1 0 0 0,-1 0-1 0 0,1 0 1 0 0,0-1 0 0 0,-1 1-1 0 0,1-1 1 0 0,0 0 0 0 0,0 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0-1-1 0 0,0 0 1 0 0,-1 1 0 0 0,1-1-1 0 0,0-1 1 0 0,-1 1 0 0 0,5-2 0 0 0,-3-1 82 0 0,1 1 1 0 0,-1-1 0 0 0,0-1-1 0 0,0 1 1 0 0,-1 0 0 0 0,1-1 0 0 0,-1 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-1-1-1 0 0,1 1 1 0 0,-1-1 0 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,3-9 0 0 0,-4 8 10 0 0,1 0 1 0 0,-1-1 0 0 0,0 1-1 0 0,-1 0 1 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,-1 0-1 0 0,0-1 1 0 0,-1 1 0 0 0,1 0-1 0 0,-1 0 1 0 0,-1 0 0 0 0,-3-7-1 0 0,5 11-143 0 0,-7-16-1470 0 0,7 18 1477 0 0,1 1 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1 0 0 0,0 0 0 0 0,1-1 0 0 0,6 2-1131 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1800.81">51 363 16007 0 0,'-3'-4'352'0'0,"3"7"64"0"0,1 1 24 0 0,-1-1 16 0 0,0 1-360 0 0,0 0-96 0 0,-1 1 0 0 0,0 3 0 0 0,-2 6 424 0 0,-1 3 72 0 0,0 0 16 0 0,-3 0 0 0 0,-1-1-1184 0 0,2-2-224 0 0,-2-2-56 0 0,1-1-8 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2442.66">1390 350 20271 0 0,'4'0'448'0'0,"-2"1"88"0"0,-2 2 16 0 0,-1-1 24 0 0,1-1-464 0 0,-1 2-112 0 0,-1-1 0 0 0,-2 4 0 0 0,-4 3 536 0 0,-2 2 80 0 0,-2 2 24 0 0,-3 0 0 0 0,1-1-1256 0 0,0-1-248 0 0,-2 0-56 0 0,6 2-8 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1698 103 12551 0 0,'-1'-3'165'0'0,"0"-1"259"0"0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,1 1-1 0 0,-1-1 1 0 0,1 1 0 0 0,-1 0 0 0 0,-5-6 0 0 0,7 9-396 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 1 0 0 0,1-1 1 0 0,0 0-1 0 0,-1 1 0 0 0,0-1 1 0 0,1 0-1 0 0,-1 1 0 0 0,0-1 1 0 0,1 1-1 0 0,-1-1 0 0 0,0 1 1 0 0,1 0-1 0 0,-1-1 0 0 0,1 1 1 0 0,-1 1-1 0 0,-17 22 210 0 0,14-19-126 0 0,-19 25 636 0 0,-1-1 1 0 0,-31 28 0 0 0,50-53-676 0 0,2 1-1 0 0,-1-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,2 0-1 0 0,-2 1 1 0 0,-1 7-1 0 0,4-10-76 0 0,-1-1-1 0 0,1 1 1 0 0,-1 0 0 0 0,1-1-1 0 0,0 1 1 0 0,0 0-1 0 0,1-1 1 0 0,-1 1 0 0 0,0 1-1 0 0,1-2 1 0 0,0 1 0 0 0,-1-1-1 0 0,1 1 1 0 0,0-1 0 0 0,0 1-1 0 0,1-1 1 0 0,-1 1-1 0 0,-1-1 1 0 0,2 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,0 0 0 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,3 2 1 0 0,1 1-149 0 0,0-2 0 0 0,0 0 1 0 0,1 0-1 0 0,-2 0 0 0 0,2 0 0 0 0,0-1 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-2-1 0 0 0,1 0 1 0 0,0 0-1 0 0,-1 0 0 0 0,1-1 0 0 0,0-1 0 0 0,0 1 0 0 0,-2-1 0 0 0,2 0 1 0 0,-1 0-1 0 0,0-1 0 0 0,-1-1 0 0 0,8-4 0 0 0,-8 2 418 0 0,0 0 0 0 0,0-1 0 0 0,0 1-1 0 0,-1-2 1 0 0,0 1 0 0 0,-2 0 0 0 0,1 0-1 0 0,0 0 1 0 0,0-2 0 0 0,-1 2 0 0 0,1-13-1 0 0,-3 17-45 0 0,0 0 0 0 0,0-1 0 0 0,-1 2 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,-3-5 0 0 0,3 5-246 0 0,1 0 1 0 0,0 1-1 0 0,-1-1 1 0 0,1 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 1 0 0,0 0-1 0 0,0-8 1 0 0,2 11-100 0 0,-1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,4-4-1057 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="495.13">2036 75 13359 0 0,'0'0'85'0'0,"0"-1"-1"0"0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 1 0 0,-1 1-1 0 0,1-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 1 0 0,-1-1-1 0 0,1 1 0 0 0,0-1 0 0 0,-1 1 1 0 0,0-2-1 0 0,1 2 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1-1 0 0 0,0 1 0 0 0,1 0 0 0 0,0 0 1 0 0,-1-1-1 0 0,0 1 0 0 0,-1 0 48 0 0,1-1-1 0 0,0 1 1 0 0,-1 0-1 0 0,1 0 1 0 0,-1-1-1 0 0,1 1 1 0 0,0 0-1 0 0,-1 0 1 0 0,1 1-1 0 0,-1-1 1 0 0,-1 0-1 0 0,-6 7 157 0 0,-1 0-1 0 0,2-1 1 0 0,-1 1-1 0 0,0 1 1 0 0,1 0 0 0 0,-10 13-1 0 0,-18 17 344 0 0,14-21-252 0 0,11-9-159 0 0,1 1-1 0 0,0 0 1 0 0,1 0 0 0 0,-16 21 0 0 0,23-28-207 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,1 1 0 0 0,1 1 0 0 0,1 2-141 0 0,-1-2 1 0 0,1 0-1 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 1 0 0,1 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,0-1-1 0 0,0 1 0 0 0,-1-1 0 0 0,2 0 1 0 0,-1-1-1 0 0,1 1 0 0 0,-1 0 0 0 0,5-1 1 0 0,0 0-193 0 0,-2 0 0 0 0,1-1 0 0 0,0 0-1 0 0,-1-1 1 0 0,1 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,1-1 0 0 0,10-4 0 0 0,-13 4 458 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0-1 0 0 0,-2 1 0 0 0,2-1 0 0 0,-1 0 0 0 0,0-1 0 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,6-10-1 0 0,-4 5 645 0 0,-2 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0-1 0 0 0,0 1-1 0 0,-2 0 1 0 0,2-14 0 0 0,-4 20-587 0 0,0 0-1 0 0,0 0 1 0 0,0 0 0 0 0,-1 1-1 0 0,1-1 1 0 0,-1-1 0 0 0,0 2-1 0 0,-3-8 1 0 0,1 6-178 0 0,2 0 0 0 0,-1 0 0 0 0,-1-14 0 0 0,3 20-108 0 0,0-1 0 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,1 0 0 0 0,-1 1-1 0 0,0-1 1 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,1-1-1 0 0,-1 1 1 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1-1-1 0 0,-1 1 1 0 0,1 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,10 3-1220 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="839.72">2424 13 15431 0 0,'0'-1'102'0'0,"-1"0"-1"0"0,0 1 0 0 0,0 0 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 0 0 0,0 0 1 0 0,-2 1-1 0 0,-18 10 954 0 0,12-4-752 0 0,1 1 1 0 0,-1-1-1 0 0,2 1 1 0 0,-1 1 0 0 0,1 0-1 0 0,-7 11 1 0 0,-3 4-131 0 0,-16 13 264 0 0,-5 7 387 0 0,37-41-812 0 0,-1-1-1 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,1 1 1 0 0,-1-1-1 0 0,1 1 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 2-1 0 0,0-2 0 0 0,1 0 1 0 0,-1 1-1 0 0,1-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 1 0 0,0 0-1 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 1 0 0,3 3-1 0 0,-2-1-102 0 0,1 0 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 0 0 0 0,1 1 0 0 0,6-1 0 0 0,-3-1-99 0 0,1 0 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 1 0 0,1-1-1 0 0,-2 1 0 0 0,2-2 0 0 0,-2 1 0 0 0,1-1 0 0 0,11-9 0 0 0,-14 9 569 0 0,0 1 0 0 0,-2-2 0 0 0,2 1 0 0 0,-1 0 1 0 0,0-1-1 0 0,0 0 0 0 0,-2 0 0 0 0,1-2 0 0 0,0 2 0 0 0,0-1 0 0 0,0 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,-2-1 0 0 0,2 0 0 0 0,-1 0 0 0 0,2-8 0 0 0,-3 6-10 0 0,-1-1-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 1 1 0 0,-1 0-1 0 0,-2-14 1 0 0,-2-24-85 0 0,5 20-1241 0 0,4 9-2414 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="-1929.66">375 45 10711 0 0,'0'0'157'0'0,"-1"-1"0"0"0,1 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1-1 0 0,1 0 1 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1-1 0 0,-1-1 1 0 0,1 1 0 0 0,-1-2 0 0 0,1 2-101 0 0,0-1 0 0 0,0 1-1 0 0,-1-1 1 0 0,1 1 0 0 0,0 0-1 0 0,0-1 1 0 0,-1 1 0 0 0,1-1-1 0 0,0 1 1 0 0,-1 0 0 0 0,1-1-1 0 0,0 1 1 0 0,0 0 0 0 0,0-1-1 0 0,-1 1 1 0 0,1 0 0 0 0,-1 0-1 0 0,1-1 1 0 0,0 1 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,-1-1-1 0 0,1 1 1 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 1 0 0 0,-1-1-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 1 0 0 0,-3 1 101 0 0,0 1 0 0 0,1-1 1 0 0,-1 1-1 0 0,0 1 1 0 0,0-1-1 0 0,0 0 0 0 0,1 1 1 0 0,0 0-1 0 0,1 0 1 0 0,-4 5-1 0 0,-3 6 227 0 0,-10 26 0 0 0,0 1-110 0 0,12-29-142 0 0,0 1-1 0 0,1-1 1 0 0,-6 21 0 0 0,10-29-74 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,4 10 0 0 0,-4-10-59 0 0,1 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,2 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,-1 1 0 0 0,2-1 0 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,0 0 0 0 0,1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,7-5 0 0 0,-5 4-18 0 0,1-2 0 0 0,-1 1 0 0 0,1-1 0 0 0,-2 0 1 0 0,1 0-1 0 0,0 0 0 0 0,0-1 0 0 0,-1-1 1 0 0,0 1-1 0 0,-1 0 0 0 0,7-12 0 0 0,-5 6 327 0 0,-1 1 0 0 0,-1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1-21 0 0 0,-4 29-191 0 0,0 1-1 0 0,-1-1 1 0 0,1 0-1 0 0,0 1 1 0 0,-1 0 0 0 0,1-1-1 0 0,-1 1 1 0 0,0-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1 0 0 0,0 0-1 0 0,-1 0 1 0 0,-1-4-1 0 0,-3-1-42 0 0,0 1-1 0 0,-1 0 0 0 0,-6-6 0 0 0,-9-8-4019 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="-1265.91">729 70 11167 0 0,'-10'-23'2680'0'0,"9"22"-2647"0"0,0 1-1 0 0,0-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,0 1-1 0 0,1-1 1 0 0,-1 1 0 0 0,0 0-1 0 0,1-1 1 0 0,-1 1-1 0 0,0 0 1 0 0,0 0-1 0 0,0-1 1 0 0,0 1-1 0 0,0 0 1 0 0,0 0-1 0 0,-1 0 1 0 0,-8-1 877 0 0,9 1-805 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 1-1 0 0,0-1 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 1 0 0,0 0-1 0 0,1 1 1 0 0,-1-1-1 0 0,0 1 1 0 0,0-1-1 0 0,1 1 1 0 0,-1 0-1 0 0,0-1 1 0 0,1 1-1 0 0,-1 0 1 0 0,1-1-1 0 0,-1 1 1 0 0,0 1-1 0 0,-13 24 626 0 0,12-22-490 0 0,-19 46 496 0 0,14-33-537 0 0,0 0 1 0 0,-11 19 0 0 0,14-31-113 0 0,2 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 2 0 0 0,1-1 0 0 0,-1 8 0 0 0,1-11-87 0 0,1 1 1 0 0,0 0 0 0 0,1-1 0 0 0,-1 2-1 0 0,1-1 1 0 0,-1-1 0 0 0,1 1 0 0 0,0-1-1 0 0,0 1 1 0 0,1-1 0 0 0,-1 1 0 0 0,1-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0-1 0 0,1 4 1 0 0,1-2-1 0 0,-1-1-1 0 0,1 0 1 0 0,0 0-1 0 0,0-1 1 0 0,-1 1 0 0 0,1-1-1 0 0,1 0 1 0 0,8 5-1 0 0,-12-7-7 0 0,2 0 0 0 0,0 1-1 0 0,-1-2 1 0 0,1 1 0 0 0,0-1-1 0 0,0 1 1 0 0,-1-1-1 0 0,1 0 1 0 0,-1 0 0 0 0,1-1-1 0 0,0 1 1 0 0,-1 0 0 0 0,1-1-1 0 0,0-1 1 0 0,-1 2 0 0 0,1-1-1 0 0,0 0 1 0 0,3-3 0 0 0,3-1-4 0 0,0 0 0 0 0,-1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,1-1 0 0 0,-1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-2-2 0 0 0,0 1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1-2 0 0 0,-2 1 0 0 0,4-13 0 0 0,-5 20 79 0 0,0 0 1 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,-1 1 0 0 0,1 0 0 0 0,1 0 0 0 0,-2 0 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 1 1 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,-1 0 0 0 0,-1-2 0 0 0,-11-5-188 0 0,-8-6 247 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="-742.93">1061 50 13359 0 0,'0'-2'140'0'0,"0"0"-1"0"0,-1 0 1 0 0,0 0 0 0 0,1 1-1 0 0,-1-1 1 0 0,0 0-1 0 0,0 0 1 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,-3-2-1 0 0,4 4-92 0 0,-1-1-1 0 0,1 1 1 0 0,-1-1 0 0 0,1 1-1 0 0,-1-2 1 0 0,1 2 0 0 0,-1 0-1 0 0,1-1 1 0 0,-1 1-1 0 0,0 0 1 0 0,1 0 0 0 0,-1-1-1 0 0,1 1 1 0 0,0 0 0 0 0,-1 0-1 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,1 0-1 0 0,-1 1 1 0 0,1-1-1 0 0,-1 0 1 0 0,0 1 0 0 0,1-1-1 0 0,-1 0 1 0 0,1 2 0 0 0,-1-2-1 0 0,1 0 1 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,0 0 0 0 0,-5 8 409 0 0,2-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,-5 17 0 0 0,-4 6 545 0 0,-11 10-152 0 0,18-33-626 0 0,2 1 0 0 0,-1-1 0 0 0,-8 21 0 0 0,13-27-207 0 0,0 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 0 0 0,1 1 0 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,-1-1 0 0 0,2 0 1 0 0,-1 0-1 0 0,0 1 0 0 0,0-2 0 0 0,3 4 0 0 0,-1-3-25 0 0,-1 0 0 0 0,0 0-1 0 0,0-1 1 0 0,1 1 0 0 0,-1-1-1 0 0,0 1 1 0 0,1-1 0 0 0,-1 0-1 0 0,1 0 1 0 0,0-1 0 0 0,-1 1-1 0 0,1-1 1 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,1 0 0 0 0,0-1-1 0 0,0 0 1 0 0,-2 1 0 0 0,2-1-1 0 0,0-1 1 0 0,-1 1 0 0 0,5-2 0 0 0,-4-1 82 0 0,2 1 1 0 0,-1-1 0 0 0,0-1-1 0 0,0 1 1 0 0,-2 0 0 0 0,2-1 0 0 0,-1-1-1 0 0,0 1 1 0 0,0 0 0 0 0,-1-1-1 0 0,0 1 1 0 0,0-1 0 0 0,-1 0 0 0 0,1 0-1 0 0,-1-1 1 0 0,3-8 0 0 0,-4 8 10 0 0,1 0 1 0 0,-1-2 0 0 0,0 2-1 0 0,-1 0 1 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,-1-1-1 0 0,0 0 1 0 0,-1 1 0 0 0,1 0-1 0 0,-1 0 1 0 0,-1 0 0 0 0,-3-8-1 0 0,5 12-143 0 0,-6-16-1470 0 0,6 18 1477 0 0,1 1 0 0 0,0-1-1 0 0,0 1 1 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1-1 0 0,0 1 1 0 0,0-1 0 0 0,0 1 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 0 0 0,0 1-1 0 0,0-2 1 0 0,1 2 0 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1-1 0 0,1-1 1 0 0,-1 1 0 0 0,0 0 0 0 0,1-1 0 0 0,5 2-1131 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1800.81">49 372 16007 0 0,'-3'-5'352'0'0,"3"9"64"0"0,1 0 24 0 0,-1-1 16 0 0,0 1-360 0 0,0 0-96 0 0,-1 1 0 0 0,0 3 0 0 0,-2 7 424 0 0,-1 2 72 0 0,1 0 16 0 0,-4 1 0 0 0,-1-2-1184 0 0,2-2-224 0 0,-1-1-56 0 0,0-2-8 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2442.66">1333 358 20271 0 0,'4'0'448'0'0,"-2"1"88"0"0,-2 2 16 0 0,-1-1 24 0 0,1-1-464 0 0,-1 2-112 0 0,-1 0 0 0 0,-2 3 0 0 0,-4 3 536 0 0,-1 2 80 0 0,-3 2 24 0 0,-2 1 0 0 0,1-2-1256 0 0,-1-1-248 0 0,-1 1-56 0 0,5 1-8 0 0</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -7394,11 +7436,11 @@
       <inkml:brushProperty name="color" value="#E71224"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">4 82 8287 0 0,'-4'-4'3425'0'0,"4"4"-3349"0"0,5-9 2629 0 0,11-11 538 0 0,-13 18-2837 0 0,0-2-279 0 0,0 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,1 1-1 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 0 0 0,1 0 0 0 0,6 0 0 0 0,-9 1-122 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,0 0-1 0 0,0 0 1 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1-1 0 0,1 0 1 0 0,-1 1 0 0 0,1 0 0 0 0,-1-1-1 0 0,2 4 1 0 0,-2-3 1 0 0,1 0 1 0 0,-1 1-1 0 0,0-1 0 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,-1 1 0 0 0,1 0 1 0 0,-1-1-1 0 0,1 1 0 0 0,-1 0 0 0 0,0-1 1 0 0,0 1-1 0 0,-1 3 0 0 0,-3 9-63 0 0,-2 0 0 0 0,1-1 0 0 0,-2 0-1 0 0,0 0 1 0 0,-17 25 0 0 0,15-25-4 0 0,0 1 0 0 0,1 0 0 0 0,0 0 0 0 0,-9 28 0 0 0,15-36 90 0 0,0 1-1 0 0,1-1 1 0 0,0 1 0 0 0,0 0-1 0 0,0 0 1 0 0,1-1-1 0 0,1 10 1 0 0,-1-15 205 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1-1 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,3 1 0 0 0,0 0-504 0 0,-1 0-1 0 0,0-1 1 0 0,0 0-1 0 0,1 0 1 0 0,-1 0-1 0 0,0-1 1 0 0,1 1-1 0 0,-1-1 1 0 0,0 0-1 0 0,5-2 1 0 0,15-3-3438 0 0,-6 4 1886 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="386.22">477 31 12551 0 0,'-2'-1'1766'0'0,"6"2"133"0"0,10 7 456 0 0,-10-4-2300 0 0,-1 1 1 0 0,1-1-1 0 0,-1 1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,0 1 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0-1 1 0 0,0 1-1 0 0,-1 10 0 0 0,0-5 112 0 0,-1 0 0 0 0,0 0 0 0 0,0 0 1 0 0,-2 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,-6 12 0 0 0,6-16-267 0 0,-2 6 443 0 0,0 0 1 0 0,-5 20-1 0 0,9-30-587 0 0,1 0-1 0 0,-1 1 1 0 0,1-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,1 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,2 2 0 0 0,0-1-1131 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="621.15">542 52 13935 0 0,'0'0'90'0'0,"-1"0"-1"0"0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0-1 1 0 0,1 1-1 0 0,-1 0 0 0 0,1 0 1 0 0,-1-1-1 0 0,1 1 0 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,-1-1 0 0 0,1 1 1 0 0,0-1-1 0 0,-1 1 0 0 0,1-1 1 0 0,0 0 28 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 1 0 0,1-1-1 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,0-1 1 0 0,1 1-1 0 0,-1 0 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,14-8 2230 0 0,-6 5-2418 0 0,79-11 1514 0 0,-47 9-2943 0 0,0-2-6430 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="915.24">547 224 17279 0 0,'21'4'4783'0'0,"19"-2"-3283"0"0,-20-3-1161 0 0,32-6 1 0 0,-32 4-870 0 0,30-1 1 0 0,-40 6-1448 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1154.09">493 412 17047 0 0,'3'2'423'0'0,"1"0"0"0"0,-1 0-1 0 0,1-1 1 0 0,0 1 0 0 0,-1-1-1 0 0,1 0 1 0 0,0-1 0 0 0,0 1-1 0 0,0 0 1 0 0,0-1 0 0 0,5 0-1 0 0,6 1 323 0 0,19 4 940 0 0,46-1-1 0 0,-65-4-2139 0 0,0-1 0 0 0,0 0-1 0 0,0-2 1 0 0,0 0 0 0 0,22-7 0 0 0,-25 5-536 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">3 84 8287 0 0,'-3'-4'3425'0'0,"3"4"-3349"0"0,4-9 2629 0 0,10-12 538 0 0,-11 19-2837 0 0,-1-2-279 0 0,1 1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,1-1 0 0 0,-1 1 1 0 0,1 1-1 0 0,-1-1 0 0 0,1 1 0 0 0,0 0 0 0 0,5 0 0 0 0,-7 1-122 0 0,0 0 0 0 0,0 1-1 0 0,-1-1 1 0 0,1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 1 0 0 0,1 0 0 0 0,-1-1-1 0 0,0 0 1 0 0,0 1 0 0 0,1 0 0 0 0,-1-1-1 0 0,1 4 1 0 0,-1-3 1 0 0,1 0 1 0 0,-1 1-1 0 0,0-1 0 0 0,0 1 0 0 0,0-1 1 0 0,-1 1-1 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 1 0 0,0 1-1 0 0,-1 3 0 0 0,-2 9-63 0 0,-3 1 0 0 0,2-2 0 0 0,-2 0-1 0 0,0 1 1 0 0,-15 25 0 0 0,13-26-4 0 0,1 2 0 0 0,0-1 0 0 0,0 0 0 0 0,-8 29 0 0 0,13-36 90 0 0,0 0-1 0 0,2-1 1 0 0,-1 1 0 0 0,0 0-1 0 0,0 1 1 0 0,1-2-1 0 0,1 10 1 0 0,-1-15 205 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 1 0 0,0 0-1 0 0,1 1 0 0 0,0-1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0-1 1 0 0,1 1-1 0 0,0-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0-1 0 0 0,2 1 0 0 0,0 0-504 0 0,0 0-1 0 0,-1-1 1 0 0,1 0-1 0 0,0 0 1 0 0,0 0-1 0 0,-1-1 1 0 0,2 1-1 0 0,-2-1 1 0 0,0 0-1 0 0,5-2 1 0 0,13-3-3438 0 0,-5 4 1886 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="386.22">414 32 12551 0 0,'-2'-1'1766'0'0,"5"2"133"0"0,9 7 456 0 0,-8-4-2300 0 0,-1 1 1 0 0,0-1-1 0 0,0 1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,-2-1 0 0 0,2 2 0 0 0,-1-1 0 0 0,0-1 1 0 0,0 1-1 0 0,-1 10 0 0 0,0-4 112 0 0,-1-1 0 0 0,0 0 0 0 0,0 0 1 0 0,-1 1-1 0 0,0-1 0 0 0,-1 0 0 0 0,-5 13 0 0 0,6-17-267 0 0,-2 6 443 0 0,-1 1 1 0 0,-4 20-1 0 0,9-31-587 0 0,0 0-1 0 0,-1 1 1 0 0,1-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,1-1 0 0 0,0 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,1 2 0 0 0,1-1-1131 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="621.15">470 53 13935 0 0,'0'0'90'0'0,"-1"0"-1"0"0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,-1 0 0 0 0,0-1 1 0 0,1 1-1 0 0,0 0 0 0 0,0 0 1 0 0,-1-1-1 0 0,1 1 0 0 0,-1-1 1 0 0,1 1-1 0 0,0 0 0 0 0,-1-1 1 0 0,1 1-1 0 0,-1-1 0 0 0,1 1 1 0 0,0-1-1 0 0,-1 1 0 0 0,1-1 1 0 0,0 0 28 0 0,0 1 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 1 0 0,1-1-1 0 0,-1 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,0-1 1 0 0,1 1-1 0 0,-1 0 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,12-8 2230 0 0,-6 5-2418 0 0,70-12 1514 0 0,-42 10-2943 0 0,1-2-6430 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="915.24">474 230 17279 0 0,'18'4'4783'0'0,"17"-2"-3283"0"0,-18-3-1161 0 0,29-6 1 0 0,-29 4-870 0 0,26-2 1 0 0,-34 7-1448 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1154.08">427 422 17047 0 0,'3'2'423'0'0,"1"0"0"0"0,-2 1-1 0 0,2-2 1 0 0,-1 1 0 0 0,0-1-1 0 0,0 0 1 0 0,1-1 0 0 0,-1 1-1 0 0,1 0 1 0 0,-1-1 0 0 0,5 0-1 0 0,5 1 323 0 0,16 4 940 0 0,41-1-1 0 0,-57-4-2139 0 0,0-1 0 0 0,0 0-1 0 0,0-2 1 0 0,0 0 0 0 0,19-7 0 0 0,-22 4-536 0 0</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -7430,10 +7472,10 @@
       <inkml:brushProperty name="color" value="#E71224"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 310 16351 0 0,'22'6'5823'0'0,"-7"-5"-5317"0"0,-1-2 1 0 0,1 0-1 0 0,0 0 1 0 0,24-6-1 0 0,4-1-840 0 0,6 2-486 0 0,2 0-3769 0 0,-35 4-2447 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="311.04">80 131 14743 0 0,'0'-1'69'0'0,"0"1"0"0"0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 1 0 0,0 0-1 0 0,1-1 0 0 0,-1 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 1 0 0,1 0-1 0 0,0-1 0 0 0,0 1 95 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,1 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,1 0-1 0 0,1 1 131 0 0,0 0-1 0 0,-1 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,1 1 0 0 0,-1-1 1 0 0,3 5-1 0 0,-2-2-121 0 0,-1 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 1 0 0 0,0-1-1 0 0,0 1 1 0 0,-1-1 0 0 0,0 1-1 0 0,0 0 1 0 0,-1 0 0 0 0,0-1-1 0 0,1 1 1 0 0,-2 0 0 0 0,0 7-1 0 0,-3 5 89 0 0,0 0-1 0 0,-1-1 0 0 0,-9 21 0 0 0,4-2-912 0 0,8-11-2724 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1165.48">777 49 16007 0 0,'-1'-3'334'0'0,"-1"0"-1"0"0,1 1 0 0 0,0-1 1 0 0,-1 1-1 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,-3-4 0 0 0,4 6-235 0 0,0-1-1 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,0 0 0 0 0,1 0 1 0 0,-1-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,1-1 0 0 0,-1 1 1 0 0,-1 1-1 0 0,-3 2-46 0 0,1 0-1 0 0,0 0 1 0 0,0 1-1 0 0,0 0 1 0 0,0-1-1 0 0,1 1 1 0 0,0 1-1 0 0,0-1 1 0 0,0 0-1 0 0,-3 12 1 0 0,-2 7 271 0 0,-6 29 0 0 0,14-52-319 0 0,-7 29 307 0 0,-6 61 1 0 0,13-88-325 0 0,0 0-1 0 0,0 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 0 0 0 0,1 0 1 0 0,0 0-1 0 0,0-1 1 0 0,-1 1-1 0 0,2 0 0 0 0,-1-1 1 0 0,0 0-1 0 0,0 1 0 0 0,1-1 1 0 0,-1 0-1 0 0,1 0 0 0 0,0-1 1 0 0,-1 1-1 0 0,1 0 1 0 0,0-1-1 0 0,0 0 0 0 0,0 1 1 0 0,0-1-1 0 0,1-1 0 0 0,-1 1 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 1 0 0,1-1-1 0 0,-1 0 1 0 0,0 0-1 0 0,0 0 0 0 0,1-1 1 0 0,-1 1-1 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,5-3-1 0 0,5-4-229 0 0,0 0-1 0 0,11-11 1 0 0,-19 15 253 0 0,0 0 1 0 0,0-1 0 0 0,-1 0-1 0 0,1 0 1 0 0,-1 0 0 0 0,0 0-1 0 0,4-8 1 0 0,-7 8 73 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 0 0 0 0,-1 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,-1-1 0 0 0,-3-8 0 0 0,1 4 342 0 0,-1 0-1 0 0,0 1 1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,-9-12-1 0 0,7 13-545 0 0,-8-9-770 0 0,15 15 719 0 0,-1 1 0 0 0,1-1-1 0 0,-1 1 1 0 0,1-1 0 0 0,-1 1-1 0 0,1-1 1 0 0,-1 0 0 0 0,1 1-1 0 0,0-1 1 0 0,0 0 0 0 0,-1 1-1 0 0,1-1 1 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0-2 0 0 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1754.07">1125 49 15775 0 0,'-5'-12'1505'0'0,"3"8"-922"0"0,1 0-1 0 0,-1 1 1 0 0,0-1 0 0 0,0 0 0 0 0,-1 1 0 0 0,-4-6 0 0 0,7 8-562 0 0,-1 0 1 0 0,0 1-1 0 0,0-1 0 0 0,1 1 1 0 0,-1 0-1 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 1 0 0,0-1-1 0 0,0 1 0 0 0,0 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,1 0-1 0 0,-1 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 1 0 0,1 1-1 0 0,-1-1 0 0 0,0 1 1 0 0,0-1-1 0 0,1 1 0 0 0,-1-1 1 0 0,0 1-1 0 0,1 0 0 0 0,-1-1 1 0 0,0 2-1 0 0,-6 5 139 0 0,0 1 0 0 0,0-1 0 0 0,1 1 0 0 0,0 1 0 0 0,1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,-5 14 0 0 0,8-18-55 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,3 5 0 0 0,-4-8-62 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,1 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,4 1 0 0 0,-4-2-53 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 1 0 0,2-2-1 0 0,1 0-155 0 0,0-1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,-1-1 0 0 0,1 1 0 0 0,-1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,3-7 0 0 0,1-8-306 0 0,0-1 0 0 0,-2 0 0 0 0,0 0-1 0 0,3-31 1 0 0,-6 47 1403 0 0,2 15 367 0 0,-2-4-1161 0 0,1 8-3 0 0,1-1-1 0 0,-2 0 1 0 0,0 1-1 0 0,0 0 0 0 0,-1 17 1 0 0,-7 70 160 0 0,0-18-109 0 0,6-36 5 0 0,2 0-1 0 0,10 61 0 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 316 16351 0 0,'20'6'5823'0'0,"-6"-5"-5317"0"0,-2-2 1 0 0,2 0-1 0 0,0 0 1 0 0,21-6-1 0 0,4-1-840 0 0,6 2-486 0 0,1-1-3769 0 0,-31 5-2447 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="311.04">73 134 14743 0 0,'0'-2'69'0'0,"0"2"0"0"0,0-1 1 0 0,0 1-1 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,0-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,0 0 0 0 0,1-1 0 0 0,-1 1 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 0 0 0,1 0 0 0 0,-1 0 0 0 0,0-1 0 0 0,1 1 0 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,0 0 1 0 0,1 0-1 0 0,0-1 0 0 0,0 1 95 0 0,0 1 0 0 0,0-1-1 0 0,0 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,0-1 0 0 0,0 1 0 0 0,1 0-1 0 0,1 1 131 0 0,-1 1-1 0 0,0-1 0 0 0,1 0 1 0 0,-1 0-1 0 0,0 1 0 0 0,0-1 1 0 0,3 5-1 0 0,-3-2-121 0 0,0 0 0 0 0,1 0-1 0 0,-1 0 1 0 0,0 1 0 0 0,-1-1-1 0 0,1 2 1 0 0,-1-2 0 0 0,0 1-1 0 0,0 0 1 0 0,-1 0 0 0 0,0-1-1 0 0,1 1 1 0 0,-2 0 0 0 0,0 8-1 0 0,-3 4 89 0 0,1 0-1 0 0,-2 0 0 0 0,-7 20 0 0 0,2-1-912 0 0,9-12-2724 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1165.48">707 50 16007 0 0,'-1'-3'334'0'0,"0"0"-1"0"0,0 1 0 0 0,0-1 1 0 0,-1 1-1 0 0,0-1 0 0 0,0 1 1 0 0,1 0-1 0 0,-4-5 0 0 0,4 7-235 0 0,0-1-1 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,1 0 0 0 0,0 0 1 0 0,-1-1-1 0 0,0 1 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,0 0 1 0 0,1 1-1 0 0,-1-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 1 1 0 0,0-1-1 0 0,0 1 0 0 0,0-1 1 0 0,0 1-1 0 0,1-1 0 0 0,-1 1 1 0 0,0 2-1 0 0,-4 1-46 0 0,1 0-1 0 0,1 0 1 0 0,-1 1-1 0 0,0 0 1 0 0,1-1-1 0 0,0 1 1 0 0,0 1-1 0 0,1-1 1 0 0,-1 0-1 0 0,-3 13 1 0 0,-1 6 271 0 0,-6 30 0 0 0,13-53-319 0 0,-6 30 307 0 0,-6 62 1 0 0,12-90-325 0 0,0 0-1 0 0,0 0 0 0 0,1 1 1 0 0,-1-1-1 0 0,1 0 0 0 0,-1 0 1 0 0,1 0-1 0 0,0 0 0 0 0,1 0 1 0 0,-2 0-1 0 0,1 0 0 0 0,1 0 1 0 0,0 0-1 0 0,0-1 1 0 0,-1 1-1 0 0,2 1 0 0 0,-2-2 1 0 0,1 0-1 0 0,0 1 0 0 0,1-1 1 0 0,-1 0-1 0 0,0 0 0 0 0,1-1 1 0 0,-1 1-1 0 0,1 0 1 0 0,-1-1-1 0 0,1 0 0 0 0,0 1 1 0 0,-1-1-1 0 0,2-1 0 0 0,-1 1 1 0 0,0 0-1 0 0,-1-1 0 0 0,1 1 1 0 0,1-1-1 0 0,-2 0 1 0 0,1 0-1 0 0,0 0 0 0 0,1-1 1 0 0,-2 1-1 0 0,1-1 0 0 0,0 0 1 0 0,-1 0-1 0 0,1 0 0 0 0,0 0 1 0 0,4-3-1 0 0,5-4-229 0 0,0 0-1 0 0,10-12 1 0 0,-18 16 253 0 0,1 0 1 0 0,-1-1 0 0 0,0 0-1 0 0,1 0 1 0 0,-2 0 0 0 0,1 0-1 0 0,3-9 1 0 0,-6 9 73 0 0,1 1 0 0 0,-1-1 0 0 0,0 1 0 0 0,0-1 0 0 0,-1 0 0 0 0,0 1 0 0 0,0-1-1 0 0,0-1 1 0 0,0 2 0 0 0,0-1 0 0 0,0 0 0 0 0,0 1 0 0 0,-1-1 0 0 0,-3-8 0 0 0,1 4 342 0 0,0-1-1 0 0,-1 2 1 0 0,0 0 0 0 0,1 0 0 0 0,-2 0 0 0 0,-8-13-1 0 0,7 14-545 0 0,-8-9-770 0 0,14 15 719 0 0,-1 1 0 0 0,1-1-1 0 0,0 1 1 0 0,0-1 0 0 0,-1 1-1 0 0,1-1 1 0 0,-1 0 0 0 0,1 1-1 0 0,0-1 1 0 0,0 0 0 0 0,-1 1-1 0 0,1-1 1 0 0,0 0 0 0 0,0 1-1 0 0,0-1 1 0 0,0 0 0 0 0,0 0-1 0 0,0 1 1 0 0,0-2 0 0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1754.07">1024 50 15775 0 0,'-4'-12'1505'0'0,"2"8"-922"0"0,1 0-1 0 0,-1 0 1 0 0,0 0 0 0 0,0 0 0 0 0,0 1 0 0 0,-5-6 0 0 0,7 8-562 0 0,-1 0 1 0 0,1 1-1 0 0,-1-1 0 0 0,1 1 1 0 0,-1 0-1 0 0,0-1 0 0 0,0 1 1 0 0,0 0-1 0 0,0-1 0 0 0,0 1 1 0 0,1 0-1 0 0,-1 0 0 0 0,0 0 1 0 0,0-1-1 0 0,1 1 0 0 0,-1 0 1 0 0,0 1-1 0 0,0-1 0 0 0,0 0 1 0 0,0 0-1 0 0,0 0 1 0 0,1 0-1 0 0,-1 1 0 0 0,0-1 1 0 0,0 0-1 0 0,0 1 0 0 0,0-1 1 0 0,1 1-1 0 0,0-1 0 0 0,-1 1 1 0 0,0-1-1 0 0,1 1 0 0 0,-1-1 1 0 0,0 1-1 0 0,1 0 0 0 0,-1-1 1 0 0,0 2-1 0 0,-5 5 139 0 0,-1 1 0 0 0,1 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,2-1 0 0 0,-1 1 0 0 0,0 0 0 0 0,-4 15 0 0 0,8-19-55 0 0,-1 0 0 0 0,1 0 0 0 0,-1 0 0 0 0,1 0 0 0 0,0 0 0 0 0,1 1 0 0 0,-1 0 0 0 0,1-1 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,1 0 0 0 0,-1 1 0 0 0,1-1 0 0 0,2 5 0 0 0,-3-8-62 0 0,0 0 0 0 0,0 0 0 0 0,0 0 0 0 0,1 0 0 0 0,-2-1 0 0 0,1 1 0 0 0,1 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,0 0 0 0 0,-1 0 0 0 0,0 1 0 0 0,1-1 0 0 0,0 0 0 0 0,3 1 0 0 0,-3-2-53 0 0,0 0 1 0 0,0 0-1 0 0,0 0 0 0 0,-1 0 0 0 0,0 0 0 0 0,1 0 0 0 0,0 0 0 0 0,0 0 0 0 0,0-1 0 0 0,-1 1 0 0 0,1-1 0 0 0,-1 0 0 0 0,1 1 0 0 0,0-1 1 0 0,1-2-1 0 0,2 0-155 0 0,0-1 0 0 0,-2 0 0 0 0,2 0 0 0 0,-2 0 0 0 0,1 0 0 0 0,-1-1 0 0 0,0 1 0 0 0,0-2 0 0 0,0 1 0 0 0,0 0 0 0 0,2-7 0 0 0,1-8-306 0 0,1-2 0 0 0,-3 1 0 0 0,1-1-1 0 0,2-31 1 0 0,-5 48 1403 0 0,2 16 367 0 0,-2-5-1161 0 0,0 8-3 0 0,2-1-1 0 0,-2 0 1 0 0,0 2-1 0 0,-1-1 0 0 0,0 18 1 0 0,-6 71 160 0 0,-1-19-109 0 0,6-36 5 0 0,2 0-1 0 0,9 62 0 0 0</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -7485,13 +7527,13 @@
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{249CB777-9A5F-4021-84E0-B3256ADAD6D3}" name="Year (Since 1994)" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{0D9AE47D-B0C0-474F-AD29-87EE0219A136}" name="Subscribers (millions)" dataDxfId="3" dataCellStyle="Comma"/>
-    <tableColumn id="4" xr3:uid="{2E42A1D7-31F0-4CBD-B8AD-92DD42230E78}" name="Estimated Subscribers" dataDxfId="0" dataCellStyle="Comma">
+    <tableColumn id="4" xr3:uid="{2E42A1D7-31F0-4CBD-B8AD-92DD42230E78}" name="Estimated Subscribers" dataDxfId="2" dataCellStyle="Comma">
       <calculatedColumnFormula>Table357[[#This Row],[Year (Since 1994)]]*1.116+1.2194</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{D04571DA-69F3-4913-9111-6E9D34198F63}" name=" Error Perentage (EP)" dataDxfId="2">
+    <tableColumn id="3" xr3:uid="{D04571DA-69F3-4913-9111-6E9D34198F63}" name=" Error Perentage (EP)" dataDxfId="1">
       <calculatedColumnFormula>(Table357[[#This Row],[Subscribers (millions)]]-Table357[[#This Row],[Estimated Subscribers]])/Table357[[#This Row],[Subscribers (millions)]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{1C9CDF07-ABBF-4FF1-91F5-E5466F814DB0}" name="Absolute EP (AEP)" dataDxfId="1">
+    <tableColumn id="5" xr3:uid="{1C9CDF07-ABBF-4FF1-91F5-E5466F814DB0}" name="Absolute EP (AEP)" dataDxfId="0">
       <calculatedColumnFormula>ABS(Table357[[#This Row],[ Error Perentage (EP)]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7817,14 +7859,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5A9607E-9A5C-4B27-AFA2-8620C6540D98}">
   <dimension ref="A1:G42"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.1328125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="19.796875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="11.19921875" customWidth="1"/>
+    <col min="1" max="1" width="25.109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="19.77734375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="11.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -7832,7 +7874,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>10</v>
       </c>
@@ -7840,7 +7882,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>20</v>
       </c>
@@ -7848,7 +7890,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>30</v>
       </c>
@@ -7856,7 +7898,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>40</v>
       </c>
@@ -7864,7 +7906,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E23" t="s">
         <v>3</v>
       </c>
@@ -7872,7 +7914,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E24" t="s">
         <v>4</v>
       </c>
@@ -7880,7 +7922,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E26" t="s">
         <v>0</v>
       </c>
@@ -7888,7 +7930,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E27" t="s">
         <v>2</v>
       </c>
@@ -7897,7 +7939,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>2012</v>
       </c>
@@ -7909,7 +7951,7 @@
         <v>27.87</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>2013</v>
       </c>
@@ -7921,7 +7963,7 @@
         <v>29.004000000000001</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>2014</v>
       </c>
@@ -7933,7 +7975,7 @@
         <v>30.138000000000002</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>2015</v>
       </c>
@@ -7945,7 +7987,7 @@
         <v>31.271999999999998</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>2016</v>
       </c>
@@ -7957,7 +7999,7 @@
         <v>32.405999999999999</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
         <v>2012</v>
       </c>
@@ -7965,7 +8007,7 @@
         <v>27.87</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
         <v>2013</v>
       </c>
@@ -7973,7 +8015,7 @@
         <v>29.004000000000001</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>2014</v>
       </c>
@@ -7981,7 +8023,7 @@
         <v>30.138000000000002</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <v>2015</v>
       </c>
@@ -7989,7 +8031,7 @@
         <v>31.271999999999998</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
         <v>2016</v>
       </c>
@@ -8009,19 +8051,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F65FCA1E-5734-4D0D-AF28-2EC54BB91DFC}">
-  <dimension ref="A1:P35"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:B35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.9296875" customWidth="1"/>
-    <col min="2" max="2" width="18.53125" style="5" customWidth="1"/>
+    <col min="1" max="1" width="15.88671875" customWidth="1"/>
+    <col min="2" max="2" width="18.5546875" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
@@ -8029,16 +8071,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>1994</v>
       </c>
       <c r="B4" s="7">
         <v>320000</v>
       </c>
-      <c r="P4" s="8"/>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.45">
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>1995</v>
       </c>
@@ -8046,7 +8087,7 @@
         <v>1200000</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>1996</v>
       </c>
@@ -8054,7 +8095,7 @@
         <v>2300000</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>1997</v>
       </c>
@@ -8062,7 +8103,7 @@
         <v>3301000</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>1998</v>
       </c>
@@ -8070,7 +8111,7 @@
         <v>4458000</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>1999</v>
       </c>
@@ -8078,7 +8119,7 @@
         <v>6679000</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>2000</v>
       </c>
@@ -8086,7 +8127,7 @@
         <v>9554000</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>2001</v>
       </c>
@@ -8094,7 +8135,7 @@
         <v>10218000</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>2002</v>
       </c>
@@ -8102,7 +8143,7 @@
         <v>11181000</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>2003</v>
       </c>
@@ -8110,7 +8151,7 @@
         <v>12290000</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>2004</v>
       </c>
@@ -8118,7 +8159,7 @@
         <v>13000000</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>2005</v>
       </c>
@@ -8126,7 +8167,7 @@
         <v>15000000</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>2006</v>
       </c>
@@ -8134,7 +8175,7 @@
         <v>15950000</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>2007</v>
       </c>
@@ -8142,7 +8183,7 @@
         <v>16830000</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>2008</v>
       </c>
@@ -8150,7 +8191,7 @@
         <v>17620000</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>2009</v>
       </c>
@@ -8158,7 +8199,7 @@
         <v>18081000</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>2010</v>
       </c>
@@ -8166,7 +8207,7 @@
         <v>19200000</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>2012</v>
       </c>
@@ -8174,7 +8215,7 @@
         <v>19900000</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>2014</v>
       </c>
@@ -8182,7 +8223,7 @@
         <v>20265000</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>8</v>
       </c>
@@ -8190,23 +8231,23 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>4</v>
       </c>
-      <c r="B31" s="9">
+      <c r="B31" s="8">
         <v>-2000000000</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>9</v>
       </c>
-      <c r="B34" s="9">
+      <c r="B34" s="8">
         <v>2015</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>10</v>
       </c>
@@ -8226,28 +8267,28 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DDFEA2A-9460-4A6A-8E23-2BD955ED7A3F}">
-  <dimension ref="A1:Q36"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:F36"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.9296875" customWidth="1"/>
-    <col min="2" max="3" width="23.46484375" style="9" customWidth="1"/>
-    <col min="4" max="4" width="34.06640625" customWidth="1"/>
-    <col min="5" max="5" width="20.796875" customWidth="1"/>
+    <col min="1" max="1" width="15.88671875" customWidth="1"/>
+    <col min="2" max="3" width="23.44140625" style="8" customWidth="1"/>
+    <col min="4" max="4" width="34.109375" customWidth="1"/>
+    <col min="5" max="5" width="20.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="10" t="s">
         <v>12</v>
       </c>
       <c r="D3" s="4" t="s">
@@ -8257,14 +8298,14 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>1994</v>
       </c>
-      <c r="B4" s="10">
+      <c r="B4" s="9">
         <v>0.32</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="9">
         <f>Table35[[#This Row],[Year]]*1.116-2224</f>
         <v>1.3040000000000873</v>
       </c>
@@ -8276,16 +8317,15 @@
         <f>ABS(Table35[[#This Row],[ Error Perentage (EP)]])</f>
         <v>3.0750000000002724</v>
       </c>
-      <c r="Q4" s="8"/>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.45">
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>1995</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="9">
         <v>1.2</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="9">
         <f>Table35[[#This Row],[Year]]*1.116-2224</f>
         <v>2.4200000000000728</v>
       </c>
@@ -8298,14 +8338,14 @@
         <v>1.0166666666667274</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>1996</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="9">
         <v>2.2999999999999998</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="9">
         <f>Table35[[#This Row],[Year]]*1.116-2224</f>
         <v>3.5360000000000582</v>
       </c>
@@ -8318,14 +8358,14 @@
         <v>0.53739130434785154</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>1997</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="9">
         <v>3.3010000000000002</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="9">
         <f>Table35[[#This Row],[Year]]*1.116-2224</f>
         <v>4.6520000000000437</v>
       </c>
@@ -8338,14 +8378,14 @@
         <v>0.40926991820661723</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>1998</v>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="9">
         <v>4.4580000000000002</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="9">
         <f>Table35[[#This Row],[Year]]*1.116-2224</f>
         <v>5.7680000000000291</v>
       </c>
@@ -8358,14 +8398,14 @@
         <v>0.29385374607447934</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>1999</v>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="9">
         <v>6.6790000000000003</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="9">
         <f>Table35[[#This Row],[Year]]*1.116-2224</f>
         <v>6.8840000000000146</v>
       </c>
@@ -8378,14 +8418,14 @@
         <v>3.0693217547539193E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>2000</v>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="9">
         <v>9.5540000000000003</v>
       </c>
-      <c r="C10" s="10">
+      <c r="C10" s="9">
         <f>Table35[[#This Row],[Year]]*1.116-2224</f>
         <v>8</v>
       </c>
@@ -8398,14 +8438,14 @@
         <v>0.16265438559765547</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>2001</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="9">
         <v>10.218</v>
       </c>
-      <c r="C11" s="10">
+      <c r="C11" s="9">
         <f>Table35[[#This Row],[Year]]*1.116-2224</f>
         <v>9.1159999999999854</v>
       </c>
@@ -8418,14 +8458,14 @@
         <v>0.10784889410843751</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>2002</v>
       </c>
-      <c r="B12" s="10">
+      <c r="B12" s="9">
         <v>11.180999999999999</v>
       </c>
-      <c r="C12" s="10">
+      <c r="C12" s="9">
         <f>Table35[[#This Row],[Year]]*1.116-2224</f>
         <v>10.232000000000426</v>
       </c>
@@ -8438,14 +8478,14 @@
         <v>8.4876129147623075E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>2003</v>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="9">
         <v>12.29</v>
       </c>
-      <c r="C13" s="10">
+      <c r="C13" s="9">
         <f>Table35[[#This Row],[Year]]*1.116-2224</f>
         <v>11.348000000000411</v>
       </c>
@@ -8458,14 +8498,14 @@
         <v>7.6647681041463633E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>2004</v>
       </c>
-      <c r="B14" s="10">
+      <c r="B14" s="9">
         <v>13</v>
       </c>
-      <c r="C14" s="10">
+      <c r="C14" s="9">
         <f>Table35[[#This Row],[Year]]*1.116-2224</f>
         <v>12.464000000000397</v>
       </c>
@@ -8478,14 +8518,14 @@
         <v>4.1230769230738727E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>2005</v>
       </c>
-      <c r="B15" s="10">
+      <c r="B15" s="9">
         <v>15</v>
       </c>
-      <c r="C15" s="10">
+      <c r="C15" s="9">
         <f>Table35[[#This Row],[Year]]*1.116-2224</f>
         <v>13.580000000000382</v>
       </c>
@@ -8498,14 +8538,14 @@
         <v>9.4666666666641197E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>2006</v>
       </c>
-      <c r="B16" s="10">
+      <c r="B16" s="9">
         <v>15.95</v>
       </c>
-      <c r="C16" s="10">
+      <c r="C16" s="9">
         <f>Table35[[#This Row],[Year]]*1.116-2224</f>
         <v>14.696000000000367</v>
       </c>
@@ -8518,14 +8558,14 @@
         <v>7.8620689655149331E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>2007</v>
       </c>
-      <c r="B17" s="10">
+      <c r="B17" s="9">
         <v>16.829999999999998</v>
       </c>
-      <c r="C17" s="10">
+      <c r="C17" s="9">
         <f>Table35[[#This Row],[Year]]*1.116-2224</f>
         <v>15.812000000000353</v>
       </c>
@@ -8538,14 +8578,14 @@
         <v>6.0487225193086483E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>2008</v>
       </c>
-      <c r="B18" s="10">
+      <c r="B18" s="9">
         <v>17.62</v>
       </c>
-      <c r="C18" s="10">
+      <c r="C18" s="9">
         <f>Table35[[#This Row],[Year]]*1.116-2224</f>
         <v>16.928000000000338</v>
       </c>
@@ -8558,14 +8598,14 @@
         <v>3.9273552780911616E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>2009</v>
       </c>
-      <c r="B19" s="10">
+      <c r="B19" s="9">
         <v>18.081</v>
       </c>
-      <c r="C19" s="10">
+      <c r="C19" s="9">
         <f>Table35[[#This Row],[Year]]*1.116-2224</f>
         <v>18.044000000000324</v>
       </c>
@@ -8578,14 +8618,14 @@
         <v>2.046346994064252E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>2010</v>
       </c>
-      <c r="B20" s="10">
+      <c r="B20" s="9">
         <v>19.2</v>
       </c>
-      <c r="C20" s="10">
+      <c r="C20" s="9">
         <f>Table35[[#This Row],[Year]]*1.116-2224</f>
         <v>19.160000000000309</v>
       </c>
@@ -8598,14 +8638,14 @@
         <v>2.0833333333171908E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>2012</v>
       </c>
-      <c r="B21" s="10">
+      <c r="B21" s="9">
         <v>19.899999999999999</v>
       </c>
-      <c r="C21" s="10">
+      <c r="C21" s="9">
         <f>Table35[[#This Row],[Year]]*1.116-2224</f>
         <v>21.39200000000028</v>
       </c>
@@ -8618,14 +8658,14 @@
         <v>7.4974874371873446E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>2014</v>
       </c>
-      <c r="B22" s="10">
+      <c r="B22" s="9">
         <v>20.265000000000001</v>
       </c>
-      <c r="C22" s="10">
+      <c r="C22" s="9">
         <f>Table35[[#This Row],[Year]]*1.116-2224</f>
         <v>23.624000000000251</v>
       </c>
@@ -8638,7 +8678,7 @@
         <v>0.16575376264496672</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E25" t="s">
         <v>15</v>
       </c>
@@ -8647,35 +8687,35 @@
         <v>0.33442311387417972</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>8</v>
       </c>
-      <c r="B31" s="9">
+      <c r="B31" s="8">
         <v>1.1160000000000001</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>4</v>
       </c>
-      <c r="B32" s="9">
+      <c r="B32" s="8">
         <v>-2224</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>9</v>
       </c>
-      <c r="B35" s="9">
+      <c r="B35" s="8">
         <v>2015</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>10</v>
       </c>
-      <c r="B36" s="9">
+      <c r="B36" s="8">
         <f xml:space="preserve"> B31*B35+B32</f>
         <v>24.740000000000236</v>
       </c>
@@ -8691,28 +8731,28 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1464571-2D35-49CE-ADA1-D3B0803893CC}">
-  <dimension ref="A1:Q36"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:F36"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.59765625" customWidth="1"/>
-    <col min="2" max="3" width="23.46484375" style="9" customWidth="1"/>
-    <col min="4" max="4" width="34.06640625" customWidth="1"/>
-    <col min="5" max="5" width="20.796875" customWidth="1"/>
+    <col min="1" max="1" width="17.5546875" customWidth="1"/>
+    <col min="2" max="3" width="23.44140625" style="8" customWidth="1"/>
+    <col min="4" max="4" width="34.109375" customWidth="1"/>
+    <col min="5" max="5" width="20.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="10" t="s">
         <v>12</v>
       </c>
       <c r="D3" s="4" t="s">
@@ -8722,14 +8762,14 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>0</v>
       </c>
-      <c r="B4" s="10">
+      <c r="B4" s="9">
         <v>0.32</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="9">
         <f>Table357[[#This Row],[Year (Since 1994)]]*1.116+1.2194</f>
         <v>1.2194</v>
       </c>
@@ -8741,16 +8781,15 @@
         <f>ABS(Table357[[#This Row],[ Error Perentage (EP)]])</f>
         <v>2.8106249999999999</v>
       </c>
-      <c r="Q4" s="8"/>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.45">
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>1</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="9">
         <v>1.2</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="9">
         <f>Table357[[#This Row],[Year (Since 1994)]]*1.116+1.2194</f>
         <v>2.3353999999999999</v>
       </c>
@@ -8763,14 +8802,14 @@
         <v>0.94616666666666671</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>2</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="9">
         <v>2.2999999999999998</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="9">
         <f>Table357[[#This Row],[Year (Since 1994)]]*1.116+1.2194</f>
         <v>3.4514000000000005</v>
       </c>
@@ -8783,14 +8822,14 @@
         <v>0.50060869565217425</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>3</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="9">
         <v>3.3010000000000002</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="9">
         <f>Table357[[#This Row],[Year (Since 1994)]]*1.116+1.2194</f>
         <v>4.5674000000000001</v>
       </c>
@@ -8803,14 +8842,14 @@
         <v>0.38364132081187519</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>4</v>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="9">
         <v>4.4580000000000002</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="9">
         <f>Table357[[#This Row],[Year (Since 1994)]]*1.116+1.2194</f>
         <v>5.6834000000000007</v>
       </c>
@@ -8823,14 +8862,14 @@
         <v>0.27487662628981618</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>5</v>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="9">
         <v>6.6790000000000003</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="9">
         <f>Table357[[#This Row],[Year (Since 1994)]]*1.116+1.2194</f>
         <v>6.7994000000000003</v>
       </c>
@@ -8843,14 +8882,14 @@
         <v>1.8026650696212017E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>6</v>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="9">
         <v>9.5540000000000003</v>
       </c>
-      <c r="C10" s="10">
+      <c r="C10" s="9">
         <f>Table357[[#This Row],[Year (Since 1994)]]*1.116+1.2194</f>
         <v>7.9154000000000009</v>
       </c>
@@ -8863,14 +8902,14 @@
         <v>0.17150931546996015</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>7</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="9">
         <v>10.218</v>
       </c>
-      <c r="C11" s="10">
+      <c r="C11" s="9">
         <f>Table357[[#This Row],[Year (Since 1994)]]*1.116+1.2194</f>
         <v>9.0314000000000014</v>
       </c>
@@ -8883,14 +8922,14 @@
         <v>0.11612840086122515</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>8</v>
       </c>
-      <c r="B12" s="10">
+      <c r="B12" s="9">
         <v>11.180999999999999</v>
       </c>
-      <c r="C12" s="10">
+      <c r="C12" s="9">
         <f>Table357[[#This Row],[Year (Since 1994)]]*1.116+1.2194</f>
         <v>10.147400000000001</v>
       </c>
@@ -8903,14 +8942,14 @@
         <v>9.2442536445756035E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>9</v>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="9">
         <v>12.29</v>
       </c>
-      <c r="C13" s="10">
+      <c r="C13" s="9">
         <f>Table357[[#This Row],[Year (Since 1994)]]*1.116+1.2194</f>
         <v>11.263400000000001</v>
       </c>
@@ -8923,14 +8962,14 @@
         <v>8.353132628152958E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>10</v>
       </c>
-      <c r="B14" s="10">
+      <c r="B14" s="9">
         <v>13</v>
       </c>
-      <c r="C14" s="10">
+      <c r="C14" s="9">
         <f>Table357[[#This Row],[Year (Since 1994)]]*1.116+1.2194</f>
         <v>12.3794</v>
       </c>
@@ -8943,14 +8982,14 @@
         <v>4.7738461538461507E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>11</v>
       </c>
-      <c r="B15" s="10">
+      <c r="B15" s="9">
         <v>15</v>
       </c>
-      <c r="C15" s="10">
+      <c r="C15" s="9">
         <f>Table357[[#This Row],[Year (Since 1994)]]*1.116+1.2194</f>
         <v>13.495400000000002</v>
       </c>
@@ -8963,14 +9002,14 @@
         <v>0.10030666666666654</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>12</v>
       </c>
-      <c r="B16" s="10">
+      <c r="B16" s="9">
         <v>15.95</v>
       </c>
-      <c r="C16" s="10">
+      <c r="C16" s="9">
         <f>Table357[[#This Row],[Year (Since 1994)]]*1.116+1.2194</f>
         <v>14.611400000000001</v>
       </c>
@@ -8983,14 +9022,14 @@
         <v>8.3924764890282E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>13</v>
       </c>
-      <c r="B17" s="10">
+      <c r="B17" s="9">
         <v>16.829999999999998</v>
       </c>
-      <c r="C17" s="10">
+      <c r="C17" s="9">
         <f>Table357[[#This Row],[Year (Since 1994)]]*1.116+1.2194</f>
         <v>15.727400000000001</v>
       </c>
@@ -9003,14 +9042,14 @@
         <v>6.5513963161021815E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>14</v>
       </c>
-      <c r="B18" s="10">
+      <c r="B18" s="9">
         <v>17.62</v>
       </c>
-      <c r="C18" s="10">
+      <c r="C18" s="9">
         <f>Table357[[#This Row],[Year (Since 1994)]]*1.116+1.2194</f>
         <v>16.843400000000003</v>
       </c>
@@ -9023,14 +9062,14 @@
         <v>4.4074914869466422E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>15</v>
       </c>
-      <c r="B19" s="10">
+      <c r="B19" s="9">
         <v>18.081</v>
       </c>
-      <c r="C19" s="10">
+      <c r="C19" s="9">
         <f>Table357[[#This Row],[Year (Since 1994)]]*1.116+1.2194</f>
         <v>17.959400000000002</v>
       </c>
@@ -9043,14 +9082,14 @@
         <v>6.7252917427131943E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>16</v>
       </c>
-      <c r="B20" s="10">
+      <c r="B20" s="9">
         <v>19.2</v>
       </c>
-      <c r="C20" s="10">
+      <c r="C20" s="9">
         <f>Table357[[#This Row],[Year (Since 1994)]]*1.116+1.2194</f>
         <v>19.075400000000002</v>
       </c>
@@ -9063,14 +9102,14 @@
         <v>6.4895833333331971E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>18</v>
       </c>
-      <c r="B21" s="10">
+      <c r="B21" s="9">
         <v>19.899999999999999</v>
       </c>
-      <c r="C21" s="10">
+      <c r="C21" s="9">
         <f>Table357[[#This Row],[Year (Since 1994)]]*1.116+1.2194</f>
         <v>21.307400000000001</v>
       </c>
@@ -9083,14 +9122,14 @@
         <v>7.0723618090452398E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>20</v>
       </c>
-      <c r="B22" s="10">
+      <c r="B22" s="9">
         <v>20.265000000000001</v>
       </c>
-      <c r="C22" s="10">
+      <c r="C22" s="9">
         <f>Table357[[#This Row],[Year (Since 1994)]]*1.116+1.2194</f>
         <v>23.539400000000001</v>
       </c>
@@ -9103,7 +9142,7 @@
         <v>0.16157907722674561</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E25" t="s">
         <v>15</v>
       </c>
@@ -9112,35 +9151,35 @@
         <v>0.31498067793128204</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>8</v>
       </c>
-      <c r="B31" s="9">
+      <c r="B31" s="8">
         <v>1.1160000000000001</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>4</v>
       </c>
-      <c r="B32" s="9">
+      <c r="B32" s="8">
         <v>1.2194</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>9</v>
       </c>
-      <c r="B35" s="9">
+      <c r="B35" s="8">
         <v>21</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>10</v>
       </c>
-      <c r="B36" s="9">
+      <c r="B36" s="8">
         <f xml:space="preserve"> B31*B35+B32</f>
         <v>24.655400000000004</v>
       </c>
@@ -9152,4 +9191,84 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DF9A6BB-64B9-4D6B-A1A7-2DF780FED969}">
+  <dimension ref="A1:A16"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>